--- a/banks/CHETWOOD FINANCIALS.xlsx
+++ b/banks/CHETWOOD FINANCIALS.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,18 +197,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chetwood Financial Limited — Cash Flow Summary by Year</a:t>
+              <a:t>Chetwood Financial Limited — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -235,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -259,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -283,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -307,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -350,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -390,13 +395,583 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Chetwood Financial Limited — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Chetwood Financial Limited — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$22:$AD$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Chetwood Financial Limited — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$29:$AL$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -428,30 +1003,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,30 +1036,30 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,30 +1069,30 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,30 +1102,30 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q9</f>
+              <f>'Overview'!AO9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$9:$V$9</f>
+              <f>'Overview'!$AP$9:$AT$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -560,30 +1135,30 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q10</f>
+              <f>'Overview'!AO10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$10:$V$10</f>
+              <f>'Overview'!$AP$10:$AT$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -593,30 +1168,30 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q11</f>
+              <f>'Overview'!AO11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$11:$V$11</f>
+              <f>'Overview'!$AP$11:$AT$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -648,8 +1223,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -688,12 +1263,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -703,9 +1278,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -715,19 +1290,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>86</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1025,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1048,6 +1689,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,14 +1725,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£'000)</t>
+          <t>Balance Sheet Summary (£'000)</t>
         </is>
       </c>
     </row>
@@ -1127,27 +1792,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021†</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024*</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1156,279 +1821,279 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>43038</v>
+        <v>4532547</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>189520</v>
+        <v>3077904</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>653419</v>
+        <v>1494541</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>16976</v>
+        <v>400038</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-92120</v>
+        <v>216524</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-92120</v>
+        <v>216524</v>
       </c>
       <c r="K6" t="n">
-        <v>16976</v>
+        <v>400038</v>
       </c>
       <c r="L6" t="n">
-        <v>653419</v>
+        <v>1494541</v>
       </c>
       <c r="M6" t="n">
-        <v>189520</v>
+        <v>3077904</v>
       </c>
       <c r="N6" t="n">
-        <v>43038</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>4532547</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>28</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>29.3</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>26.6</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AT6" t="n">
         <v>15.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-741638</v>
+        <v>2691247</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-389775</v>
+        <v>1833411</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-124128</v>
+        <v>649179</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-177719</v>
+        <v>302546</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>26853</v>
+        <v>156249</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>26853</v>
+        <v>156249</v>
       </c>
       <c r="K7" t="n">
-        <v>-177719</v>
+        <v>302546</v>
       </c>
       <c r="L7" t="n">
-        <v>-124128</v>
+        <v>649179</v>
       </c>
       <c r="M7" t="n">
-        <v>-389775</v>
+        <v>1833411</v>
       </c>
       <c r="N7" t="n">
-        <v>-741638</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>2691247</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>28</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>29.3</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>26.6</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AT7" t="n">
         <v>15.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) financing activities</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>500016</v>
+        <v>3812429</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>98027</v>
+        <v>2856737</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>84573</v>
+        <v>1383305</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>183068</v>
+        <v>322625</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>28960</v>
+        <v>160015</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) financing activities</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28960</v>
+        <v>160015</v>
       </c>
       <c r="K8" t="n">
-        <v>183068</v>
+        <v>322625</v>
       </c>
       <c r="L8" t="n">
-        <v>84573</v>
+        <v>1383305</v>
       </c>
       <c r="M8" t="n">
-        <v>98027</v>
+        <v>2856737</v>
       </c>
       <c r="N8" t="n">
-        <v>500016</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>3812429</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="AP8" t="n">
         <v>28</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AQ8" t="n">
         <v>29.3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AR8" t="n">
         <v>26.6</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AT8" t="n">
         <v>15.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Closing cash and cash equivalents</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>387550</v>
+        <v>196143</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>586134</v>
+        <v>173082</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>688362</v>
+        <v>92483</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>74498</v>
+        <v>65993</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>52173</v>
+        <v>50830</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Closing cash and cash equivalents</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>52173</v>
+        <v>50830</v>
       </c>
       <c r="K9" t="n">
-        <v>74498</v>
+        <v>65993</v>
       </c>
       <c r="L9" t="n">
-        <v>688362</v>
+        <v>92483</v>
       </c>
       <c r="M9" t="n">
-        <v>586134</v>
+        <v>173082</v>
       </c>
       <c r="N9" t="n">
-        <v>387550</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>196143</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="AP9" t="n">
         <v>23.4</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AQ9" t="n">
         <v>14.58</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AR9" t="n">
         <v>6.01</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AT9" t="n">
         <v>5.19</v>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="AP10" t="n">
         <v>51086</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AQ10" t="n">
         <v>4823</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AR10" t="n">
         <v>1015</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AT10" t="n">
         <v>194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pillar 3 Key Metrics</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+          <t>Profit &amp; Loss Summary (£'000)</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="AP11" t="n">
         <v>146.5</v>
       </c>
-      <c r="S11" t="n">
+      <c r="AQ11" t="n">
         <v>162.9</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AR11" t="n">
         <v>243</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AT11" t="n">
         <v>145</v>
       </c>
     </row>
@@ -1463,177 +2128,831 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024*</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>54238</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>45989</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>21471</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>27428</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>14447</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>14447</v>
+      </c>
+      <c r="S13" t="n">
+        <v>27428</v>
+      </c>
+      <c r="T13" t="n">
+        <v>21471</v>
+      </c>
+      <c r="U13" t="n">
+        <v>45989</v>
+      </c>
+      <c r="V13" t="n">
+        <v>54238</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-57209</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-53995</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-56119</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-30809</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-22372</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-22372</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-30809</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-56119</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-53995</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-57209</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Loss after tax and loss for the year</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>-4702</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-8861</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-58148</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-29753</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-21310</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Loss after tax and loss for the year</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>-21310</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-29753</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-58148</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-8861</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-4702</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024*</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024*</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>173082</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>92483</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>65993</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>50830</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>43067</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>43067</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>50830</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>65993</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>92483</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>173082</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-4084</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-8685</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-58324</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-29873</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-21339</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>-21339</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-29873</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-58324</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-8685</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-4084</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other movements, net</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>27145</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>89284</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>84814</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>45036</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>29102</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Other movements, net</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>29102</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>45036</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>84814</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>89284</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>27145</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>196143</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>173082</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>92483</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>65993</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>50830</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>50830</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>65993</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>92483</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>173082</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>196143</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FY2024*</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>FY2024*</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from operating activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>43038</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>189520</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>653419</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>16976</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-92120</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash from operating activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>-92120</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>16976</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>653419</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>189520</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>43038</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-741638</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-389775</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>-124128</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-177719</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>26853</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>26853</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-177719</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-124128</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-389775</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-741638</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>500016</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>98027</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>84573</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>28960</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>28960</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>183068</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>84573</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>98027</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>500016</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Closing cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>387550</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>586134</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>688362</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>74498</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>52173</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Closing cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>52173</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>74498</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>688362</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>586134</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>387550</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FY2024*</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>26.6%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>29.3%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>26.6%</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>29.3%</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>26.6%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>29.3%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>5.19%</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>6.01%</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>14.58%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>23.4%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>194%</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>1,015%</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>4,823%</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>51,086%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>145%</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>243%</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>162.9%</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>146.5%</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note.</t>
         </is>
@@ -1641,7 +2960,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A40:F40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1654,7 +2973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1668,14 +2987,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Leverage Ratio</t>
+          <t>Chetwood Financial Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000 / %</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -1714,60 +3033,40 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Leverage ratio total exposure measure</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>3615720</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
       </c>
       <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n">
-        <v>1519817</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>394658</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>216375</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Leverage ratio (%)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>6.01%</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>14.58%</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>23.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. Unlike Barclays/Monzo, Chetwood's disclosures do not distinguish an 'excluding/including claims on central banks' basis in any year - a single leverage ratio definition is used throughout (Tier 1 capital / total exposure measure). FY2021 used a pre-KM1 narrative table; FY2022 onward uses the formal KM1 rows 13-14.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="150" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
@@ -1780,8 +3079,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1793,7 +3092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1807,14 +3106,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — LCR</t>
+          <t>Chetwood Financial Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000 / %</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -1853,112 +3152,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total high-quality liquid assets (HQLA) (weighted value - average)</t>
+          <t>Total capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>897493</v>
+        <v>187605</v>
       </c>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n">
-        <v>302266</v>
+        <v>91268</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>67841</v>
-      </c>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Cash outflows - total weighted value</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>489794</v>
-      </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n">
-        <v>52035</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>5627</v>
-      </c>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Cash inflows - total weighted value</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>28009</v>
-      </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n">
-        <v>15169</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>13656</v>
-      </c>
-      <c r="F6" s="6" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Total net cash outflows (adjusted value)</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>461785</v>
-      </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n">
-        <v>36865</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>1407</v>
-      </c>
-      <c r="F7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity Coverage Ratio (%)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>194%</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>1,015%</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>4,823%</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>51,086%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. FY2021 disclosed only the headline ratio in narrative form (no HQLA/outflow £ breakdown was published that year - the formal KM1 liquidity rows were introduced from FY2022). Chetwood's LCR ratios are extremely high because, as a young/small deposit-taker at the time, its regulatory outflow assumptions were small relative to its liquid asset holdings - this is as disclosed by Chetwood, not a transcription error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+        <v>57554</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>50637</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. Equal to CET1/Tier 1 capital in every year shown - Chetwood has no Tier 2 capital either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
@@ -1971,8 +3190,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1984,7 +3203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1998,14 +3217,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — NSFR</t>
+          <t>Chetwood Financial Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000 / %</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -2044,76 +3263,40 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total available stable funding</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>3677559</v>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
       </c>
       <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n">
-        <v>1387511</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>380549</v>
-      </c>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Total required stable funding</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>2536343</v>
-      </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n">
-        <v>572002</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>233566</v>
-      </c>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Net Stable Funding Ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>145%</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>243%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>162.9%</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>146.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. FY2021's NSFR figure (146.5%) is quoted exactly as printed in the FY2021 Pillar 3 report, which oddly labels it 'as at the 31 March 2020' in a document otherwise dated 'as at 31 March 2021' - this looks like a typo in Chetwood's own document, but it is reproduced verbatim rather than silently corrected; no £ breakdown was published for FY2021 (the formal KM1 NSFR rows were introduced from FY2022).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="150" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
@@ -2126,8 +3309,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2153,6 +3336,807 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Chetwood Financial Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024*</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1233321</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>824623</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>343668</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>196750</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>178987</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2024 is populated (unlike the other Pillar 3 sheets) because the FY2025 Pillar 3 document's own OV1 table (Section 6.3) discloses a full FY2024 comparative Total row (824,623) - the same figure the RWA Breakdown sheet's FY2024 column sums to. The KM1 template (Section 5) and LCR/NSFR/Overall Capital Requirement tables (Sections 5-6.6) that supply every other Pillar 3 metric on this workbook are all single-column ('as at 31 March 2025' only, no FY2024 comparative) - confirmed by reading the full FY2025 Pillar 3 document page by page, so CET1/Tier 1/Total Capital/all ratios/Leverage/LCR/NSFR/MREL genuinely remain blank for FY2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources (see entity note on Cash Flow Statement sheet):
+FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
+FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000, Group/consolidated basis (FY2021: standalone entity). See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024* (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021† (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>RWA by risk category</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (excluding CCR)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1017779</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>703828</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>290536</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>179962</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>126942</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (CCR)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>23777</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>13638</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>4143</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1937</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Securitisation exposures in the non-trading book</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>102610</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>62980</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>18124</v>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>89154</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>30865</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>14852</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>51595</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1233321</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>824623</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>343668</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>196750</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>178987</v>
+      </c>
+    </row>
+    <row r="11" ht="220" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Chetwood's own Pillar 3 Disclosures, Section 6 'Overview of RWAs' (OV1 template from FY2022 onward; FY2021 uses an equivalent pre-KM1 category table).
+FY2025/FY2024: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 6.3, which unlike the standalone FY2024 KM1 gap noted on the other Pillar 3 sheets, discloses its OV1 table's FY2024 comparative RWEA column in full - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
+FY2023/FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 8.3 (OV1 table with FY2022 comparative) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 5.4 (pre-KM1 category table) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf
+ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021 (marked †), which is Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement for FY2021. Companies House confirms FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2021 is included on a standalone basis and clearly flagged, rather than omitted.
+FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+FINDING: the other Pillar 3 sheets in this workbook leave FY2024 blank because no dedicated 'as at 31 March 2024' Pillar 3 document was ever published - true for the CET1/Tier 1/Total Capital/ratio figures. However the FY2025 Pillar 3 document's own OV1 table (used here) discloses a full FY2024 comparative RWEA-by-category column, so RWA Breakdown alone can be populated for FY2024 even though the other Pillar 3 sheets cannot.
+PRESENTATION NOTE: FY2021's pre-KM1 category table has no separate 'Securitisation' line (Chetwood had no securitised exposures that early) and combines credit valuation adjustment into Counterparty credit risk rather than breaking it out - both blank rather than assumed zero-and-separate.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A11:F11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited — Leverage Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 / %</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024*</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio total exposure measure</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>3615720</v>
+      </c>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n">
+        <v>1519817</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>394658</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>216375</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>6.01%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>14.58%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>23.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. Unlike Barclays/Monzo, Chetwood's disclosures do not distinguish an 'excluding/including claims on central banks' basis in any year - a single leverage ratio definition is used throughout (Tier 1 capital / total exposure measure). FY2021 used a pre-KM1 narrative table; FY2022 onward uses the formal KM1 rows 13-14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Sources (see entity note on Cash Flow Statement sheet):
+FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
+FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 / %</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024*</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total high-quality liquid assets (HQLA) (weighted value - average)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>897493</v>
+      </c>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n">
+        <v>302266</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>67841</v>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash outflows - total weighted value</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>489794</v>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n">
+        <v>52035</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>5627</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Cash inflows - total weighted value</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>28009</v>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n">
+        <v>15169</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>13656</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Total net cash outflows (adjusted value)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>461785</v>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n">
+        <v>36865</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1407</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>194%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>1,015%</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>4,823%</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>51,086%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. FY2021 disclosed only the headline ratio in narrative form (no HQLA/outflow £ breakdown was published that year - the formal KM1 liquidity rows were introduced from FY2022). Chetwood's LCR ratios are extremely high because, as a young/small deposit-taker at the time, its regulatory outflow assumptions were small relative to its liquid asset holdings - this is as disclosed by Chetwood, not a transcription error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Sources (see entity note on Cash Flow Statement sheet):
+FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
+FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 / %</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024*</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total available stable funding</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>3677559</v>
+      </c>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n">
+        <v>1387511</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>380549</v>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>2536343</v>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n">
+        <v>572002</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>233566</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>145%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>243%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>162.9%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>146.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. FY2021's NSFR figure (146.5%) is quoted exactly as printed in the FY2021 Pillar 3 report, which oddly labels it 'as at the 31 March 2020' in a document otherwise dated 'as at 31 March 2021' - this looks like a typo in Chetwood's own document, but it is reproduced verbatim rather than silently corrected; no £ breakdown was published for FY2021 (the formal KM1 NSFR rows were introduced from FY2022).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Sources (see entity note on Cash Flow Statement sheet):
+FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
+FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Chetwood Financial Limited — MREL Ratio</t>
         </is>
       </c>
@@ -2253,6 +4237,2057 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited — Consolidated Statement of Financial Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000. Consolidated (Group) basis except FY2021 († standalone entity - Group and Company are identical that year). See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024* (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021† (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents / Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>387550</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>586134</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>688362</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>74498</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>52173</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial assets</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>49410</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>58475</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>4565</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>138</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Investment in debt securities</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1321666</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>537291</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>129595</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>4883</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>2691247</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1833411</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>649179</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>302546</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>156249</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fair value adjustments on hedged assets</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>5615</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>12926</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-1069</v>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>63998</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>43910</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>18897</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>8620</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>3486</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Prepayments and accrued income</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>4177</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>4353</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>930</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>913</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>883</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>1246</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>690</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>2044</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>521</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>2767</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>7669</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>5927</v>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>4532547</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3077904</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1494541</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>400038</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>216524</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Customer deposits</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>3812429</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>2856737</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1383305</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>322625</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>160015</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Fair value adjustments on hedged liabilities</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>621</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-1073</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-3286</v>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>2252</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>2909</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>591</v>
+      </c>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Amounts owed to credit institutions</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>488932</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>9107</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Debt securities in issue</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Accruals</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>10864</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>9766</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>7279</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>6790</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>4127</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>12216</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>18713</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>6645</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>457</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>8795</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>8564</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>6100</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>3582</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>206</v>
+      </c>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>4336404</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>2904822</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1402058</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>334045</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>165694</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Called up share capital</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>253913</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>253730</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>253297</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>168688</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>113688</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Share premium account</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>118236</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>2851</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>2851</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>2851</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Capital redemption reserve / Capital contribution</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>6247</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>6247</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>6247</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>6247</v>
+      </c>
+      <c r="F30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>877</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>692</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>232</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>203</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Retained losses</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>-183900</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>-179775</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-170914</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-112766</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-65823</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Merger reserve</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>770</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>770</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>770</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>770</v>
+      </c>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>196143</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>173082</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>92483</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>65993</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>50830</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>4532547</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>3077904</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1494541</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>400038</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>216524</v>
+      </c>
+    </row>
+    <row r="37" ht="220" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Chetwood Financial Limited's own Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, transcribed from each year's own Annual Report (not a later year's comparative column, except where noted). See entity note below re: FY2021 (standalone) and the FY2024 P&amp;L OCR-corruption note.
+FY2025/FY2024: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2025, p.44-47 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
+FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.24-27 (prior-year comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (As with the Cash Flow Statement, the FY2023 Annual Report's own PDF has a text-encoding fault; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
+FY2022/FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.22-25 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, Group and Company for FY2021) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
+ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021 (marked †), which is Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement for FY2021. Companies House confirms FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2021 is included on a standalone basis and clearly flagged, rather than omitted.
+FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
+PRESENTATION NOTE: 'Cash and cash equivalents' (FY2023-25) and 'Loans and advances to banks' (FY2021-22) are the same balance-sheet line under two labels - shown on one row. 'Capital redemption reserve' (FY2023-25) and 'Capital contribution' (FY2022, first appearing that year as a debt waiver from the ultimate controlling party) are the same £6,247k reserve under two labels - shown on one row. P&amp;L structure changed across the five years as the business grew: FY2025 nets fee income/expense into a single 'Net fee and commission (expense)/income' line with no separate 'Other income' row; FY2022-23 include a 'Net gain arising from derecognition of financial assets at amortised cost' line with no FY2024-25 equivalent; only FY2024-25 disclose 'Deferred tax liabilities' or a 'Goodwill' balance sheet line, both absent 2021-23; only FY2025 discloses 'Debt securities in issue' as a live balance (£89k), though the line existed as a zero balance from FY2024. Blank cells indicate that year's report did not disclose that specific line.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A37:F37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="66" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited — Consolidated Statement of Total Comprehensive Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000. Consolidated (Group) basis except FY2021 († standalone entity - Group and Company are identical that year). See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024* (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021† (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest income calculated using the effective interest rate method</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>216716</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>149127</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>35406</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>29755</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>17567</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest payable and similar charges</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-174940</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-104811</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-14914</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-2542</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-3135</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>41776</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>44316</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>20492</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>27213</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>14432</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission income</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>851</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1794</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>2731</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>244</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission expense</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-4758</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-3162</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-718</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-152</v>
+      </c>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fee and commission income/(expense)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>-3907</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-1368</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="F10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Net income/(expense) from financial instruments held at fair value through profit and loss</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>16369</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>3041</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>-1160</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>54238</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>45989</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>21471</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>27428</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>14447</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-57209</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-53995</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-56119</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-30809</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-22372</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Impairment of loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>-1731</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>-855</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-25126</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-30737</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-13375</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Net gain arising from derecognition of financial assets measured at amortised cost</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n">
+        <v>1727</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>4369</v>
+      </c>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Loss before taxation</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>-4702</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-8861</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-58047</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-29749</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-21300</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Taxation</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n">
+        <v>-101</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Loss after tax and loss for the year</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>-4702</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-8861</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-58148</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-29753</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-21310</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(expense)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Fair value gains/(losses) on debt instruments during the year</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>824</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-178</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-120</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Debt instruments at FVOCI - reclassified to profit or loss</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n">
+        <v>-34</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax on fair value gains on debt instruments</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-206</v>
+      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Total other comprehensive income/(expense) for the year</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>618</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>176</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-176</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-29</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-4084</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>-8685</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-58324</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-29873</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-21339</v>
+      </c>
+    </row>
+    <row r="27" ht="220" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Chetwood Financial Limited's own Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, transcribed from each year's own Annual Report (not a later year's comparative column, except where noted). See entity note below re: FY2021 (standalone) and the FY2024 P&amp;L OCR-corruption note.
+FY2025/FY2024: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2025, p.44-47 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
+FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.24-27 (prior-year comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (As with the Cash Flow Statement, the FY2023 Annual Report's own PDF has a text-encoding fault; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
+FY2022/FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.22-25 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, Group and Company for FY2021) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
+ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021 (marked †), which is Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement for FY2021. Companies House confirms FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2021 is included on a standalone basis and clearly flagged, rather than omitted.
+FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
+PRESENTATION NOTE: 'Cash and cash equivalents' (FY2023-25) and 'Loans and advances to banks' (FY2021-22) are the same balance-sheet line under two labels - shown on one row. 'Capital redemption reserve' (FY2023-25) and 'Capital contribution' (FY2022, first appearing that year as a debt waiver from the ultimate controlling party) are the same £6,247k reserve under two labels - shown on one row. P&amp;L structure changed across the five years as the business grew: FY2025 nets fee income/expense into a single 'Net fee and commission (expense)/income' line with no separate 'Other income' row; FY2022-23 include a 'Net gain arising from derecognition of financial assets at amortised cost' line with no FY2024-25 equivalent; only FY2024-25 disclose 'Deferred tax liabilities' or a 'Goodwill' balance sheet line, both absent 2021-23; only FY2025 discloses 'Debt securities in issue' as a live balance (£89k), though the line existed as a zero balance from FY2024. Blank cells indicate that year's report did not disclose that specific line.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A27:F27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis (FY2021 standalone entity), £'000, chronological (oldest to newest). See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Called-up Share Capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Share Premium</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Retained losses</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Share-based payment reserve</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Debt securities revaluation reserve</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Capital redemption/contribution reserve</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Merger reserve</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>At 1 April 2020</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>84688</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>2851</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-44513</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n">
+        <v>43067</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the period (FY2021)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n">
+        <v>-21310</v>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n">
+        <v>-21310</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Net changes in fair value</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Reclassified to income statement</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n">
+        <v>-34</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Equity-settled share-based payment transactions</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Issue of shares</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>29000</v>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2021</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>113688</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2851</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-65823</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n">
+        <v>50830</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the period (FY2022)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n">
+        <v>-29753</v>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n">
+        <v>-29753</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Retained losses acquired on purchase of subsidiary</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n">
+        <v>-17190</v>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n">
+        <v>-17190</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Net changes in fair value</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n">
+        <v>-120</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Equity-settled share-based payment transactions</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n">
+        <v>209</v>
+      </c>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Debt waiver by ultimate controlling party</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n">
+        <v>6247</v>
+      </c>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n">
+        <v>6247</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Merger reserve arising on consolidation</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n">
+        <v>770</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Issue of shares</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2022</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>168688</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2851</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-112766</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>323</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>6247</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>770</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>65993</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the period (FY2023)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n">
+        <v>-58148</v>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n">
+        <v>-58148</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Net changes in fair value</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n">
+        <v>-58</v>
+      </c>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n">
+        <v>-58</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Reclassified to income statement</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Equity-settled share-based payment transactions</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Issue of shares</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>84609</v>
+      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n">
+        <v>84609</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2023</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>253297</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>2851</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-170914</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>408</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-176</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>6247</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>770</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>92483</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the period (FY2024)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n">
+        <v>-8861</v>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n">
+        <v>-8861</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Net changes in fair value</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Reclassified to income statement</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Equity-settled share-based payment transactions</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n">
+        <v>284</v>
+      </c>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Issue of shares</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>433</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>88561</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n">
+        <v>89000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2024</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>253730</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-179775</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>692</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>6247</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>770</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>173082</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the period (FY2025)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n">
+        <v>-4702</v>
+      </c>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n">
+        <v>-4702</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Net changes in fair value</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n">
+        <v>824</v>
+      </c>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Tax on other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n">
+        <v>-206</v>
+      </c>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n">
+        <v>-206</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Equity-settled share-based payment transactions</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Reclassified to retained losses</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n">
+        <v>577</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>-577</v>
+      </c>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Issue of shares</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>183</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>26818</v>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n">
+        <v>27001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2025</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>253913</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>118236</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>-183900</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>259</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>618</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>6247</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>770</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>196143</v>
+      </c>
+    </row>
+    <row r="39" ht="220" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Chetwood Financial Limited's own Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, transcribed from each year's own Annual Report (not a later year's comparative column, except where noted). See entity note below re: FY2021 (standalone) and the FY2024 P&amp;L OCR-corruption note.
+FY2025/FY2024: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2025, p.44-47 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
+FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.24-27 (prior-year comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (As with the Cash Flow Statement, the FY2023 Annual Report's own PDF has a text-encoding fault; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
+FY2022/FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.22-25 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, Group and Company for FY2021) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
+ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021 (marked †), which is Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement for FY2021. Companies House confirms FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2021 is included on a standalone basis and clearly flagged, rather than omitted.
+FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
+PRESENTATION NOTE: 'Cash and cash equivalents' (FY2023-25) and 'Loans and advances to banks' (FY2021-22) are the same balance-sheet line under two labels - shown on one row. 'Capital redemption reserve' (FY2023-25) and 'Capital contribution' (FY2022, first appearing that year as a debt waiver from the ultimate controlling party) are the same £6,247k reserve under two labels - shown on one row. P&amp;L structure changed across the five years as the business grew: FY2025 nets fee income/expense into a single 'Net fee and commission (expense)/income' line with no separate 'Other income' row; FY2022-23 include a 'Net gain arising from derecognition of financial assets at amortised cost' line with no FY2024-25 equivalent; only FY2024-25 disclose 'Deferred tax liabilities' or a 'Goodwill' balance sheet line, both absent 2021-23; only FY2025 discloses 'Debt securities in issue' as a live balance (£89k), though the line existed as a zero balance from FY2024. Blank cells indicate that year's report did not disclose that specific line.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A39:I39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3391,16 +7426,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3411,441 +7446,423 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — CET1 Capital</t>
+          <t>Chetwood Financial Limited — Asset Quality / Credit Risk Disclosures</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000, Group/consolidated basis (FY2021: standalone entity)</t>
+          <t>£'000. Consolidated (Group) basis except FY2021 († standalone entity). See source note at bottom.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£'000)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024* (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£'000)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£'000)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021†</t>
+          <t>FY2021† (£'000)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>187605</v>
-      </c>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Loan book by IFRS 9 stage (secured + unsecured combined)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n">
-        <v>91268</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>57554</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>50637</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources (see entity note on Cash Flow Statement sheet):
-FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 - gross carrying amount</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>2129852</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1632661</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>594912</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>273792</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>145496</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 - gross carrying amount</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>520622</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>186714</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>47246</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>24685</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>22064</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 - gross carrying amount</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>15152</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>30817</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>26237</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>21297</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>14585</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Purchased or originated credit-impaired (POCI) - gross carrying amount</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>284</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total gross loans and advances to customers (amortised cost)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2665626</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1850192</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>668679</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>320324</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>182145</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 - ECL allowance</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>-1356</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>-1887</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>-5118</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>-7791</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-6292</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 - ECL allowance</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>-2912</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>-4073</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>-8469</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>-8517</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-7149</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 - ECL allowance</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>-5974</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>-24527</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>-23300</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>-18255</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-12455</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>POCI - ECL allowance</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-17</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-13</v>
+      </c>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total ECL allowance</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-10242</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-30487</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-36904</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-34576</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-25896</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Net loans and advances to customers (amortised cost)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>2655384</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1819705</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>631775</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>285748</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>156249</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Derived ratios</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 / NPL ratio (Stage 3 gross / total gross)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>0.57%</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>3.92%</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>6.65%</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>8.01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>ECL coverage ratio (total allowance / total gross)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>5.52%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>10.79%</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>14.22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 coverage ratio (Stage 3 allowance / Stage 3 gross)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>39.43%</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>79.59%</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>88.81%</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>85.71%</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>85.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="220" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Chetwood Financial Limited's own Credit Risk / Note 36 (37 in earlier years) disclosures, combining the separately-disclosed 'unsecured lending at amortised cost' and 'secured lending' IFRS 9 stage tables (secured mortgage lending only exists from FY2022, when CHL Mortgages for Intermediaries Limited was acquired - FY2021 is unsecured lending only, and ties exactly to that year's Balance Sheet loan figure).
+FY2025/FY2024: Annual Report 2025, p.96-100 (Note 36.2/36.3 Credit quality) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
+FY2023: Annual Report 2024, p.51-52 (Note 37, FY2023 comparative tables) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf
+FY2022/FY2021: Annual Report 2022, p.49-52 (Note 31.2 Credit quality) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
+ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021 (marked †), which is Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement for FY2021. Companies House confirms FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2021 is included on a standalone basis and clearly flagged, rather than omitted.
+FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+PRESENTATION NOTE: these Note 36/37 tables report gross/net loans and advances measured at amortised cost only. The Balance Sheet's own 'Loans and advances to customers' line is larger in every year from FY2022 onward (e.g. FY2025: £2,691,247k on the Balance Sheet vs £2,665,626k gross / £2,655,384k net summed here) because some loans are measured at fair value through profit or loss and fall outside this amortised-cost IFRS 9 note - this gap is a genuine measurement-basis difference disclosed by the Bank, not a transcription error, and is not force-reconciled here. FY2021 is the exception: with no secured book yet and no FVTPL loans, the combined stage total ties to the Balance Sheet exactly (£156,249k both ways).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Chetwood Financial Limited — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>% of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024*</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021†</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>26.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>29.3%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. FY2021 is as stated in the source (rounded to the nearest whole percent; no decimal figure was disclosed that year).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources (see entity note on Cash Flow Statement sheet):
-FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Chetwood Financial Limited — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024*</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021†</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>187605</v>
-      </c>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n">
-        <v>91268</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>57554</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>50637</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. Equal to CET1 capital in every year shown - Chetwood has no Additional Tier 1 (AT1) instruments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources (see entity note on Cash Flow Statement sheet):
-FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Chetwood Financial Limited — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>% of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024*</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021†</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>26.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>29.3%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources (see entity note on Cash Flow Statement sheet):
-FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3871,14 +7888,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Total Capital</t>
+          <t>Chetwood Financial Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>£'000, Group/consolidated basis (FY2021: standalone entity)</t>
         </is>
       </c>
     </row>
@@ -3917,7 +7934,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
+          <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
@@ -3937,7 +7954,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. Equal to CET1/Tier 1 capital in every year shown - Chetwood has no Tier 2 capital either.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note.</t>
         </is>
       </c>
     </row>
@@ -3982,7 +7999,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Total Capital Ratio</t>
+          <t>Chetwood Financial Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -4028,7 +8045,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -4056,7 +8073,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. FY2021 is as stated in the source (rounded to the nearest whole percent; no decimal figure was disclosed that year).</t>
         </is>
       </c>
     </row>
@@ -4101,7 +8118,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Total RWAs</t>
+          <t>Chetwood Financial Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -4147,27 +8164,27 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
+          <t>Tier 1 capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1233321</v>
+        <v>187605</v>
       </c>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n">
-        <v>343668</v>
+        <v>91268</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>196750</v>
+        <v>57554</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>178987</v>
+        <v>50637</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. Equal to CET1 capital in every year shown - Chetwood has no Additional Tier 1 (AT1) instruments.</t>
         </is>
       </c>
     </row>

--- a/banks/CHETWOOD FINANCIALS.xlsx
+++ b/banks/CHETWOOD FINANCIALS.xlsx
@@ -236,7 +236,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!I6</f>
+              <f>'Overview'!K6</f>
             </strRef>
           </tx>
           <spPr>
@@ -246,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$L$5:$R$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$6:$N$6</f>
+              <f>'Overview'!$L$6:$R$6</f>
             </numRef>
           </val>
         </ser>
@@ -260,7 +260,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!I7</f>
+              <f>'Overview'!K7</f>
             </strRef>
           </tx>
           <spPr>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$L$5:$R$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$7:$N$7</f>
+              <f>'Overview'!$L$7:$R$7</f>
             </numRef>
           </val>
         </ser>
@@ -284,7 +284,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!I8</f>
+              <f>'Overview'!K8</f>
             </strRef>
           </tx>
           <spPr>
@@ -294,12 +294,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$L$5:$R$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$8:$N$8</f>
+              <f>'Overview'!$L$8:$R$8</f>
             </numRef>
           </val>
         </ser>
@@ -308,7 +308,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!I9</f>
+              <f>'Overview'!K9</f>
             </strRef>
           </tx>
           <spPr>
@@ -318,12 +318,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$L$5:$R$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$9:$N$9</f>
+              <f>'Overview'!$L$9:$R$9</f>
             </numRef>
           </val>
         </ser>
@@ -434,7 +434,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q13</f>
+              <f>'Overview'!U13</f>
             </strRef>
           </tx>
           <spPr>
@@ -444,12 +444,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$V$12:$AB$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$13:$V$13</f>
+              <f>'Overview'!$V$13:$AB$13</f>
             </numRef>
           </val>
         </ser>
@@ -458,7 +458,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q14</f>
+              <f>'Overview'!U14</f>
             </strRef>
           </tx>
           <spPr>
@@ -468,12 +468,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$V$12:$AB$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$14:$V$14</f>
+              <f>'Overview'!$V$14:$AB$14</f>
             </numRef>
           </val>
         </ser>
@@ -482,7 +482,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q15</f>
+              <f>'Overview'!U15</f>
             </strRef>
           </tx>
           <spPr>
@@ -492,12 +492,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$V$12:$AB$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$15:$V$15</f>
+              <f>'Overview'!$V$15:$AB$15</f>
             </numRef>
           </val>
         </ser>
@@ -608,7 +608,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y19</f>
+              <f>'Overview'!AE19</f>
             </strRef>
           </tx>
           <spPr>
@@ -618,12 +618,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AF$18:$AL$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$19:$AD$19</f>
+              <f>'Overview'!$AF$19:$AL$19</f>
             </numRef>
           </val>
         </ser>
@@ -632,7 +632,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y20</f>
+              <f>'Overview'!AE20</f>
             </strRef>
           </tx>
           <spPr>
@@ -642,12 +642,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AF$18:$AL$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$20:$AD$20</f>
+              <f>'Overview'!$AF$20:$AL$20</f>
             </numRef>
           </val>
         </ser>
@@ -656,7 +656,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y21</f>
+              <f>'Overview'!AE21</f>
             </strRef>
           </tx>
           <spPr>
@@ -666,12 +666,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AF$18:$AL$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$21:$AD$21</f>
+              <f>'Overview'!$AF$21:$AL$21</f>
             </numRef>
           </val>
         </ser>
@@ -680,7 +680,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y22</f>
+              <f>'Overview'!AE22</f>
             </strRef>
           </tx>
           <spPr>
@@ -690,12 +690,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AF$18:$AL$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$22:$AD$22</f>
+              <f>'Overview'!$AF$22:$AL$22</f>
             </numRef>
           </val>
         </ser>
@@ -806,7 +806,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG26</f>
+              <f>'Overview'!AO26</f>
             </strRef>
           </tx>
           <spPr>
@@ -816,12 +816,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AP$25:$AV$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$26:$AL$26</f>
+              <f>'Overview'!$AP$26:$AV$26</f>
             </numRef>
           </val>
         </ser>
@@ -830,7 +830,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG27</f>
+              <f>'Overview'!AO27</f>
             </strRef>
           </tx>
           <spPr>
@@ -840,12 +840,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AP$25:$AV$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$27:$AL$27</f>
+              <f>'Overview'!$AP$27:$AV$27</f>
             </numRef>
           </val>
         </ser>
@@ -854,7 +854,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG28</f>
+              <f>'Overview'!AO28</f>
             </strRef>
           </tx>
           <spPr>
@@ -864,12 +864,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AP$25:$AV$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$28:$AL$28</f>
+              <f>'Overview'!$AP$28:$AV$28</f>
             </numRef>
           </val>
         </ser>
@@ -878,7 +878,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG29</f>
+              <f>'Overview'!AO29</f>
             </strRef>
           </tx>
           <spPr>
@@ -888,12 +888,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AP$25:$AV$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$29:$AL$29</f>
+              <f>'Overview'!$AP$29:$AV$29</f>
             </numRef>
           </val>
         </ser>
@@ -1003,7 +1003,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO6</f>
+              <f>'Overview'!AY6</f>
             </strRef>
           </tx>
           <spPr>
@@ -1021,12 +1021,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AZ$5:$BF$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$6:$AT$6</f>
+              <f>'Overview'!$AZ$6:$BF$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1036,7 +1036,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO7</f>
+              <f>'Overview'!AY7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1054,12 +1054,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AZ$5:$BF$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$7:$AT$7</f>
+              <f>'Overview'!$AZ$7:$BF$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1069,7 +1069,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO8</f>
+              <f>'Overview'!AY8</f>
             </strRef>
           </tx>
           <spPr>
@@ -1087,12 +1087,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AZ$5:$BF$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$8:$AT$8</f>
+              <f>'Overview'!$AZ$8:$BF$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1102,7 +1102,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO9</f>
+              <f>'Overview'!AY9</f>
             </strRef>
           </tx>
           <spPr>
@@ -1120,12 +1120,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AZ$5:$BF$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$9:$AT$9</f>
+              <f>'Overview'!$AZ$9:$BF$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1135,7 +1135,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO10</f>
+              <f>'Overview'!AY10</f>
             </strRef>
           </tx>
           <spPr>
@@ -1153,12 +1153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AZ$5:$BF$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$10:$AT$10</f>
+              <f>'Overview'!$AZ$10:$BF$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1168,7 +1168,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO11</f>
+              <f>'Overview'!AY11</f>
             </strRef>
           </tx>
           <spPr>
@@ -1186,12 +1186,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AZ$5:$BF$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$11:$AT$11</f>
+              <f>'Overview'!$AZ$11:$BF$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1666,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:BF40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1675,8 +1675,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
     <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
     <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
@@ -1713,6 +1713,18 @@
     <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
     <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
     <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
+    <col hidden="1" width="13" customWidth="1" min="47" max="47"/>
+    <col hidden="1" width="13" customWidth="1" min="48" max="48"/>
+    <col hidden="1" width="13" customWidth="1" min="49" max="49"/>
+    <col hidden="1" width="13" customWidth="1" min="50" max="50"/>
+    <col hidden="1" width="13" customWidth="1" min="51" max="51"/>
+    <col hidden="1" width="13" customWidth="1" min="52" max="52"/>
+    <col hidden="1" width="13" customWidth="1" min="53" max="53"/>
+    <col hidden="1" width="13" customWidth="1" min="54" max="54"/>
+    <col hidden="1" width="13" customWidth="1" min="55" max="55"/>
+    <col hidden="1" width="13" customWidth="1" min="56" max="56"/>
+    <col hidden="1" width="13" customWidth="1" min="57" max="57"/>
+    <col hidden="1" width="13" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1767,52 +1779,82 @@
           <t>FY2021†</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>FY2021†</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>FY2024*</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>FY2021†</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>FY2024*</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1839,41 +1881,53 @@
       <c r="F6" s="5" t="n">
         <v>216524</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" s="5" t="n">
+        <v>266053</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>77767</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
+        <v>77767</v>
+      </c>
+      <c r="M6" t="n">
+        <v>266053</v>
+      </c>
+      <c r="N6" t="n">
         <v>216524</v>
       </c>
-      <c r="K6" t="n">
+      <c r="O6" t="n">
         <v>400038</v>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>1494541</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>3077904</v>
       </c>
-      <c r="N6" t="n">
+      <c r="R6" t="n">
         <v>4532547</v>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="BB6" t="n">
         <v>28</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="BC6" t="n">
         <v>29.3</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="BD6" t="n">
         <v>26.6</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BF6" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -1898,41 +1952,53 @@
       <c r="F7" s="5" t="n">
         <v>156249</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" s="5" t="n">
+        <v>145022</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Loans and advances to customers</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
+        <v>46269</v>
+      </c>
+      <c r="M7" t="n">
+        <v>145022</v>
+      </c>
+      <c r="N7" t="n">
         <v>156249</v>
       </c>
-      <c r="K7" t="n">
+      <c r="O7" t="n">
         <v>302546</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>649179</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>1833411</v>
       </c>
-      <c r="N7" t="n">
+      <c r="R7" t="n">
         <v>2691247</v>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="BB7" t="n">
         <v>28</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="BC7" t="n">
         <v>29.3</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BD7" t="n">
         <v>26.6</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BF7" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -1957,41 +2023,53 @@
       <c r="F8" s="5" t="n">
         <v>160015</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="G8" s="5" t="n">
+        <v>210783</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>26107</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Customer deposits</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
+        <v>26107</v>
+      </c>
+      <c r="M8" t="n">
+        <v>210783</v>
+      </c>
+      <c r="N8" t="n">
         <v>160015</v>
       </c>
-      <c r="K8" t="n">
+      <c r="O8" t="n">
         <v>322625</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>1383305</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>2856737</v>
       </c>
-      <c r="N8" t="n">
+      <c r="R8" t="n">
         <v>3812429</v>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="BB8" t="n">
         <v>28</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="BC8" t="n">
         <v>29.3</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BD8" t="n">
         <v>26.6</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BF8" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -2016,60 +2094,72 @@
       <c r="F9" s="5" t="n">
         <v>50830</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="G9" s="5" t="n">
+        <v>51182</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>49484</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
+        <v>49484</v>
+      </c>
+      <c r="M9" t="n">
+        <v>51182</v>
+      </c>
+      <c r="N9" t="n">
         <v>50830</v>
       </c>
-      <c r="K9" t="n">
+      <c r="O9" t="n">
         <v>65993</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>92483</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>173082</v>
       </c>
-      <c r="N9" t="n">
+      <c r="R9" t="n">
         <v>196143</v>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="BB9" t="n">
         <v>23.4</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="BC9" t="n">
         <v>14.58</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BD9" t="n">
         <v>6.01</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BF9" t="n">
         <v>5.19</v>
       </c>
     </row>
     <row r="10">
-      <c r="AO10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="BB10" t="n">
         <v>51086</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="BC10" t="n">
         <v>4823</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BD10" t="n">
         <v>1015</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BF10" t="n">
         <v>194</v>
       </c>
     </row>
@@ -2079,21 +2169,21 @@
           <t>Profit &amp; Loss Summary (£'000)</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="BB11" t="n">
         <v>146.5</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="BC11" t="n">
         <v>162.9</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BD11" t="n">
         <v>243</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BF11" t="n">
         <v>145</v>
       </c>
     </row>
@@ -2128,27 +2218,47 @@
           <t>FY2021†</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>FY2021†</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>FY2024*</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2175,24 +2285,36 @@
       <c r="F13" s="5" t="n">
         <v>14447</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="G13" s="5" t="n">
+        <v>7673</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1699</v>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>Total income</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="V13" t="n">
+        <v>1699</v>
+      </c>
+      <c r="W13" t="n">
+        <v>7673</v>
+      </c>
+      <c r="X13" t="n">
         <v>14447</v>
       </c>
-      <c r="S13" t="n">
+      <c r="Y13" t="n">
         <v>27428</v>
       </c>
-      <c r="T13" t="n">
+      <c r="Z13" t="n">
         <v>21471</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AA13" t="n">
         <v>45989</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AB13" t="n">
         <v>54238</v>
       </c>
     </row>
@@ -2217,24 +2339,36 @@
       <c r="F14" s="5" t="n">
         <v>-22372</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="G14" s="5" t="n">
+        <v>-14413</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>-11240</v>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>Administrative expenses</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="V14" t="n">
+        <v>-11240</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-14413</v>
+      </c>
+      <c r="X14" t="n">
         <v>-22372</v>
       </c>
-      <c r="S14" t="n">
+      <c r="Y14" t="n">
         <v>-30809</v>
       </c>
-      <c r="T14" t="n">
+      <c r="Z14" t="n">
         <v>-56119</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AA14" t="n">
         <v>-53995</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AB14" t="n">
         <v>-57209</v>
       </c>
     </row>
@@ -2259,24 +2393,36 @@
       <c r="F15" s="5" t="n">
         <v>-21310</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="G15" s="5" t="n">
+        <v>-18314</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>-11536</v>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>Loss after tax and loss for the year</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="V15" t="n">
+        <v>-11536</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-18314</v>
+      </c>
+      <c r="X15" t="n">
         <v>-21310</v>
       </c>
-      <c r="S15" t="n">
+      <c r="Y15" t="n">
         <v>-29753</v>
       </c>
-      <c r="T15" t="n">
+      <c r="Z15" t="n">
         <v>-58148</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AA15" t="n">
         <v>-8861</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AB15" t="n">
         <v>-4702</v>
       </c>
     </row>
@@ -2318,27 +2464,47 @@
           <t>FY2021†</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
         <is>
           <t>FY2021†</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AK18" t="inlineStr">
         <is>
           <t>FY2024*</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AL18" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2365,24 +2531,36 @@
       <c r="F19" s="5" t="n">
         <v>43067</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="G19" s="5" t="n">
+        <v>49484</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>5783</v>
+      </c>
+      <c r="AE19" t="inlineStr">
         <is>
           <t>Opening equity</t>
         </is>
       </c>
-      <c r="Z19" t="n">
+      <c r="AF19" t="n">
+        <v>5783</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>49484</v>
+      </c>
+      <c r="AH19" t="n">
         <v>43067</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AI19" t="n">
         <v>50830</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AJ19" t="n">
         <v>65993</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AK19" t="n">
         <v>92483</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AL19" t="n">
         <v>173082</v>
       </c>
     </row>
@@ -2407,24 +2585,36 @@
       <c r="F20" s="5" t="n">
         <v>-21339</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="G20" s="5" t="n">
+        <v>-18314</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>-11536</v>
+      </c>
+      <c r="AE20" t="inlineStr">
         <is>
           <t>Total comprehensive income/(loss)</t>
         </is>
       </c>
-      <c r="Z20" t="n">
+      <c r="AF20" t="n">
+        <v>-11536</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-18314</v>
+      </c>
+      <c r="AH20" t="n">
         <v>-21339</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AI20" t="n">
         <v>-29873</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AJ20" t="n">
         <v>-58324</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AK20" t="n">
         <v>-8685</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AL20" t="n">
         <v>-4084</v>
       </c>
     </row>
@@ -2449,24 +2639,36 @@
       <c r="F21" s="5" t="n">
         <v>29102</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="G21" s="5" t="n">
+        <v>20012</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>55237</v>
+      </c>
+      <c r="AE21" t="inlineStr">
         <is>
           <t>Other movements, net</t>
         </is>
       </c>
-      <c r="Z21" t="n">
+      <c r="AF21" t="n">
+        <v>55237</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>20012</v>
+      </c>
+      <c r="AH21" t="n">
         <v>29102</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AI21" t="n">
         <v>45036</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AJ21" t="n">
         <v>84814</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AK21" t="n">
         <v>89284</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AL21" t="n">
         <v>27145</v>
       </c>
     </row>
@@ -2491,24 +2693,36 @@
       <c r="F22" s="5" t="n">
         <v>50830</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="G22" s="5" t="n">
+        <v>51182</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>49484</v>
+      </c>
+      <c r="AE22" t="inlineStr">
         <is>
           <t>Closing equity</t>
         </is>
       </c>
-      <c r="Z22" t="n">
+      <c r="AF22" t="n">
+        <v>49484</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>51182</v>
+      </c>
+      <c r="AH22" t="n">
         <v>50830</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AI22" t="n">
         <v>65993</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AJ22" t="n">
         <v>92483</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AK22" t="n">
         <v>173082</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AL22" t="n">
         <v>196143</v>
       </c>
     </row>
@@ -2550,27 +2764,47 @@
           <t>FY2021†</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
         <is>
           <t>FY2021†</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AS25" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="AT25" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr">
+      <c r="AU25" t="inlineStr">
         <is>
           <t>FY2024*</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="AV25" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2597,24 +2831,36 @@
       <c r="F26" s="5" t="n">
         <v>-92120</v>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="G26" s="5" t="n">
+        <v>69197</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>-27621</v>
+      </c>
+      <c r="AO26" t="inlineStr">
         <is>
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="AH26" t="n">
+      <c r="AP26" t="n">
+        <v>-27621</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>69197</v>
+      </c>
+      <c r="AR26" t="n">
         <v>-92120</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AS26" t="n">
         <v>16976</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AT26" t="n">
         <v>653419</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AU26" t="n">
         <v>189520</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AV26" t="n">
         <v>43038</v>
       </c>
     </row>
@@ -2639,24 +2885,36 @@
       <c r="F27" s="5" t="n">
         <v>26853</v>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="G27" s="5" t="n">
+        <v>-149</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>-514</v>
+      </c>
+      <c r="AO27" t="inlineStr">
         <is>
           <t>Net cash from/(used in) investing activities</t>
         </is>
       </c>
-      <c r="AH27" t="n">
+      <c r="AP27" t="n">
+        <v>-514</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>-149</v>
+      </c>
+      <c r="AR27" t="n">
         <v>26853</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AS27" t="n">
         <v>-177719</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AT27" t="n">
         <v>-124128</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AU27" t="n">
         <v>-389775</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AV27" t="n">
         <v>-741638</v>
       </c>
     </row>
@@ -2681,24 +2939,36 @@
       <c r="F28" s="5" t="n">
         <v>28960</v>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="G28" s="5" t="n">
+        <v>-8176</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>53243</v>
+      </c>
+      <c r="AO28" t="inlineStr">
         <is>
           <t>Net cash from/(used in) financing activities</t>
         </is>
       </c>
-      <c r="AH28" t="n">
+      <c r="AP28" t="n">
+        <v>53243</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>-8176</v>
+      </c>
+      <c r="AR28" t="n">
         <v>28960</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AS28" t="n">
         <v>183068</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AT28" t="n">
         <v>84573</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AU28" t="n">
         <v>98027</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AV28" t="n">
         <v>500016</v>
       </c>
     </row>
@@ -2723,24 +2993,36 @@
       <c r="F29" s="5" t="n">
         <v>52173</v>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="G29" s="5" t="n">
+        <v>88480</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>27607</v>
+      </c>
+      <c r="AO29" t="inlineStr">
         <is>
           <t>Closing cash and cash equivalents</t>
         </is>
       </c>
-      <c r="AH29" t="n">
+      <c r="AP29" t="n">
+        <v>27607</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>88480</v>
+      </c>
+      <c r="AR29" t="n">
         <v>52173</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AS29" t="n">
         <v>74498</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AT29" t="n">
         <v>688362</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AU29" t="n">
         <v>586134</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AV29" t="n">
         <v>387550</v>
       </c>
     </row>
@@ -2782,6 +3064,16 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -2810,6 +3102,8 @@
           <t>28%</t>
         </is>
       </c>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -2838,6 +3132,8 @@
           <t>28%</t>
         </is>
       </c>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -2866,6 +3162,8 @@
           <t>28%</t>
         </is>
       </c>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -2894,6 +3192,8 @@
           <t>23.4%</t>
         </is>
       </c>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -2922,6 +3222,8 @@
           <t>51,086%</t>
         </is>
       </c>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -2950,17 +3252,19 @@
           <t>146.5%</t>
         </is>
       </c>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note.</t>
+          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Ratios are blank for FY2019/FY2020 (no Pillar 3 disclosure published for those years). Note the ~£8.1m FY2020-closing/FY2021-opening equity gap explained on the Statement of Changes in Equity sheet (FRS 102-to-IFRS transition). FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2973,7 +3277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2982,6 +3286,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3029,6 +3335,16 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3057,11 +3373,13 @@
           <t>28%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note.</t>
         </is>
       </c>
     </row>
@@ -3073,14 +3391,15 @@
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3092,7 +3411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3101,6 +3420,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3148,6 +3469,16 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3168,11 +3499,13 @@
       <c r="F4" s="6" t="n">
         <v>50637</v>
       </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. Equal to CET1/Tier 1 capital in every year shown - Chetwood has no Tier 2 capital either.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note. Equal to CET1/Tier 1 capital in every year shown - Chetwood has no Tier 2 capital either.</t>
         </is>
       </c>
     </row>
@@ -3184,14 +3517,15 @@
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3203,7 +3537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3212,6 +3546,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3259,6 +3595,16 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3287,11 +3633,13 @@
           <t>28%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note.</t>
         </is>
       </c>
     </row>
@@ -3303,14 +3651,15 @@
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3322,7 +3671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3331,6 +3680,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3378,6 +3729,16 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3400,6 +3761,8 @@
       <c r="F4" s="6" t="n">
         <v>178987</v>
       </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -3416,14 +3779,15 @@
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3435,7 +3799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3444,6 +3808,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3456,7 +3822,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000, Group/consolidated basis (FY2021: standalone entity). See source note at bottom.</t>
+          <t>£'000, Group/consolidated basis (FY2021: standalone entity). FY2019-FY2020 blank - no Pillar 3 disclosure was ever published for those years. See source note at bottom.</t>
         </is>
       </c>
     </row>
@@ -3489,6 +3855,16 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021† (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡ (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡ (£'000)</t>
         </is>
       </c>
     </row>
@@ -3503,6 +3879,8 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3525,6 +3903,8 @@
       <c r="F5" s="6" t="n">
         <v>126942</v>
       </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3547,6 +3927,8 @@
       <c r="F6" s="6" t="n">
         <v>450</v>
       </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -3565,6 +3947,8 @@
       </c>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -3587,6 +3971,8 @@
       <c r="F8" s="6" t="n">
         <v>51595</v>
       </c>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -3609,6 +3995,8 @@
       <c r="F9" s="5" t="n">
         <v>178987</v>
       </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="11" ht="220" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
@@ -3617,8 +4005,14 @@
 FY2025/FY2024: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 6.3, which unlike the standalone FY2024 KM1 gap noted on the other Pillar 3 sheets, discloses its OV1 table's FY2024 comparative RWEA column in full - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2023/FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 8.3 (OV1 table with FY2022 comparative) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 5.4 (pre-KM1 category table) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf
-ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021 (marked †), which is Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement for FY2021. Companies House confirms FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2021 is included on a standalone basis and clearly flagged, rather than omitted.
+ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
 FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
+- Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
+- FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
+- FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
+- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
+- A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 FINDING: the other Pillar 3 sheets in this workbook leave FY2024 blank because no dedicated 'as at 31 March 2024' Pillar 3 document was ever published - true for the CET1/Tier 1/Total Capital/ratio figures. However the FY2025 Pillar 3 document's own OV1 table (used here) discloses a full FY2024 comparative RWEA-by-category column, so RWA Breakdown alone can be populated for FY2024 even though the other Pillar 3 sheets cannot.
 PRESENTATION NOTE: FY2021's pre-KM1 category table has no separate 'Securitisation' line (Chetwood had no securitised exposures that early) and combines credit valuation adjustment into Counterparty credit risk rather than breaking it out - both blank rather than assumed zero-and-separate.</t>
         </is>
@@ -3626,7 +4020,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A11:H11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3638,7 +4032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3647,6 +4041,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3694,6 +4090,16 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3714,6 +4120,8 @@
       <c r="F4" s="6" t="n">
         <v>216375</v>
       </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3742,11 +4150,13 @@
           <t>23.4%</t>
         </is>
       </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. Unlike Barclays/Monzo, Chetwood's disclosures do not distinguish an 'excluding/including claims on central banks' basis in any year - a single leverage ratio definition is used throughout (Tier 1 capital / total exposure measure). FY2021 used a pre-KM1 narrative table; FY2022 onward uses the formal KM1 rows 13-14.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note. Unlike Barclays/Monzo, Chetwood's disclosures do not distinguish an 'excluding/including claims on central banks' basis in any year - a single leverage ratio definition is used throughout (Tier 1 capital / total exposure measure). FY2021 used a pre-KM1 narrative table; FY2022 onward uses the formal KM1 rows 13-14.</t>
         </is>
       </c>
     </row>
@@ -3758,14 +4168,15 @@
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A6:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3777,7 +4188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3786,6 +4197,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3833,6 +4246,16 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3851,6 +4274,8 @@
         <v>67841</v>
       </c>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3869,6 +4294,8 @@
         <v>5627</v>
       </c>
       <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3887,6 +4314,8 @@
         <v>13656</v>
       </c>
       <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -3905,6 +4334,8 @@
         <v>1407</v>
       </c>
       <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -3933,11 +4364,13 @@
           <t>51,086%</t>
         </is>
       </c>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. FY2021 disclosed only the headline ratio in narrative form (no HQLA/outflow £ breakdown was published that year - the formal KM1 liquidity rows were introduced from FY2022). Chetwood's LCR ratios are extremely high because, as a young/small deposit-taker at the time, its regulatory outflow assumptions were small relative to its liquid asset holdings - this is as disclosed by Chetwood, not a transcription error.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note. FY2021 disclosed only the headline ratio in narrative form (no HQLA/outflow £ breakdown was published that year - the formal KM1 liquidity rows were introduced from FY2022). Chetwood's LCR ratios are extremely high because, as a young/small deposit-taker at the time, its regulatory outflow assumptions were small relative to its liquid asset holdings - this is as disclosed by Chetwood, not a transcription error.</t>
         </is>
       </c>
     </row>
@@ -3949,14 +4382,15 @@
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A11:H11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3968,7 +4402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3977,6 +4411,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4024,6 +4460,16 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4042,6 +4488,8 @@
         <v>380549</v>
       </c>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4060,6 +4508,8 @@
         <v>233566</v>
       </c>
       <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4088,11 +4538,13 @@
           <t>146.5%</t>
         </is>
       </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. FY2021's NSFR figure (146.5%) is quoted exactly as printed in the FY2021 Pillar 3 report, which oddly labels it 'as at the 31 March 2020' in a document otherwise dated 'as at 31 March 2021' - this looks like a typo in Chetwood's own document, but it is reproduced verbatim rather than silently corrected; no £ breakdown was published for FY2021 (the formal KM1 NSFR rows were introduced from FY2022).</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note. FY2021's NSFR figure (146.5%) is quoted exactly as printed in the FY2021 Pillar 3 report, which oddly labels it 'as at the 31 March 2020' in a document otherwise dated 'as at 31 March 2021' - this looks like a typo in Chetwood's own document, but it is reproduced verbatim rather than silently corrected; no £ breakdown was published for FY2021 (the formal KM1 NSFR rows were introduced from FY2022).</t>
         </is>
       </c>
     </row>
@@ -4104,14 +4556,15 @@
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4123,7 +4576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4132,6 +4585,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4175,6 +4630,16 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4207,11 +4672,13 @@
           <t>Not applicable</t>
         </is>
       </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Chetwood is classified as a 'small and non-complex institution' (SNCI) and is not subject to any MREL requirement above its minimum capital requirement - stated explicitly in the FY2021, FY2022 and FY2023 Pillar 3 reports ('...has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its [minimum capital requirement]'). The FY2025 report uses a shorter reduced-disclosure format that omits this narrative section, but there is no indication Chetwood's MREL/SNCI status has changed.</t>
+          <t>Note: Chetwood is classified as a 'small and non-complex institution' (SNCI) and is not subject to any MREL requirement above its minimum capital requirement - stated explicitly in the FY2021, FY2022 and FY2023 Pillar 3 reports ('...has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its [minimum capital requirement]'). The FY2025 report uses a shorter reduced-disclosure format that omits this narrative section, but there is no indication Chetwood's MREL/SNCI status has changed. FY2019/FY2020 are left blank rather than 'Not applicable' - no Pillar 3 disclosure was published for those years, so Chetwood's SNCI/MREL status at that time was never publicly stated.</t>
         </is>
       </c>
     </row>
@@ -4223,14 +4690,15 @@
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4242,7 +4710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -4251,6 +4719,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4263,7 +4733,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000. Consolidated (Group) basis except FY2021 († standalone entity - Group and Company are identical that year). See source note at bottom.</t>
+          <t>£'000. Consolidated (Group) basis except FY2019-FY2021 († standalone entity - Group and Company are identical those years; FY2019-FY2020 also FRS 102 basis, marked ‡). See source note at bottom.</t>
         </is>
       </c>
     </row>
@@ -4296,6 +4766,16 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021† (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡ (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡ (£'000)</t>
         </is>
       </c>
     </row>
@@ -4310,6 +4790,8 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4332,6 +4814,12 @@
       <c r="F5" s="6" t="n">
         <v>52173</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>88480</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>27607</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4354,6 +4842,10 @@
       <c r="F6" s="6" t="n">
         <v>19</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4374,6 +4866,12 @@
         <v>4883</v>
       </c>
       <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n">
+        <v>30170</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1994</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4396,6 +4894,12 @@
       <c r="F8" s="6" t="n">
         <v>156249</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>145022</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>46269</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4414,6 +4918,8 @@
       </c>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -4436,6 +4942,12 @@
       <c r="F10" s="6" t="n">
         <v>3486</v>
       </c>
+      <c r="G10" s="6" t="n">
+        <v>605</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>448</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4458,6 +4970,12 @@
       <c r="F11" s="6" t="n">
         <v>555</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>810</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>406</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4480,6 +4998,12 @@
       <c r="F12" s="6" t="n">
         <v>819</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>477</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>557</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -4501,6 +5025,12 @@
       </c>
       <c r="F13" s="6" t="n">
         <v>3178</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>485</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>486</v>
       </c>
     </row>
     <row r="14">
@@ -4516,6 +5046,8 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -4537,6 +5069,12 @@
       </c>
       <c r="F15" s="5" t="n">
         <v>216524</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>266053</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>77767</v>
       </c>
     </row>
     <row r="16">
@@ -4550,6 +5088,8 @@
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4572,6 +5112,12 @@
       <c r="F17" s="6" t="n">
         <v>160015</v>
       </c>
+      <c r="G17" s="6" t="n">
+        <v>210783</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>26107</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4590,6 +5136,8 @@
       </c>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4610,6 +5158,8 @@
         <v>591</v>
       </c>
       <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -4626,6 +5176,8 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -4642,6 +5194,8 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -4664,6 +5218,12 @@
       <c r="F22" s="6" t="n">
         <v>4127</v>
       </c>
+      <c r="G22" s="6" t="n">
+        <v>2768</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1649</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -4686,6 +5246,10 @@
       <c r="F23" s="6" t="n">
         <v>5</v>
       </c>
+      <c r="G23" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -4707,6 +5271,12 @@
       </c>
       <c r="F24" s="6" t="n">
         <v>1547</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1311</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>527</v>
       </c>
     </row>
     <row r="25">
@@ -4722,6 +5292,8 @@
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -4743,6 +5315,12 @@
       </c>
       <c r="F26" s="5" t="n">
         <v>165694</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>214871</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>28283</v>
       </c>
     </row>
     <row r="27">
@@ -4756,6 +5334,8 @@
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -4778,6 +5358,12 @@
       <c r="F28" s="6" t="n">
         <v>113688</v>
       </c>
+      <c r="G28" s="6" t="n">
+        <v>84688</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>64688</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -4800,6 +5386,12 @@
       <c r="F29" s="6" t="n">
         <v>2851</v>
       </c>
+      <c r="G29" s="6" t="n">
+        <v>2851</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>2851</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -4820,6 +5412,8 @@
         <v>6247</v>
       </c>
       <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -4842,6 +5436,8 @@
       <c r="F31" s="6" t="n">
         <v>114</v>
       </c>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4864,6 +5460,12 @@
       <c r="F32" s="6" t="n">
         <v>-65823</v>
       </c>
+      <c r="G32" s="6" t="n">
+        <v>-36357</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-18055</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -4884,6 +5486,8 @@
         <v>770</v>
       </c>
       <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -4906,6 +5510,12 @@
       <c r="F34" s="5" t="n">
         <v>50830</v>
       </c>
+      <c r="G34" s="5" t="n">
+        <v>51182</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>49484</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -4927,6 +5537,12 @@
       </c>
       <c r="F35" s="5" t="n">
         <v>216524</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>266053</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>77767</v>
       </c>
     </row>
     <row r="37" ht="220" customHeight="1">
@@ -4936,8 +5552,16 @@
 FY2025/FY2024: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2025, p.44-47 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
 FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.24-27 (prior-year comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (As with the Cash Flow Statement, the FY2023 Annual Report's own PDF has a text-encoding fault; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
 FY2022/FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.22-25 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, Group and Company for FY2021) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
-ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021 (marked †), which is Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement for FY2021. Companies House confirms FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2021 is included on a standalone basis and clearly flagged, rather than omitted.
+FY2020: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2020, p.19-21 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
+FY2019: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2019, p.14-16 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
+ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
 FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
+- Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
+- FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
+- FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
+- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
+- A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
 PRESENTATION NOTE: 'Cash and cash equivalents' (FY2023-25) and 'Loans and advances to banks' (FY2021-22) are the same balance-sheet line under two labels - shown on one row. 'Capital redemption reserve' (FY2023-25) and 'Capital contribution' (FY2022, first appearing that year as a debt waiver from the ultimate controlling party) are the same £6,247k reserve under two labels - shown on one row. P&amp;L structure changed across the five years as the business grew: FY2025 nets fee income/expense into a single 'Net fee and commission (expense)/income' line with no separate 'Other income' row; FY2022-23 include a 'Net gain arising from derecognition of financial assets at amortised cost' line with no FY2024-25 equivalent; only FY2024-25 disclose 'Deferred tax liabilities' or a 'Goodwill' balance sheet line, both absent 2021-23; only FY2025 discloses 'Debt securities in issue' as a live balance (£89k), though the line existed as a zero balance from FY2024. Blank cells indicate that year's report did not disclose that specific line.</t>
         </is>
@@ -4945,7 +5569,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4957,7 +5581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -4966,6 +5590,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4978,7 +5604,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000. Consolidated (Group) basis except FY2021 († standalone entity - Group and Company are identical that year). See source note at bottom.</t>
+          <t>£'000. Consolidated (Group) basis except FY2019-FY2021 († standalone entity - Group and Company are identical those years; FY2019-FY2020 also FRS 102 basis, marked ‡). See source note at bottom.</t>
         </is>
       </c>
     </row>
@@ -5011,6 +5637,16 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021† (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡ (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡ (£'000)</t>
         </is>
       </c>
     </row>
@@ -5025,6 +5661,8 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5047,6 +5685,12 @@
       <c r="F5" s="6" t="n">
         <v>17567</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>9687</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>2666</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -5069,6 +5713,12 @@
       <c r="F6" s="6" t="n">
         <v>-3135</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>-2014</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>-967</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -5091,6 +5741,12 @@
       <c r="F7" s="5" t="n">
         <v>14432</v>
       </c>
+      <c r="G7" s="5" t="n">
+        <v>7673</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1699</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -5111,6 +5767,8 @@
         <v>244</v>
       </c>
       <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -5131,6 +5789,8 @@
         <v>-152</v>
       </c>
       <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -5151,6 +5811,8 @@
         <v>92</v>
       </c>
       <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -5173,6 +5835,8 @@
       <c r="F11" s="6" t="n">
         <v>15</v>
       </c>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5189,6 +5853,8 @@
         <v>15</v>
       </c>
       <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -5211,6 +5877,12 @@
       <c r="F13" s="5" t="n">
         <v>14447</v>
       </c>
+      <c r="G13" s="5" t="n">
+        <v>7673</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1699</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -5233,6 +5905,12 @@
       <c r="F14" s="6" t="n">
         <v>-22372</v>
       </c>
+      <c r="G14" s="6" t="n">
+        <v>-14413</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-11240</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -5254,6 +5932,12 @@
       </c>
       <c r="F15" s="6" t="n">
         <v>-13375</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-11574</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-1995</v>
       </c>
     </row>
     <row r="16">
@@ -5271,6 +5955,8 @@
         <v>4369</v>
       </c>
       <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -5292,6 +5978,12 @@
       </c>
       <c r="F17" s="5" t="n">
         <v>-21300</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-18314</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-11536</v>
       </c>
     </row>
     <row r="18">
@@ -5311,6 +6003,8 @@
       <c r="F18" s="6" t="n">
         <v>-10</v>
       </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -5332,6 +6026,12 @@
       </c>
       <c r="F19" s="5" t="n">
         <v>-21310</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-18314</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>-11536</v>
       </c>
     </row>
     <row r="20">
@@ -5345,6 +6045,8 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -5367,6 +6069,8 @@
       <c r="F21" s="6" t="n">
         <v>5</v>
       </c>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5387,6 +6091,8 @@
       <c r="F22" s="6" t="n">
         <v>-34</v>
       </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5401,6 +6107,8 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -5423,6 +6131,8 @@
       <c r="F24" s="5" t="n">
         <v>-29</v>
       </c>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -5444,6 +6154,12 @@
       </c>
       <c r="F25" s="5" t="n">
         <v>-21339</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>-18314</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>-11536</v>
       </c>
     </row>
     <row r="27" ht="220" customHeight="1">
@@ -5453,8 +6169,16 @@
 FY2025/FY2024: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2025, p.44-47 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
 FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.24-27 (prior-year comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (As with the Cash Flow Statement, the FY2023 Annual Report's own PDF has a text-encoding fault; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
 FY2022/FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.22-25 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, Group and Company for FY2021) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
-ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021 (marked †), which is Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement for FY2021. Companies House confirms FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2021 is included on a standalone basis and clearly flagged, rather than omitted.
+FY2020: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2020, p.19-21 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
+FY2019: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2019, p.14-16 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
+ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
 FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
+- Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
+- FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
+- FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
+- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
+- A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
 PRESENTATION NOTE: 'Cash and cash equivalents' (FY2023-25) and 'Loans and advances to banks' (FY2021-22) are the same balance-sheet line under two labels - shown on one row. 'Capital redemption reserve' (FY2023-25) and 'Capital contribution' (FY2022, first appearing that year as a debt waiver from the ultimate controlling party) are the same £6,247k reserve under two labels - shown on one row. P&amp;L structure changed across the five years as the business grew: FY2025 nets fee income/expense into a single 'Net fee and commission (expense)/income' line with no separate 'Other income' row; FY2022-23 include a 'Net gain arising from derecognition of financial assets at amortised cost' line with no FY2024-25 equivalent; only FY2024-25 disclose 'Deferred tax liabilities' or a 'Goodwill' balance sheet line, both absent 2021-23; only FY2025 discloses 'Debt securities in issue' as a live balance (£89k), though the line existed as a zero balance from FY2024. Blank cells indicate that year's report did not disclose that specific line.</t>
         </is>
@@ -5462,7 +6186,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A27:H27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5474,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5498,7 +6222,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis (FY2021 standalone entity), £'000, chronological (oldest to newest). See source note at bottom.</t>
+          <t>Consolidated basis (FY2019-FY2021 standalone entity), £'000, chronological (oldest to newest). FY2019-FY2020 as filed under FRS 102; a ~£8.1m gap vs the FY2021 AR's own FY2020-comparative opening balance is shown and explained, not bridged - see source note at bottom.</t>
         </is>
       </c>
     </row>
@@ -5552,264 +6276,268 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>At 1 April 2020</t>
+          <t>At 1 April 2018</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>84688</v>
+        <v>9451</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>2851</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-44513</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>29</v>
-      </c>
+        <v>-6519</v>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>43067</v>
+        <v>5783</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Loss for the period (FY2021)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
+          <t>Issue of shares</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>55237</v>
+      </c>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n">
-        <v>-21310</v>
-      </c>
+      <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
       <c r="I5" s="6" t="n">
-        <v>-21310</v>
+        <v>55237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Net changes in fair value</t>
+          <t>Loss for the period (FY2019)</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="6" t="n">
+        <v>-11536</v>
+      </c>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n">
-        <v>5</v>
-      </c>
+      <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n">
-        <v>5</v>
+        <v>-11536</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Reclassified to income statement</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n">
-        <v>-34</v>
-      </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n">
-        <v>-34</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2019</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>64688</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>2851</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-18055</v>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n">
+        <v>49484</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Equity-settled share-based payment transactions</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
+          <t>Issue of shares</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>20000</v>
+      </c>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n">
-        <v>102</v>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="6" t="n">
-        <v>102</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Issue of shares</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>29000</v>
-      </c>
+          <t>Equity-settled share-based payment transactions</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
+      <c r="D9" s="6" t="n">
+        <v>12</v>
+      </c>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="6" t="n">
-        <v>29000</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2021</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>113688</v>
-      </c>
-      <c r="C10" s="5" t="n">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the period (FY2020)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n">
+        <v>-18314</v>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n">
+        <v>-18314</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2020 (as filed in the FY2020 accounts)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>84688</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>2851</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>-65823</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>114</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n">
-        <v>50830</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Loss for the period (FY2022)</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n">
-        <v>-29753</v>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n">
-        <v>-29753</v>
+      <c r="D11" s="5" t="n">
+        <v>-36357</v>
+      </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n">
+        <v>51182</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Retained losses acquired on purchase of subsidiary</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n">
-        <v>-17190</v>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n">
-        <v>-17190</v>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>At 1 April 2020 (per FY2021 AR's own comparative - see gap note)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>84688</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2851</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-44513</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n">
+        <v>43067</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Net changes in fair value</t>
+          <t>Loss for the period (FY2021)</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
+      <c r="D13" s="6" t="n">
+        <v>-21310</v>
+      </c>
       <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n">
-        <v>-120</v>
-      </c>
+      <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n">
-        <v>-120</v>
+        <v>-21310</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Equity-settled share-based payment transactions</t>
+          <t>Net changes in fair value</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n">
-        <v>209</v>
-      </c>
-      <c r="F14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="n">
-        <v>209</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Debt waiver by ultimate controlling party</t>
+          <t>Reclassified to income statement</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n">
-        <v>6247</v>
-      </c>
+      <c r="F15" s="6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n">
-        <v>6247</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Merger reserve arising on consolidation</t>
+          <t>Equity-settled share-based payment transactions</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>102</v>
+      </c>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n">
-        <v>770</v>
-      </c>
+      <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n">
-        <v>770</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
@@ -5819,7 +6547,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>55000</v>
+        <v>29000</v>
       </c>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
@@ -5828,82 +6556,78 @@
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n">
-        <v>55000</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>At 31 March 2022</t>
+          <t>At 31 March 2021</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>168688</v>
+        <v>113688</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>2851</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-112766</v>
+        <v>-65823</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>323</v>
+        <v>114</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-120</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>6247</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>770</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n">
-        <v>65993</v>
+        <v>50830</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Loss for the period (FY2023)</t>
+          <t>Loss for the period (FY2022)</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n">
-        <v>-58148</v>
+        <v>-29753</v>
       </c>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n">
-        <v>-58148</v>
+        <v>-29753</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Net changes in fair value</t>
+          <t>Retained losses acquired on purchase of subsidiary</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
+      <c r="D20" s="6" t="n">
+        <v>-17190</v>
+      </c>
       <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n">
-        <v>-58</v>
-      </c>
+      <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
       <c r="I20" s="6" t="n">
-        <v>-58</v>
+        <v>-17190</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Reclassified to income statement</t>
+          <t>Net changes in fair value</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
@@ -5911,12 +6635,12 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n">
-        <v>2</v>
+        <v>-120</v>
       </c>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="6" t="n">
-        <v>2</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="22">
@@ -5929,351 +6653,523 @@
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n">
-        <v>85</v>
+        <v>209</v>
       </c>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n">
-        <v>85</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Issue of shares</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>84609</v>
-      </c>
+          <t>Debt waiver by ultimate controlling party</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
+      <c r="G23" s="6" t="n">
+        <v>6247</v>
+      </c>
       <c r="H23" s="6" t="n"/>
       <c r="I23" s="6" t="n">
-        <v>84609</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2023</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>253297</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>2851</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>-170914</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>408</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>-176</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>6247</v>
-      </c>
-      <c r="H24" s="5" t="n">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Merger reserve arising on consolidation</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n">
         <v>770</v>
       </c>
-      <c r="I24" s="5" t="n">
-        <v>92483</v>
+      <c r="I24" s="6" t="n">
+        <v>770</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Loss for the period (FY2024)</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
+          <t>Issue of shares</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>55000</v>
+      </c>
       <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n">
-        <v>-8861</v>
-      </c>
+      <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
       <c r="I25" s="6" t="n">
-        <v>-8861</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Net changes in fair value</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n">
-        <v>145</v>
-      </c>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n">
-        <v>145</v>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2022</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>168688</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>2851</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-112766</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>323</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>6247</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>770</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>65993</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Reclassified to income statement</t>
+          <t>Loss for the period (FY2023)</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
+      <c r="D27" s="6" t="n">
+        <v>-58148</v>
+      </c>
       <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n">
-        <v>31</v>
-      </c>
+      <c r="F27" s="6" t="n"/>
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="n">
-        <v>31</v>
+        <v>-58148</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Equity-settled share-based payment transactions</t>
+          <t>Net changes in fair value</t>
         </is>
       </c>
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n">
-        <v>284</v>
-      </c>
-      <c r="F28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n">
+        <v>-58</v>
+      </c>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="6" t="n"/>
       <c r="I28" s="6" t="n">
-        <v>284</v>
+        <v>-58</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Issue of shares</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>433</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>88561</v>
-      </c>
+          <t>Reclassified to income statement</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
       <c r="D29" s="6" t="n"/>
       <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
+      <c r="F29" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="6" t="n">
-        <v>89000</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2024</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>253730</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>91418</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>-179775</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>692</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>6247</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>770</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>173082</v>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Equity-settled share-based payment transactions</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Loss for the period (FY2025)</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n"/>
+          <t>Issue of shares</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>84609</v>
+      </c>
       <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n">
-        <v>-4702</v>
-      </c>
+      <c r="D31" s="6" t="n"/>
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="n">
-        <v>-4702</v>
+        <v>84609</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Net changes in fair value</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n">
-        <v>824</v>
-      </c>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n">
-        <v>824</v>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2023</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>253297</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>2851</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>-170914</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>408</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>-176</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>6247</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>770</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>92483</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Tax on other comprehensive income</t>
+          <t>Loss for the period (FY2024)</t>
         </is>
       </c>
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
+      <c r="D33" s="6" t="n">
+        <v>-8861</v>
+      </c>
       <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n">
-        <v>-206</v>
-      </c>
+      <c r="F33" s="6" t="n"/>
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="6" t="n">
-        <v>-206</v>
+        <v>-8861</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Equity-settled share-based payment transactions</t>
+          <t>Net changes in fair value</t>
         </is>
       </c>
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="6" t="n"/>
       <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n">
-        <v>144</v>
-      </c>
-      <c r="F34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n">
+        <v>145</v>
+      </c>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="n"/>
       <c r="I34" s="6" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Reclassified to retained losses</t>
+          <t>Reclassified to income statement</t>
         </is>
       </c>
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n">
-        <v>577</v>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>-577</v>
-      </c>
-      <c r="F35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n">
+        <v>31</v>
+      </c>
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="6" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Issue of shares</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n">
-        <v>183</v>
-      </c>
-      <c r="C36" s="6" t="n">
-        <v>26818</v>
-      </c>
+          <t>Equity-settled share-based payment transactions</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
       <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
+      <c r="E36" s="6" t="n">
+        <v>284</v>
+      </c>
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="6" t="n"/>
       <c r="I36" s="6" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Issue of shares</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>433</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>88561</v>
+      </c>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n">
+        <v>89000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2024</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>253730</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>-179775</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>692</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>6247</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>770</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>173082</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the period (FY2025)</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n">
+        <v>-4702</v>
+      </c>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n">
+        <v>-4702</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Net changes in fair value</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n">
+        <v>824</v>
+      </c>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Tax on other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n">
+        <v>-206</v>
+      </c>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n">
+        <v>-206</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Equity-settled share-based payment transactions</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
+      <c r="I42" s="6" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Reclassified to retained losses</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n">
+        <v>577</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>-577</v>
+      </c>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Issue of shares</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>183</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>26818</v>
+      </c>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="n">
         <v>27001</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>At 31 March 2025</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B45" s="5" t="n">
         <v>253913</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C45" s="5" t="n">
         <v>118236</v>
       </c>
-      <c r="D37" s="5" t="n">
+      <c r="D45" s="5" t="n">
         <v>-183900</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E45" s="5" t="n">
         <v>259</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F45" s="5" t="n">
         <v>618</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="G45" s="5" t="n">
         <v>6247</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H45" s="5" t="n">
         <v>770</v>
       </c>
-      <c r="I37" s="5" t="n">
+      <c r="I45" s="5" t="n">
         <v>196143</v>
       </c>
     </row>
-    <row r="39" ht="220" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="47" ht="220" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>Sources - Chetwood Financial Limited's own Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, transcribed from each year's own Annual Report (not a later year's comparative column, except where noted). See entity note below re: FY2021 (standalone) and the FY2024 P&amp;L OCR-corruption note.
 FY2025/FY2024: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2025, p.44-47 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
 FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.24-27 (prior-year comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (As with the Cash Flow Statement, the FY2023 Annual Report's own PDF has a text-encoding fault; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
 FY2022/FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.22-25 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, Group and Company for FY2021) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
-ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021 (marked †), which is Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement for FY2021. Companies House confirms FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2021 is included on a standalone basis and clearly flagged, rather than omitted.
+FY2020: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2020, p.19-21 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
+FY2019: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2019, p.14-16 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
+ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
 FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
+- Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
+- FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
+- FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
+- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
+- A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
 PRESENTATION NOTE: 'Cash and cash equivalents' (FY2023-25) and 'Loans and advances to banks' (FY2021-22) are the same balance-sheet line under two labels - shown on one row. 'Capital redemption reserve' (FY2023-25) and 'Capital contribution' (FY2022, first appearing that year as a debt waiver from the ultimate controlling party) are the same £6,247k reserve under two labels - shown on one row. P&amp;L structure changed across the five years as the business grew: FY2025 nets fee income/expense into a single 'Net fee and commission (expense)/income' line with no separate 'Other income' row; FY2022-23 include a 'Net gain arising from derecognition of financial assets at amortised cost' line with no FY2024-25 equivalent; only FY2024-25 disclose 'Deferred tax liabilities' or a 'Goodwill' balance sheet line, both absent 2021-23; only FY2025 discloses 'Debt securities in issue' as a live balance (£89k), though the line existed as a zero balance from FY2024. Blank cells indicate that year's report did not disclose that specific line.</t>
         </is>
@@ -6281,7 +7177,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A47:I47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6293,7 +7189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -6302,6 +7198,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6314,7 +7212,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000 unless stated. Consolidated (Group) basis except FY2021 († standalone entity). See source note at bottom.</t>
+          <t>£'000 unless stated. Consolidated (Group) basis except FY2019-FY2021 († standalone entity). See source note at bottom.</t>
         </is>
       </c>
     </row>
@@ -6347,6 +7245,16 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021† (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡ (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡ (£'000)</t>
         </is>
       </c>
     </row>
@@ -6361,6 +7269,8 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6381,1029 +7291,1267 @@
       <c r="F5" s="6" t="n">
         <v>-21310</v>
       </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>(Loss)/profit before tax</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>-4702</v>
-      </c>
+          <t>Loss for the period (FY2019-FY2020, FRS 102 basis)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>-18314</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>-11536</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Depreciation of property, plant and equipment</t>
+          <t>(Loss)/profit before tax</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>615</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>560</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>496</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>322</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>347</v>
-      </c>
+        <v>-4702</v>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Remeasurement of right-of-use asset</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+          <t>Depreciation of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>615</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>560</v>
+      </c>
       <c r="D8" s="6" t="n">
-        <v>-217</v>
+        <v>496</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>304</v>
-      </c>
-      <c r="F8" s="6" t="n"/>
+        <v>322</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>347</v>
+      </c>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Amortisation of intangibles</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>536</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>1261</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>2235</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>694</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>106</v>
+          <t>Depreciation and amortisation (combined line, FY2019-FY2020 only)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>151</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Impairment of intangibles</t>
+          <t>Remeasurement of right-of-use asset</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n">
-        <v>985</v>
-      </c>
+      <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n">
-        <v>3069</v>
-      </c>
-      <c r="E10" s="6" t="n"/>
+        <v>-217</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>304</v>
+      </c>
       <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Interest income on debt securities</t>
+          <t>Amortisation of intangibles</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>-50560</v>
+        <v>536</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>-18163</v>
+        <v>1261</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-1885</v>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
+        <v>2235</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>694</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Interest expense/(income) on financing activities</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>6800</v>
-      </c>
+          <t>Impairment of intangibles</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n">
-        <v>180</v>
+        <v>985</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>40</v>
-      </c>
+        <v>3069</v>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Equity-settled share-based payment transactions</t>
+          <t>Interest income on debt securities</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>144</v>
+        <v>-50560</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>284</v>
+        <v>-18163</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>85</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>209</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>102</v>
-      </c>
+        <v>-1885</v>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Movement in fair value of financial instruments at FVTPL</t>
+          <t>Interest expense/(income) on financing activities</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>-22983</v>
+        <v>6800</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>9208</v>
+        <v>180</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1399</v>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Movement in fair value of derivative financial assets</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
+          <t>Equity-settled share-based payment transactions</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>284</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>85</v>
+      </c>
       <c r="E15" s="6" t="n">
-        <v>-119</v>
+        <v>209</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-15</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Movement in fair value of derivative financial liabilities</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n">
-        <v>452</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>-4</v>
-      </c>
+          <t>Movement in fair value of financial instruments at FVTPL</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>-22983</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>9208</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Fair value adjustment on hedged items</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>9005</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>-11782</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>-2217</v>
-      </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
+          <t>Movement in fair value of derivative financial assets</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n">
+        <v>-119</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Loss on disposal of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>Movement in fair value of derivative financial liabilities</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n">
-        <v>8</v>
-      </c>
+      <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n">
-        <v>1</v>
+        <v>452</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>12</v>
-      </c>
+        <v>-4</v>
+      </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Profit on sale of investments in debt securities</t>
+          <t>Fair value adjustment on hedged items</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>-1</v>
+        <v>9005</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-42</v>
-      </c>
-      <c r="D19" s="6" t="n"/>
+        <v>-11782</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-2217</v>
+      </c>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Discount unwind on debt securities</t>
+          <t>Loss on disposal of property, plant and equipment</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>536</v>
+        <v>1</v>
       </c>
       <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
+      <c r="D20" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Loss on disposal of intangible assets</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
+          <t>Profit on sale of investments in debt securities</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>-42</v>
+      </c>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>402</v>
-      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Movement in provision</t>
+          <t>Discount unwind on debt securities</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>-657</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>894</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>1424</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>591</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Impairment of investment in subsidiary / impairment of Yobota</t>
+          <t>Loss on disposal of intangible assets</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>402</v>
+      </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Net gain arising from derecognition of financial assets measured at amortised cost</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
+          <t>Movement in provision</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>-657</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>894</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>1424</v>
+      </c>
       <c r="E24" s="6" t="n">
-        <v>-4369</v>
+        <v>591</v>
       </c>
       <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n">
+        <v>11316</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1920</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Net increase in loans and advances to customers</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>-857836</v>
-      </c>
+          <t>Impairment of investment in subsidiary / impairment of Yobota</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n">
-        <v>-1184232</v>
+        <v>0</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-346633</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>-146297</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>-19344</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Net interest paid on derivative financial assets</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>25551</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>1448</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="E26" s="6" t="n"/>
+          <t>Net gain arising from derecognition of financial assets measured at amortised cost</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n">
+        <v>-4369</v>
+      </c>
       <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Net cash flow on derivative financial instruments</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
+          <t>Net increase in loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>-857836</v>
+      </c>
       <c r="C27" s="6" t="n">
-        <v>-52498</v>
+        <v>-1184232</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>325</v>
-      </c>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
+        <v>-346633</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>-146297</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-19344</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>-110070</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-44506</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Increase/(decrease) in prepayments and accrued income</t>
+          <t>Net interest paid on derivative financial assets</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>324</v>
+        <v>25551</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>-3353</v>
+        <v>1448</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>-69</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>-175</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>223</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Increase in other assets</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>-20076</v>
-      </c>
+          <t>Net cash flow on derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
       <c r="C29" s="6" t="n">
-        <v>-25013</v>
+        <v>-52498</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>-10277</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>-4696</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>-2881</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>(Increase)/decrease in tax asset</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
+          <t>Increase/(decrease) in prepayments and accrued income</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>324</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>-3353</v>
+      </c>
       <c r="D30" s="6" t="n">
-        <v>64</v>
+        <v>-69</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>-19</v>
+        <v>-175</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-45</v>
+        <v>223</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>-404</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>-159</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Increase/(decrease) in customer deposits</t>
+          <t>Increase in other assets</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>955692</v>
+        <v>-20076</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1473432</v>
+        <v>-25013</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1060680</v>
+        <v>-10277</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>162610</v>
+        <v>-4696</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-52195</v>
+        <v>-2881</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-157</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-421</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Increase/(decrease) in accruals and deferred income</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>507</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>2487</v>
-      </c>
+          <t>(Increase)/decrease in tax asset</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
       <c r="D32" s="6" t="n">
-        <v>489</v>
+        <v>64</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>1612</v>
+        <v>-19</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>2838</v>
-      </c>
+        <v>-45</v>
+      </c>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Increase/(decrease) in other liabilities</t>
+          <t>Increase/(decrease) in customer deposits</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>142</v>
+        <v>955692</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>2725</v>
+        <v>1473432</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>2518</v>
+        <v>1060680</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>1447</v>
+        <v>162610</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-396</v>
+        <v>-52195</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>184676</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>26107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Purchase of mortgage portfolio</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
+          <t>Increase/(decrease) in accruals and deferred income</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>507</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>2487</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>489</v>
+      </c>
       <c r="E34" s="6" t="n">
-        <v>157842</v>
-      </c>
-      <c r="F34" s="6" t="n"/>
+        <v>1612</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>2838</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>1119</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>829</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
+          <t>Increase/(decrease) in other liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>142</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>2725</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>2518</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>1447</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>-396</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>784</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Purchase of mortgage portfolio</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n">
+        <v>157842</v>
+      </c>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
           <t>Derecognition of assets at amortised cost on sale</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n">
-        <v>-123733</v>
-      </c>
-      <c r="F35" s="6" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Net cash from operating activities</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>43038</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>189520</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>653419</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>16976</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>-92120</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
+      <c r="E37" s="6" t="n">
+        <v>-123733</v>
+      </c>
       <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Proceeds from sale and maturity of debt securities</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
-        <v>1401</v>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>36835</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>11031</v>
-      </c>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from operating activities</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>43038</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>189520</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>653419</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>16976</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>-92120</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>69197</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>-27621</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Acquisition of debt securities</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n">
-        <v>-910238</v>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>-505077</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>-135674</v>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>-5003</v>
-      </c>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Cash flows from investing activities</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
       <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Principal repayments on investments in debt securities</t>
+          <t>Proceeds from sale and maturity of debt securities</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>134509</v>
+        <v>1401</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>61327</v>
-      </c>
-      <c r="D40" s="6" t="n"/>
+        <v>36835</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>11031</v>
+      </c>
       <c r="E40" s="6" t="n"/>
       <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Interest received from investing activities</t>
+          <t>Acquisition of debt securities</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>40802</v>
+        <v>-910238</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>17601</v>
+        <v>-505077</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>1760</v>
-      </c>
-      <c r="E41" s="6" t="n"/>
+        <v>-135674</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>-5003</v>
+      </c>
       <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Net maturity/(purchase) of debt securities</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
+          <t>Principal repayments on investments in debt securities</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>134509</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>61327</v>
+      </c>
       <c r="D42" s="6" t="n"/>
       <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n">
-        <v>30170</v>
-      </c>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Purchase of loans and advances to customers</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n">
-        <v>-157842</v>
-      </c>
+          <t>Interest received from investing activities</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>40802</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>17601</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>1760</v>
+      </c>
+      <c r="E43" s="6" t="n"/>
       <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Purchases of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n">
-        <v>-617</v>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>-461</v>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>-843</v>
-      </c>
-      <c r="E44" s="6" t="n">
-        <v>-119</v>
-      </c>
+          <t>Net maturity/(purchase) of debt securities</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
       <c r="F44" s="6" t="n">
-        <v>-116</v>
-      </c>
+        <v>30170</v>
+      </c>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Proceeds from sale of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="n">
-        <v>11</v>
-      </c>
+          <t>Purchase of loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n"/>
       <c r="C45" s="6" t="n"/>
       <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
+      <c r="E45" s="6" t="n">
+        <v>-157842</v>
+      </c>
       <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Investment in Intangible assets</t>
+          <t>Purchases of property, plant and equipment</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>-9</v>
-      </c>
-      <c r="C46" s="6" t="n"/>
+        <v>-617</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>-461</v>
+      </c>
       <c r="D46" s="6" t="n">
-        <v>-402</v>
+        <v>-843</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>-1852</v>
+        <v>-119</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>-3201</v>
+        <v>-116</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>-85</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>-462</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Acquisition of subsidiary net of cash acquired</t>
+          <t>Proceeds from sale of property, plant and equipment</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>-7497</v>
+        <v>11</v>
       </c>
       <c r="C47" s="6" t="n"/>
       <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n">
-        <v>-12903</v>
-      </c>
+      <c r="E47" s="6" t="n"/>
       <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="6" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Net cash from/(used in) investing activities</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>-741638</v>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>-389775</v>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>-124128</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>-177719</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>26853</v>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Investment in Intangible assets</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n">
+        <v>-402</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>-1852</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>-3201</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>-64</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>-52</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Cash flows from financing activities</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n"/>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Acquisition of subsidiary net of cash acquired</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>-7497</v>
+      </c>
       <c r="C49" s="6" t="n"/>
       <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
+      <c r="E49" s="6" t="n">
+        <v>-12903</v>
+      </c>
       <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Principal drawdowns on amounts owed to credit institutions</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n">
-        <v>476000</v>
-      </c>
-      <c r="C50" s="6" t="n">
-        <v>9000</v>
-      </c>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>-741638</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>-389775</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>-124128</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>-177719</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>26853</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-149</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>-514</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Interest paid on amounts owed to credit institutions</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="n">
-        <v>-2930</v>
-      </c>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n"/>
       <c r="C51" s="6" t="n"/>
       <c r="D51" s="6" t="n"/>
       <c r="E51" s="6" t="n"/>
       <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Issuance of ordinary shares</t>
+          <t>Principal drawdowns on amounts owed to credit institutions</t>
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>27001</v>
+        <v>476000</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>89000</v>
-      </c>
-      <c r="D52" s="6" t="n">
-        <v>84609</v>
-      </c>
-      <c r="E52" s="6" t="n">
-        <v>55000</v>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>29000</v>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Issuance of debt securities</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n">
-        <v>100</v>
-      </c>
+          <t>Interest paid on amounts owed to credit institutions</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>-2930</v>
+      </c>
+      <c r="C53" s="6" t="n"/>
       <c r="D53" s="6" t="n"/>
       <c r="E53" s="6" t="n"/>
       <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Repayment of debt securities</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="n">
-        <v>-10</v>
-      </c>
+          <t>Purchase of financial investments (FY2019-FY2020 only - classified under financing that year, see presentation note)</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n"/>
       <c r="C54" s="6" t="n"/>
       <c r="D54" s="6" t="n"/>
       <c r="E54" s="6" t="n"/>
       <c r="F54" s="6" t="n"/>
+      <c r="G54" s="6" t="n">
+        <v>-28176</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>-1994</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Interest (paid)/received on debt securities</t>
+          <t>Issuance of ordinary shares</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>-6</v>
-      </c>
-      <c r="C55" s="6" t="n"/>
-      <c r="D55" s="6" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="6" t="n"/>
+        <v>27001</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>89000</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>84609</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>29000</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>55237</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Interest expense on debt securities</t>
+          <t>Issuance of debt securities</t>
         </is>
       </c>
       <c r="B56" s="6" t="n"/>
       <c r="C56" s="6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D56" s="6" t="n"/>
       <c r="E56" s="6" t="n"/>
       <c r="F56" s="6" t="n"/>
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Proceeds from the sale of loans and advances at amortised cost</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="n"/>
+          <t>Repayment of debt securities</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>-10</v>
+      </c>
       <c r="C57" s="6" t="n"/>
       <c r="D57" s="6" t="n"/>
-      <c r="E57" s="6" t="n">
-        <v>128103</v>
-      </c>
+      <c r="E57" s="6" t="n"/>
       <c r="F57" s="6" t="n"/>
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Interest paid on lease liabilities</t>
+          <t>Interest (paid)/received on debt securities</t>
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>-39</v>
-      </c>
-      <c r="C58" s="6" t="n">
-        <v>-73</v>
-      </c>
-      <c r="D58" s="6" t="n">
-        <v>-36</v>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>-35</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>-40</v>
-      </c>
+        <v>-6</v>
+      </c>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n"/>
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="6" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Net cash from/(used in) financing activities</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="n">
-        <v>500016</v>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>98027</v>
-      </c>
-      <c r="D59" s="5" t="n">
-        <v>84573</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>183068</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>28960</v>
-      </c>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Interest expense on debt securities</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="6" t="n"/>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>Net cash flows for the period</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>-198584</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>-102228</v>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>613864</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>22325</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>-36307</v>
-      </c>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Proceeds from the sale of loans and advances at amortised cost</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n">
+        <v>128103</v>
+      </c>
+      <c r="F60" s="6" t="n"/>
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Opening cash and cash equivalents</t>
+          <t>Interest paid on lease liabilities</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>586134</v>
+        <v>-39</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>688362</v>
+        <v>-73</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>74498</v>
+        <v>-36</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>52173</v>
+        <v>-35</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>88480</v>
-      </c>
+        <v>-40</v>
+      </c>
+      <c r="G61" s="6" t="n"/>
+      <c r="H61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
+          <t>Net cash from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>500016</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>98027</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>84573</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>28960</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>-8176</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>53243</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flows for the period</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>-198584</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>-102228</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>613864</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>22325</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>-36307</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>60872</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>25108</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Opening cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>586134</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>688362</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>74498</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>52173</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>88480</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>27608</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
           <t>Closing cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n">
+      <c r="B65" s="5" t="n">
         <v>387550</v>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C65" s="5" t="n">
         <v>586134</v>
       </c>
-      <c r="D62" s="5" t="n">
+      <c r="D65" s="5" t="n">
         <v>688362</v>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="E65" s="5" t="n">
         <v>74498</v>
       </c>
-      <c r="F62" s="5" t="n">
+      <c r="F65" s="5" t="n">
         <v>52173</v>
       </c>
-    </row>
-    <row r="64" ht="150" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="G65" s="5" t="n">
+        <v>88480</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>27607</v>
+      </c>
+    </row>
+    <row r="67" ht="150" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Chetwood Financial Limited Group (consolidated) cash flow statement, £'000, unless noted. See entity note above re: FY2021 (standalone) and FY2024 (Pillar 3 gap).
 FY2025: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2025, p.48-49 (Consolidated and company statement of cashflows) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
@@ -7411,16 +8559,25 @@
 FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.29 (prior-year comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (The FY2023 Annual Report's own PDF has a text-encoding fault that corrupts extracted figures; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
 FY2022: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.26 (Consolidated and Company Statement of Cashflows) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
 FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2021, p.28 (Statement of Cashflows, standalone entity) - http://web.archive.org/web/20210830132929/https://chetwood.co/static/3d0ade6e892213e246ca03dc1d84b417/AnnualReport.pdf
-ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021 (marked †), which is Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement for FY2021. Companies House confirms FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2021 is included on a standalone basis and clearly flagged, rather than omitted.
+FY2020: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2020, p.22 (Statement of Cashflows, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
+FY2019: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2019, p.17 (Statement of Cashflows, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
+ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
 FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
+- Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
+- FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
+- FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
+- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
+- A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 PRESENTATION NOTE: Line items changed across the five years as the business grew (e.g. debt securities and derivative-related lines were introduced/split differently year to year, and FY2025 switched the starting line from 'Loss after tax' to '(Loss)/profit before tax'). Blank cells indicate that year's report did not disclose that specific split. Section totals (net cash from operating/investing/financing, cash and cash equivalents) are consistent and reconcile exactly across all 5 years.
-DATA QUALITY NOTE (added 2026-08-27, found during a project-wide sanity check): the AR24/AR25 source statements print BOTH a Group and a Company column side by side for each year; three line items were originally transcribed from the wrong column or with a digit error, causing FY2023/FY2024's operating and investing TOTALs to not reconcile to their own line items. Corrected against both AR24 (own-year figures) and AR25's FY2024 comparative column (cross-checked, both agree): 'Fair value adjustment on hedged items' FY2024 corrected from -11,182 to the Group figure -11,782 (a transcription slip); 'Interest received from investing activities' FY2024 corrected from 11,601 to the Group figure 17,601 (transcription slip); 'Loss on disposal of property, plant and equipment' FY2023 corrected from 4 to the Group figure 8 (was the Company figure); 'Impairment of investment in subsidiary/Yobota' FY2023 corrected from 6,753 to 0/nil (the Group figure is nil - 6,753 was the Company-only figure); 'Subscription of shares in subsidiary undertaking' FY2023 (-1,500) removed entirely - it is a Company-only line with no Group-basis equivalent, so it never belonged in this Group-basis statement. All four sections now reconcile exactly to the penny against the primary source.</t>
+DATA QUALITY NOTE (added 2026-08-27, found during a project-wide sanity check): the AR24/AR25 source statements print BOTH a Group and a Company column side by side for each year; three line items were originally transcribed from the wrong column or with a digit error, causing FY2023/FY2024's operating and investing TOTALs to not reconcile to their own line items. Corrected against both AR24 (own-year figures) and AR25's FY2024 comparative column (cross-checked, both agree): 'Fair value adjustment on hedged items' FY2024 corrected from -11,182 to the Group figure -11,782 (a transcription slip); 'Interest received from investing activities' FY2024 corrected from 11,601 to the Group figure 17,601 (transcription slip); 'Loss on disposal of property, plant and equipment' FY2023 corrected from 4 to the Group figure 8 (was the Company figure); 'Impairment of investment in subsidiary/Yobota' FY2023 corrected from 6,753 to 0/nil (the Group figure is nil - 6,753 was the Company-only figure); 'Subscription of shares in subsidiary undertaking' FY2023 (-1,500) removed entirely - it is a Company-only line with no Group-basis equivalent, so it never belonged in this Group-basis statement. All four sections now reconcile exactly to the penny against the primary source.
+FY2019/FY2020 PRESENTATION NOTE: these two years' statements (FRS 102 basis) do not split depreciation from amortisation, so a single combined line is shown for those years only rather than force-splitting it across the FY2021+ 'Depreciation of property, plant and equipment' / 'Amortisation of intangibles' rows. 'Purchase of financial investments' (debt securities) is classified by Chetwood's own FY2019/FY2020 statements under Financing activities, not Investing activities as in every later year - kept in its own as-disclosed section rather than moved. FY2020's own statement shows FY2019 comparative figures (£27,620k operating cashflow, £25,109k net cashflow for the period, £27,608k closing cash) that differ by £1k from FY2019's own filed figures (£27,621k / £25,108k / £27,607k) used here - an immaterial rounding difference between the two filings, not corrected.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A67:H67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7432,7 +8589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -7441,6 +8598,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7453,7 +8612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000. Consolidated (Group) basis except FY2021 († standalone entity). See source note at bottom.</t>
+          <t>£'000. Consolidated (Group) basis except FY2019-FY2021 († standalone entity). No IFRS 9 stage table for FY2019-FY2020 (FRS 102 basis - see source note). See source note at bottom.</t>
         </is>
       </c>
     </row>
@@ -7486,6 +8645,16 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021† (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡ (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡ (£'000)</t>
         </is>
       </c>
     </row>
@@ -7500,6 +8669,8 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7522,6 +8693,8 @@
       <c r="F5" s="6" t="n">
         <v>145496</v>
       </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -7544,6 +8717,8 @@
       <c r="F6" s="6" t="n">
         <v>22064</v>
       </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7566,6 +8741,8 @@
       <c r="F7" s="6" t="n">
         <v>14585</v>
       </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -7586,6 +8763,8 @@
         <v>550</v>
       </c>
       <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -7608,6 +8787,8 @@
       <c r="F9" s="5" t="n">
         <v>182145</v>
       </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -7630,6 +8811,8 @@
       <c r="F10" s="6" t="n">
         <v>-6292</v>
       </c>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7652,6 +8835,8 @@
       <c r="F11" s="6" t="n">
         <v>-7149</v>
       </c>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7674,6 +8859,8 @@
       <c r="F12" s="6" t="n">
         <v>-12455</v>
       </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -7694,6 +8881,8 @@
         <v>-13</v>
       </c>
       <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -7716,6 +8905,8 @@
       <c r="F14" s="5" t="n">
         <v>-25896</v>
       </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -7737,6 +8928,12 @@
       </c>
       <c r="F15" s="5" t="n">
         <v>156249</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>145022</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="16">
@@ -7750,6 +8947,8 @@
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -7782,6 +8981,8 @@
           <t>8.01%</t>
         </is>
       </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -7814,6 +9015,8 @@
           <t>14.22%</t>
         </is>
       </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -7846,6 +9049,8 @@
           <t>85.40%</t>
         </is>
       </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
     </row>
     <row r="21" ht="220" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
@@ -7854,15 +9059,24 @@
 FY2025/FY2024: Annual Report 2025, p.96-100 (Note 36.2/36.3 Credit quality) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
 FY2023: Annual Report 2024, p.51-52 (Note 37, FY2023 comparative tables) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf
 FY2022/FY2021: Annual Report 2022, p.49-52 (Note 31.2 Credit quality) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
-ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021 (marked †), which is Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement for FY2021. Companies House confirms FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2021 is included on a standalone basis and clearly flagged, rather than omitted.
+FY2020: Annual Report and Financial Statements, year ended 31 March 2020, p.20/28 (Statement of Financial Position net loan balance; no IFRS 9 stage table - see FRS 102 note below) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2019: Annual Report and Financial Statements, year ended 31 March 2019, p.15 (Statement of Financial Position net loan balance; no IFRS 9 stage table - see FRS 102 note below) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0
+ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
 FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
-PRESENTATION NOTE: these Note 36/37 tables report gross/net loans and advances measured at amortised cost only. The Balance Sheet's own 'Loans and advances to customers' line is larger in every year from FY2022 onward (e.g. FY2025: £2,691,247k on the Balance Sheet vs £2,665,626k gross / £2,655,384k net summed here) because some loans are measured at fair value through profit or loss and fall outside this amortised-cost IFRS 9 note - this gap is a genuine measurement-basis difference disclosed by the Bank, not a transcription error, and is not force-reconciled here. FY2021 is the exception: with no secured book yet and no FVTPL loans, the combined stage total ties to the Balance Sheet exactly (£156,249k both ways).</t>
+HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
+- Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
+- FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
+- FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
+- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
+- A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
+PRESENTATION NOTE: these Note 36/37 tables report gross/net loans and advances measured at amortised cost only. The Balance Sheet's own 'Loans and advances to customers' line is larger in every year from FY2022 onward (e.g. FY2025: £2,691,247k on the Balance Sheet vs £2,665,626k gross / £2,655,384k net summed here) because some loans are measured at fair value through profit or loss and fall outside this amortised-cost IFRS 9 note - this gap is a genuine measurement-basis difference disclosed by the Bank, not a transcription error, and is not force-reconciled here. FY2021 is the exception: with no secured book yet and no FVTPL loans, the combined stage total ties to the Balance Sheet exactly (£156,249k both ways).
+FY2019/FY2020 NOTE: these two years' statutory accounts were prepared under UK GAAP FRS 102 (not IFRS), before Chetwood adopted IFRS 9 - there is no loan-staging (Stage 1/2/3) table in either year's accounts, only a single aggregate net loan balance and a simple impairment-allowance movement in the notes. The Stage/ECL breakdown rows above are genuinely 'Not publicly disclosed' for FY2019 and FY2020; only the single 'Net loans and advances to customers' total row is populated for those two years, tying exactly to the Balance Sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A21:H21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7874,7 +9088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7883,6 +9097,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7930,6 +9146,16 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -7950,11 +9176,13 @@
       <c r="F4" s="6" t="n">
         <v>50637</v>
       </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note.</t>
         </is>
       </c>
     </row>
@@ -7966,14 +9194,15 @@
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7985,7 +9214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7994,6 +9223,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8041,6 +9272,16 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -8069,11 +9310,13 @@
           <t>28%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. FY2021 is as stated in the source (rounded to the nearest whole percent; no decimal figure was disclosed that year).</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note. FY2021 is as stated in the source (rounded to the nearest whole percent; no decimal figure was disclosed that year).</t>
         </is>
       </c>
     </row>
@@ -8085,14 +9328,15 @@
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8104,7 +9348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -8113,6 +9357,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8160,6 +9406,16 @@
           <t>FY2021†</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -8180,11 +9436,13 @@
       <c r="F4" s="6" t="n">
         <v>50637</v>
       </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. See source note. Equal to CET1 capital in every year shown - Chetwood has no Additional Tier 1 (AT1) instruments.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note. Equal to CET1 capital in every year shown - Chetwood has no Additional Tier 1 (AT1) instruments.</t>
         </is>
       </c>
     </row>
@@ -8196,14 +9454,15 @@
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)</t>
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/CHETWOOD FINANCIALS.xlsx
+++ b/banks/CHETWOOD FINANCIALS.xlsx
@@ -4710,7 +4710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -4850,240 +4850,242 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Investment in debt securities</t>
+          <t>UK government treasury bills, measured at FVOCI</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1321666</v>
+        <v>202151</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>537291</v>
+        <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>129595</v>
+        <v>4825</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>4883</v>
       </c>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n">
-        <v>30170</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>1994</v>
-      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Loans and advances to customers</t>
+          <t>Other debt securities (ABS loan notes / fixed rate bonds / covered bonds / senior loan notes), at amortised cost</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2691247</v>
+        <v>1119515</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1833411</v>
+        <v>537291</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>649179</v>
+        <v>124770</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>302546</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>156249</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>145022</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>46269</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Fair value adjustments on hedged assets</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>5615</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>12926</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>-1069</v>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Investment in debt securities - total</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1321666</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>537291</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>129595</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4883</v>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n">
+        <v>30170</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1994</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Other assets</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>63998</v>
+        <v>2691247</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>43910</v>
+        <v>1833411</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>18897</v>
+        <v>649179</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>8620</v>
+        <v>302546</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>3486</v>
+        <v>156249</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>605</v>
+        <v>145022</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>448</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Prepayments and accrued income</t>
+          <t>Fair value adjustments on hedged assets</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>4177</v>
+        <v>5615</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4353</v>
+        <v>12926</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>930</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>555</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>810</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>406</v>
-      </c>
+        <v>-1069</v>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
+          <t>Other assets</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>913</v>
+        <v>63998</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>883</v>
+        <v>43910</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1246</v>
+        <v>18897</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>690</v>
+        <v>8620</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>819</v>
+        <v>3486</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>477</v>
+        <v>605</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>557</v>
+        <v>448</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
+          <t>Prepayments and accrued income</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>2044</v>
+        <v>4177</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>521</v>
+        <v>4353</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2767</v>
+        <v>999</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>7669</v>
+        <v>930</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>3178</v>
+        <v>555</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>485</v>
+        <v>810</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>486</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>913</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>883</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1246</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>690</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>819</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>477</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>2044</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>521</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>2767</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>7669</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>3178</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>485</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B16" s="6" t="n">
         <v>5927</v>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>4532547</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>3077904</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1494541</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>400038</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>216524</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>266053</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>77767</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
@@ -5092,48 +5094,42 @@
       <c r="H16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Customer deposits</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>3812429</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>2856737</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>1383305</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>322625</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>160015</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>210783</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>26107</v>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>4532547</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3077904</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1494541</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>400038</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>216524</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>266053</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>77767</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Fair value adjustments on hedged liabilities</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>621</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>-1073</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>-3286</v>
-      </c>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
@@ -5142,38 +5138,46 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Provisions</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>2252</v>
+        <v>3812429</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>2909</v>
+        <v>2856737</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2015</v>
+        <v>1383305</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>591</v>
-      </c>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+        <v>322625</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>160015</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>210783</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>26107</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Amounts owed to credit institutions</t>
+          <t>Fair value adjustments on hedged liabilities</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>488932</v>
+        <v>621</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>9107</v>
-      </c>
-      <c r="D20" s="6" t="n"/>
+        <v>-1073</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-3286</v>
+      </c>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
@@ -5182,17 +5186,21 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Debt securities in issue</t>
+          <t>Provisions</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>89</v>
+        <v>2252</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
+        <v>2909</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>591</v>
+      </c>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
@@ -5200,136 +5208,130 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Accruals</t>
+          <t>Amounts owed to credit institutions</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>10864</v>
+        <v>488932</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>9766</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>7279</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>6790</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>4127</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>2768</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1649</v>
-      </c>
+        <v>9107</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial liabilities</t>
+          <t>Debt securities in issue</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>12216</v>
+        <v>89</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>18713</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>6645</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>457</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>9</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Other liabilities</t>
+          <t>Accruals</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>8795</v>
+        <v>10864</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>8564</v>
+        <v>9766</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>6100</v>
+        <v>7279</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>3582</v>
+        <v>6790</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1547</v>
+        <v>4127</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>1311</v>
+        <v>2768</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>527</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>Derivative financial liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>12216</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>18713</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>6645</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>457</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>8795</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>8564</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>6100</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>3582</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>1547</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>1311</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>Deferred tax liabilities</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B27" s="6" t="n">
         <v>206</v>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>4336404</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>2904822</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>1402058</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>334045</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>165694</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>214871</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>28283</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
@@ -5338,215 +5340,257 @@
       <c r="H27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Called up share capital</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>253913</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>253730</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>253297</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>168688</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>113688</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>84688</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>64688</v>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4336404</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>2904822</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1402058</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>334045</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>165694</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>214871</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>28283</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Share premium account</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>118236</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>91418</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>2851</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>2851</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>2851</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>2851</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>2851</v>
-      </c>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Capital redemption reserve / Capital contribution</t>
+          <t>Called up share capital</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>6247</v>
+        <v>253913</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>6247</v>
+        <v>253730</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>6247</v>
+        <v>253297</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>6247</v>
-      </c>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
+        <v>168688</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>113688</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>84688</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>64688</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Other reserves</t>
+          <t>Share premium account</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>877</v>
+        <v>118236</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>692</v>
+        <v>91418</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>232</v>
+        <v>2851</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>203</v>
+        <v>2851</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>114</v>
-      </c>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
+        <v>2851</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>2851</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>2851</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Retained losses</t>
+          <t>Capital redemption reserve / Capital contribution</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>-183900</v>
+        <v>6247</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-179775</v>
+        <v>6247</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-170914</v>
+        <v>6247</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-112766</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>-65823</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>-36357</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>-18055</v>
-      </c>
+        <v>6247</v>
+      </c>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Merger reserve</t>
+          <t>Other reserves</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>770</v>
+        <v>877</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>770</v>
+        <v>692</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>770</v>
+        <v>232</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>770</v>
-      </c>
-      <c r="F33" s="6" t="n"/>
+        <v>203</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>114</v>
+      </c>
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Retained losses</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>-183900</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>-179775</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>-170914</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>-112766</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>-65823</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>-36357</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>-18055</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Merger reserve</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>770</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>770</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>770</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>770</v>
+      </c>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B36" s="5" t="n">
         <v>196143</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C36" s="5" t="n">
         <v>173082</v>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D36" s="5" t="n">
         <v>92483</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E36" s="5" t="n">
         <v>65993</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F36" s="5" t="n">
         <v>50830</v>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="G36" s="5" t="n">
         <v>51182</v>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H36" s="5" t="n">
         <v>49484</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Total liabilities and equity</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B37" s="5" t="n">
         <v>4532547</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C37" s="5" t="n">
         <v>3077904</v>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D37" s="5" t="n">
         <v>1494541</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E37" s="5" t="n">
         <v>400038</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F37" s="5" t="n">
         <v>216524</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="G37" s="5" t="n">
         <v>266053</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H37" s="5" t="n">
         <v>77767</v>
       </c>
     </row>
-    <row r="37" ht="220" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="39" ht="220" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Sources - Chetwood Financial Limited's own Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, transcribed from each year's own Annual Report (not a later year's comparative column, except where noted). See entity note below re: FY2021 (standalone) and the FY2024 P&amp;L OCR-corruption note.
 FY2025/FY2024: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2025, p.44-47 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
@@ -5563,13 +5607,18 @@
 - FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
 - A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
+INVESTMENT IN DEBT SECURITIES BREAKDOWN NOTE (added 2026-09-07): 'Investment in debt securities' is split into 'UK government treasury bills, measured at FVOCI' and 'Other debt securities (ABS loan notes / fixed rate bonds / covered bonds / senior loan notes), at amortised cost', sourced from each year's own Note 14/15/16 ('Investment in debt securities'), which reconciles exactly to the original total in every year it is disclosed:
+FY2025/FY2024: Annual Report 2025, p.71 (Note 14) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf. FY2025: FVOCI Treasury Bills £202,151k; amortised cost £1,119,515k (ABS £525,248k + Fixed rate bonds £384,031k + Covered bonds £39,059k + Senior loan notes £171,177k). FY2024: no Treasury Bills held (FVOCI leg £nil); amortised cost £537,291k (ABS £435,075k + Fixed rate bonds £102,216k).
+FY2023: Annual Report 2024, p.40 (Note 15, FY2023 comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. FVOCI Treasury Bills £4,825k; amortised cost £124,770k (ABS loan notes only).
+FY2022: Annual Report 2022, p.39 (Note 16) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf. The entire £4,883k balance is Treasury Bills measured at FVOCI ('all instruments are investments in UK sovereign treasury bills') - no amortised-cost leg that year.
+FY2020/FY2019: no note breaks down this line at all in either year's own Annual Report - the Statement of Financial Position shows 'Investment in debt securities' with no note-reference number next to it (unlike every other line, which cross-references a numbered note), confirmed by reading both years' full note set (pages 23-39 of the FY2020 AR, pages 18-32 of the FY2019 AR) - genuinely no further detail available for these two years.
 PRESENTATION NOTE: 'Cash and cash equivalents' (FY2023-25) and 'Loans and advances to banks' (FY2021-22) are the same balance-sheet line under two labels - shown on one row. 'Capital redemption reserve' (FY2023-25) and 'Capital contribution' (FY2022, first appearing that year as a debt waiver from the ultimate controlling party) are the same £6,247k reserve under two labels - shown on one row. P&amp;L structure changed across the five years as the business grew: FY2025 nets fee income/expense into a single 'Net fee and commission (expense)/income' line with no separate 'Other income' row; FY2022-23 include a 'Net gain arising from derecognition of financial assets at amortised cost' line with no FY2024-25 equivalent; only FY2024-25 disclose 'Deferred tax liabilities' or a 'Goodwill' balance sheet line, both absent 2021-23; only FY2025 discloses 'Debt securities in issue' as a live balance (£89k), though the line existed as a zero balance from FY2024. Blank cells indicate that year's report did not disclose that specific line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A39:H39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6180,6 +6229,11 @@
 - FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
 - A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
+INVESTMENT IN DEBT SECURITIES BREAKDOWN NOTE (added 2026-09-07): 'Investment in debt securities' is split into 'UK government treasury bills, measured at FVOCI' and 'Other debt securities (ABS loan notes / fixed rate bonds / covered bonds / senior loan notes), at amortised cost', sourced from each year's own Note 14/15/16 ('Investment in debt securities'), which reconciles exactly to the original total in every year it is disclosed:
+FY2025/FY2024: Annual Report 2025, p.71 (Note 14) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf. FY2025: FVOCI Treasury Bills £202,151k; amortised cost £1,119,515k (ABS £525,248k + Fixed rate bonds £384,031k + Covered bonds £39,059k + Senior loan notes £171,177k). FY2024: no Treasury Bills held (FVOCI leg £nil); amortised cost £537,291k (ABS £435,075k + Fixed rate bonds £102,216k).
+FY2023: Annual Report 2024, p.40 (Note 15, FY2023 comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. FVOCI Treasury Bills £4,825k; amortised cost £124,770k (ABS loan notes only).
+FY2022: Annual Report 2022, p.39 (Note 16) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf. The entire £4,883k balance is Treasury Bills measured at FVOCI ('all instruments are investments in UK sovereign treasury bills') - no amortised-cost leg that year.
+FY2020/FY2019: no note breaks down this line at all in either year's own Annual Report - the Statement of Financial Position shows 'Investment in debt securities' with no note-reference number next to it (unlike every other line, which cross-references a numbered note), confirmed by reading both years' full note set (pages 23-39 of the FY2020 AR, pages 18-32 of the FY2019 AR) - genuinely no further detail available for these two years.
 PRESENTATION NOTE: 'Cash and cash equivalents' (FY2023-25) and 'Loans and advances to banks' (FY2021-22) are the same balance-sheet line under two labels - shown on one row. 'Capital redemption reserve' (FY2023-25) and 'Capital contribution' (FY2022, first appearing that year as a debt waiver from the ultimate controlling party) are the same £6,247k reserve under two labels - shown on one row. P&amp;L structure changed across the five years as the business grew: FY2025 nets fee income/expense into a single 'Net fee and commission (expense)/income' line with no separate 'Other income' row; FY2022-23 include a 'Net gain arising from derecognition of financial assets at amortised cost' line with no FY2024-25 equivalent; only FY2024-25 disclose 'Deferred tax liabilities' or a 'Goodwill' balance sheet line, both absent 2021-23; only FY2025 discloses 'Debt securities in issue' as a live balance (£89k), though the line existed as a zero balance from FY2024. Blank cells indicate that year's report did not disclose that specific line.</t>
         </is>
       </c>
@@ -7171,6 +7225,11 @@
 - FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
 - A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
+INVESTMENT IN DEBT SECURITIES BREAKDOWN NOTE (added 2026-09-07): 'Investment in debt securities' is split into 'UK government treasury bills, measured at FVOCI' and 'Other debt securities (ABS loan notes / fixed rate bonds / covered bonds / senior loan notes), at amortised cost', sourced from each year's own Note 14/15/16 ('Investment in debt securities'), which reconciles exactly to the original total in every year it is disclosed:
+FY2025/FY2024: Annual Report 2025, p.71 (Note 14) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf. FY2025: FVOCI Treasury Bills £202,151k; amortised cost £1,119,515k (ABS £525,248k + Fixed rate bonds £384,031k + Covered bonds £39,059k + Senior loan notes £171,177k). FY2024: no Treasury Bills held (FVOCI leg £nil); amortised cost £537,291k (ABS £435,075k + Fixed rate bonds £102,216k).
+FY2023: Annual Report 2024, p.40 (Note 15, FY2023 comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. FVOCI Treasury Bills £4,825k; amortised cost £124,770k (ABS loan notes only).
+FY2022: Annual Report 2022, p.39 (Note 16) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf. The entire £4,883k balance is Treasury Bills measured at FVOCI ('all instruments are investments in UK sovereign treasury bills') - no amortised-cost leg that year.
+FY2020/FY2019: no note breaks down this line at all in either year's own Annual Report - the Statement of Financial Position shows 'Investment in debt securities' with no note-reference number next to it (unlike every other line, which cross-references a numbered note), confirmed by reading both years' full note set (pages 23-39 of the FY2020 AR, pages 18-32 of the FY2019 AR) - genuinely no further detail available for these two years.
 PRESENTATION NOTE: 'Cash and cash equivalents' (FY2023-25) and 'Loans and advances to banks' (FY2021-22) are the same balance-sheet line under two labels - shown on one row. 'Capital redemption reserve' (FY2023-25) and 'Capital contribution' (FY2022, first appearing that year as a debt waiver from the ultimate controlling party) are the same £6,247k reserve under two labels - shown on one row. P&amp;L structure changed across the five years as the business grew: FY2025 nets fee income/expense into a single 'Net fee and commission (expense)/income' line with no separate 'Other income' row; FY2022-23 include a 'Net gain arising from derecognition of financial assets at amortised cost' line with no FY2024-25 equivalent; only FY2024-25 disclose 'Deferred tax liabilities' or a 'Goodwill' balance sheet line, both absent 2021-23; only FY2025 discloses 'Debt securities in issue' as a live balance (£89k), though the line existed as a zero balance from FY2024. Blank cells indicate that year's report did not disclose that specific line.</t>
         </is>
       </c>

--- a/banks/CHETWOOD FINANCIALS.xlsx
+++ b/banks/CHETWOOD FINANCIALS.xlsx
@@ -1918,6 +1918,9 @@
           <t>CET1 Ratio</t>
         </is>
       </c>
+      <c r="BA6" t="n">
+        <v>30</v>
+      </c>
       <c r="BB6" t="n">
         <v>28</v>
       </c>
@@ -1989,6 +1992,9 @@
           <t>Tier 1 Ratio</t>
         </is>
       </c>
+      <c r="BA7" t="n">
+        <v>30</v>
+      </c>
       <c r="BB7" t="n">
         <v>28</v>
       </c>
@@ -2060,6 +2066,9 @@
           <t>Total Capital Ratio</t>
         </is>
       </c>
+      <c r="BA8" t="n">
+        <v>31</v>
+      </c>
       <c r="BB8" t="n">
         <v>28</v>
       </c>
@@ -2131,6 +2140,9 @@
           <t>Leverage Ratio</t>
         </is>
       </c>
+      <c r="BA9" t="n">
+        <v>19</v>
+      </c>
       <c r="BB9" t="n">
         <v>23.4</v>
       </c>
@@ -2150,6 +2162,9 @@
           <t>LCR</t>
         </is>
       </c>
+      <c r="BA10" t="n">
+        <v>68110</v>
+      </c>
       <c r="BB10" t="n">
         <v>51086</v>
       </c>
@@ -2174,6 +2189,9 @@
           <t>NSFR</t>
         </is>
       </c>
+      <c r="BA11" t="n">
+        <v>193</v>
+      </c>
       <c r="BB11" t="n">
         <v>146.5</v>
       </c>
@@ -3102,7 +3120,11 @@
           <t>28%</t>
         </is>
       </c>
-      <c r="G33" s="6" t="n"/>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
       <c r="H33" s="6" t="n"/>
     </row>
     <row r="34">
@@ -3132,7 +3154,11 @@
           <t>28%</t>
         </is>
       </c>
-      <c r="G34" s="6" t="n"/>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
       <c r="H34" s="6" t="n"/>
     </row>
     <row r="35">
@@ -3162,7 +3188,11 @@
           <t>28%</t>
         </is>
       </c>
-      <c r="G35" s="6" t="n"/>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
       <c r="H35" s="6" t="n"/>
     </row>
     <row r="36">
@@ -3192,7 +3222,11 @@
           <t>23.4%</t>
         </is>
       </c>
-      <c r="G36" s="6" t="n"/>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
       <c r="H36" s="6" t="n"/>
     </row>
     <row r="37">
@@ -3222,7 +3256,11 @@
           <t>51,086%</t>
         </is>
       </c>
-      <c r="G37" s="6" t="n"/>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>68,110%</t>
+        </is>
+      </c>
       <c r="H37" s="6" t="n"/>
     </row>
     <row r="38">
@@ -3252,13 +3290,21 @@
           <t>146.5%</t>
         </is>
       </c>
-      <c r="G38" s="6" t="n"/>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>193%</t>
+        </is>
+      </c>
       <c r="H38" s="6" t="n"/>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Ratios are blank for FY2019/FY2020 (no Pillar 3 disclosure published for those years). Note the ~£8.1m FY2020-closing/FY2021-opening equity gap explained on the Statement of Changes in Equity sheet (FRS 102-to-IFRS transition). FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note.</t>
+          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Ratios are blank for FY2019 (Chetwood published no Pillar 3 disclosure that year); FY2020 was blank on the same basis until 2026-09-15, when its own 'as at 31 March 2020' Pillar 3 document was located - see any Pillar 3 sheet's source note for that correction. Note the ~£8.1m FY2020-closing/FY2021-opening equity gap explained on the Statement of Changes in Equity sheet (FRS 102-to-IFRS transition). FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
+SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
+Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one.</t>
         </is>
       </c>
     </row>
@@ -3373,13 +3419,22 @@
           <t>28%</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
+SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
+Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one.
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
     </row>
@@ -3389,10 +3444,14 @@
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
     </row>
@@ -3499,13 +3558,20 @@
       <c r="F4" s="6" t="n">
         <v>50637</v>
       </c>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="6" t="n">
+        <v>52835</v>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note. Equal to CET1/Tier 1 capital in every year shown - Chetwood has no Tier 2 capital either.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
+SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
+Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. Equal to CET1/Tier 1 capital in FY2021-FY2025 - Chetwood had no Tier 2 capital in those years. FY2020 is the exception and the only year that differs: its capital-resources table discloses £2,138k of Tier 2 capital on top of CET1 £50,697k, giving Total regulatory capital £52,835k as printed.
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
     </row>
@@ -3515,10 +3581,14 @@
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
     </row>
@@ -3633,13 +3703,22 @@
           <t>28%</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
+SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
+Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one.
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's 31% is higher than that year's 30% Tier 1 ratio because of the £2,138k of Tier 2 capital described on the Total Capital sheet - both figures are printed in the document's own Summary-analysis table, neither is derived.</t>
         </is>
       </c>
     </row>
@@ -3649,10 +3728,14 @@
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
     </row>
@@ -3761,13 +3844,16 @@
       <c r="F4" s="6" t="n">
         <v>178987</v>
       </c>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="6" t="n">
+        <v>171000</v>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is populated (unlike the other Pillar 3 sheets) because the FY2025 Pillar 3 document's own OV1 table (Section 6.3) discloses a full FY2024 comparative Total row (824,623) - the same figure the RWA Breakdown sheet's FY2024 column sums to. The KM1 template (Section 5) and LCR/NSFR/Overall Capital Requirement tables (Sections 5-6.6) that supply every other Pillar 3 metric on this workbook are all single-column ('as at 31 March 2025' only, no FY2024 comparative) - confirmed by reading the full FY2025 Pillar 3 document page by page, so CET1/Tier 1/Total Capital/all ratios/Leverage/LCR/NSFR/MREL genuinely remain blank for FY2024.</t>
+          <t>Note: FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's £171,000k is the document's own printed 'Risk Weighted Assets (£m) £171.0m' - disclosed to one decimal place of £m only, so the trailing three digits are the unit conversion, not spurious precision. It reconciles exactly to that document's own two components (Credit Risk RWAs £119.4m + operational-risk RWAs £51.6m = £171.0m), shown on the RWA Breakdown sheet.
+FY2024 is populated (unlike the other Pillar 3 sheets) because the FY2025 Pillar 3 document's own OV1 table (Section 6.3) discloses a full FY2024 comparative Total row (824,623) - the same figure the RWA Breakdown sheet's FY2024 column sums to. The KM1 template (Section 5) and LCR/NSFR/Overall Capital Requirement tables (Sections 5-6.6) that supply every other Pillar 3 metric on this workbook are all single-column ('as at 31 March 2025' only, no FY2024 comparative) - confirmed by reading the full FY2025 Pillar 3 document page by page, so CET1/Tier 1/Total Capital/all ratios/Leverage/LCR/NSFR/MREL genuinely remain blank for FY2024.</t>
         </is>
       </c>
     </row>
@@ -3777,10 +3863,14 @@
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3912,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000, Group/consolidated basis (FY2021: standalone entity). FY2019-FY2020 blank - no Pillar 3 disclosure was ever published for those years. See source note at bottom.</t>
+          <t>£'000, Group/consolidated basis (FY2020-FY2021: standalone entity). FY2019 blank - Chetwood published no Pillar 3 disclosure that year. FY2020 added 2026-09-15 and is stated to 0.1 of £m only. See source note at bottom.</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3993,9 @@
       <c r="F5" s="6" t="n">
         <v>126942</v>
       </c>
-      <c r="G5" s="6" t="n"/>
+      <c r="G5" s="6" t="n">
+        <v>119400</v>
+      </c>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
@@ -3971,7 +4063,9 @@
       <c r="F8" s="6" t="n">
         <v>51595</v>
       </c>
-      <c r="G8" s="6" t="n"/>
+      <c r="G8" s="6" t="n">
+        <v>51600</v>
+      </c>
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
@@ -3995,7 +4089,9 @@
       <c r="F9" s="5" t="n">
         <v>178987</v>
       </c>
-      <c r="G9" s="5" t="n"/>
+      <c r="G9" s="5" t="n">
+        <v>171000</v>
+      </c>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="11" ht="220" customHeight="1">
@@ -4005,13 +4101,14 @@
 FY2025/FY2024: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 6.3, which unlike the standalone FY2024 KM1 gap noted on the other Pillar 3 sheets, discloses its OV1 table's FY2024 comparative RWEA column in full - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2023/FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 8.3 (OV1 table with FY2022 comparative) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 5.4 (pre-KM1 category table) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 (as at 31st March 2020), Section 1.2 ('Credit Risk Weighted Assets', p.3) and Section 8 (Operational risk, p.19) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf. This edition has no OV1 or category table at all; it states only Credit Risk RWAs of £119.4m (itself split in the narrative into £112.1m customer lending + £5.5m other assets + £1.8m lending to banks) and an operational-risk RWA requirement of £51.6m, which together make its printed £171.0m total exactly. Counterparty credit risk and securitisation are left blank rather than assumed nil - the document never mentions either, and Chetwood had no securitised exposures that early.
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
 FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
 HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
 - Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
 - FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
 - FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
-- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
+- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table. SUPERSEDED IN PART (2026-09-15): this note previously also claimed FY2019 and FY2020 had 'no Pillar 3 disclosure at all' and that all 11 Pillar 3 metric sheets plus the RWA Breakdown sheet were genuinely not disclosed for both years. That holds for FY2019 only. A 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' document was located 2026-09-15 and FY2020 is now populated across the Pillar 3 sheets - see the source note on any Pillar 3 sheet for the document and the correction. The accounting-framework point itself is unaffected: FY2019 and FY2020 statutory accounts remain FRS 102, and that FY2020 Pillar 3 document says so itself ('Chetwood currently prepares its Financial Statements under FRS 102. Chetwood has developed an IFRS9 expected loss model that will be adopted in due course').
 - A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 FINDING: the other Pillar 3 sheets in this workbook leave FY2024 blank because no dedicated 'as at 31 March 2024' Pillar 3 document was ever published - true for the CET1/Tier 1/Total Capital/ratio figures. However the FY2025 Pillar 3 document's own OV1 table (used here) discloses a full FY2024 comparative RWEA-by-category column, so RWA Breakdown alone can be populated for FY2024 even though the other Pillar 3 sheets cannot.
 PRESENTATION NOTE: FY2021's pre-KM1 category table has no separate 'Securitisation' line (Chetwood had no securitised exposures that early) and combines credit valuation adjustment into Counterparty credit risk rather than breaking it out - both blank rather than assumed zero-and-separate.</t>
@@ -4150,13 +4247,22 @@
           <t>23.4%</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note. Unlike Barclays/Monzo, Chetwood's disclosures do not distinguish an 'excluding/including claims on central banks' basis in any year - a single leverage ratio definition is used throughout (Tier 1 capital / total exposure measure). FY2021 used a pre-KM1 narrative table; FY2022 onward uses the formal KM1 rows 13-14.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
+SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
+Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. Unlike Barclays/Monzo, Chetwood's disclosures do not distinguish an 'excluding/including claims on central banks' basis in any year - a single leverage ratio definition is used throughout (Tier 1 capital / total exposure measure). FY2021 used a pre-KM1 narrative table; FY2022 onward uses the formal KM1 rows 13-14.
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020 discloses only the headline ratio (19%, stated twice - in the Summary-analysis table and again in Section 3.6, 'At 31 March 2020, the leverage ratio stood at 19%'); no total exposure measure is given anywhere in that document, so that row stays blank for FY2020 rather than being back-solved from the ratio.</t>
         </is>
       </c>
     </row>
@@ -4166,10 +4272,14 @@
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
     </row>
@@ -4364,13 +4474,22 @@
           <t>51,086%</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>68,110%</t>
+        </is>
+      </c>
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note. FY2021 disclosed only the headline ratio in narrative form (no HQLA/outflow £ breakdown was published that year - the formal KM1 liquidity rows were introduced from FY2022). Chetwood's LCR ratios are extremely high because, as a young/small deposit-taker at the time, its regulatory outflow assumptions were small relative to its liquid asset holdings - this is as disclosed by Chetwood, not a transcription error.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
+SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
+Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. FY2020 and FY2021 disclosed only the headline ratio in narrative form (no HQLA/outflow £ breakdown was published those years - the formal KM1 liquidity rows were introduced from FY2022). Chetwood's LCR ratios are extremely high because, as a young/small deposit-taker at the time, its regulatory outflow assumptions were small relative to its liquid asset holdings - this is as disclosed by Chetwood, not a transcription error; the FY2020 document says so in terms ('Given the early stage of Chetwood's development and the limited value of outflows the calculation of the Liquidity Coverage Ratio (LCR) results in a very high value. Chetwood's LCR ratio as at 31st March 2020 was 68,110%').
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
     </row>
@@ -4380,10 +4499,14 @@
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
     </row>
@@ -4538,13 +4661,22 @@
           <t>146.5%</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>193%</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note. FY2021's NSFR figure (146.5%) is quoted exactly as printed in the FY2021 Pillar 3 report, which oddly labels it 'as at the 31 March 2020' in a document otherwise dated 'as at 31 March 2021' - this looks like a typo in Chetwood's own document, but it is reproduced verbatim rather than silently corrected; no £ breakdown was published for FY2021 (the formal KM1 NSFR rows were introduced from FY2022).</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
+SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
+Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. FY2021's NSFR figure (146.5%) is quoted exactly as printed in the FY2021 Pillar 3 report, which oddly labels it 'as at the 31 March 2020' in a document otherwise dated 'as at 31 March 2021' - this looks like a typo in Chetwood's own document, but it is reproduced verbatim rather than silently corrected; no £ breakdown was published for FY2020 or FY2021 (the formal KM1 NSFR rows were introduced from FY2022).
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's own 193% comes from that year's own document ('The Company's Net Stable Funding Ratio (NSFR) as at the 31 March 2020 was 193%') and is a genuinely different figure from the 146.5% the FY2021 report mislabels as 'at the 31 March 2020' - further evidence that the FY2021 label is the typo, and that 146.5% belongs to FY2021 as carried here.</t>
         </is>
       </c>
     </row>
@@ -4554,10 +4686,14 @@
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4814,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Chetwood is classified as a 'small and non-complex institution' (SNCI) and is not subject to any MREL requirement above its minimum capital requirement - stated explicitly in the FY2021, FY2022 and FY2023 Pillar 3 reports ('...has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its [minimum capital requirement]'). The FY2025 report uses a shorter reduced-disclosure format that omits this narrative section, but there is no indication Chetwood's MREL/SNCI status has changed. FY2019/FY2020 are left blank rather than 'Not applicable' - no Pillar 3 disclosure was published for those years, so Chetwood's SNCI/MREL status at that time was never publicly stated.</t>
+          <t>Note: Chetwood is classified as a 'small and non-complex institution' (SNCI) and is not subject to any MREL requirement above its minimum capital requirement - stated explicitly in the FY2021, FY2022 and FY2023 Pillar 3 reports ('...has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its [minimum capital requirement]'). The FY2025 report uses a shorter reduced-disclosure format that omits this narrative section, but there is no indication Chetwood's MREL/SNCI status has changed. FY2019/FY2020 are left blank rather than 'Not applicable'. For FY2019 no Pillar 3 disclosure was published at all. For FY2020 one was (located 2026-09-15 - see the source note), but it was read in full and the word MREL does not appear anywhere in it, so Chetwood's SNCI/MREL status as at 31 March 2020 was still never publicly stated - blank remains correct for that year, now on evidence rather than on the absence of a document.</t>
         </is>
       </c>
     </row>
@@ -4688,10 +4824,14 @@
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5744,7 @@
 - Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
 - FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
 - FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
-- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
+- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table. SUPERSEDED IN PART (2026-09-15): this note previously also claimed FY2019 and FY2020 had 'no Pillar 3 disclosure at all' and that all 11 Pillar 3 metric sheets plus the RWA Breakdown sheet were genuinely not disclosed for both years. That holds for FY2019 only. A 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' document was located 2026-09-15 and FY2020 is now populated across the Pillar 3 sheets - see the source note on any Pillar 3 sheet for the document and the correction. The accounting-framework point itself is unaffected: FY2019 and FY2020 statutory accounts remain FRS 102, and that FY2020 Pillar 3 document says so itself ('Chetwood currently prepares its Financial Statements under FRS 102. Chetwood has developed an IFRS9 expected loss model that will be adopted in due course').
 - A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
 INVESTMENT IN DEBT SECURITIES BREAKDOWN NOTE (added 2026-09-07): 'Investment in debt securities' is split into 'UK government treasury bills, measured at FVOCI' and 'Other debt securities (ABS loan notes / fixed rate bonds / covered bonds / senior loan notes), at amortised cost', sourced from each year's own Note 14/15/16 ('Investment in debt securities'), which reconciles exactly to the original total in every year it is disclosed:
@@ -6226,7 +6366,7 @@
 - Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
 - FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
 - FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
-- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
+- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table. SUPERSEDED IN PART (2026-09-15): this note previously also claimed FY2019 and FY2020 had 'no Pillar 3 disclosure at all' and that all 11 Pillar 3 metric sheets plus the RWA Breakdown sheet were genuinely not disclosed for both years. That holds for FY2019 only. A 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' document was located 2026-09-15 and FY2020 is now populated across the Pillar 3 sheets - see the source note on any Pillar 3 sheet for the document and the correction. The accounting-framework point itself is unaffected: FY2019 and FY2020 statutory accounts remain FRS 102, and that FY2020 Pillar 3 document says so itself ('Chetwood currently prepares its Financial Statements under FRS 102. Chetwood has developed an IFRS9 expected loss model that will be adopted in due course').
 - A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
 INVESTMENT IN DEBT SECURITIES BREAKDOWN NOTE (added 2026-09-07): 'Investment in debt securities' is split into 'UK government treasury bills, measured at FVOCI' and 'Other debt securities (ABS loan notes / fixed rate bonds / covered bonds / senior loan notes), at amortised cost', sourced from each year's own Note 14/15/16 ('Investment in debt securities'), which reconciles exactly to the original total in every year it is disclosed:
@@ -7222,7 +7362,7 @@
 - Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
 - FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
 - FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
-- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
+- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table. SUPERSEDED IN PART (2026-09-15): this note previously also claimed FY2019 and FY2020 had 'no Pillar 3 disclosure at all' and that all 11 Pillar 3 metric sheets plus the RWA Breakdown sheet were genuinely not disclosed for both years. That holds for FY2019 only. A 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' document was located 2026-09-15 and FY2020 is now populated across the Pillar 3 sheets - see the source note on any Pillar 3 sheet for the document and the correction. The accounting-framework point itself is unaffected: FY2019 and FY2020 statutory accounts remain FRS 102, and that FY2020 Pillar 3 document says so itself ('Chetwood currently prepares its Financial Statements under FRS 102. Chetwood has developed an IFRS9 expected loss model that will be adopted in due course').
 - A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
 INVESTMENT IN DEBT SECURITIES BREAKDOWN NOTE (added 2026-09-07): 'Investment in debt securities' is split into 'UK government treasury bills, measured at FVOCI' and 'Other debt securities (ABS loan notes / fixed rate bonds / covered bonds / senior loan notes), at amortised cost', sourced from each year's own Note 14/15/16 ('Investment in debt securities'), which reconciles exactly to the original total in every year it is disclosed:
@@ -8626,7 +8766,7 @@
 - Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
 - FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
 - FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
-- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
+- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table. SUPERSEDED IN PART (2026-09-15): this note previously also claimed FY2019 and FY2020 had 'no Pillar 3 disclosure at all' and that all 11 Pillar 3 metric sheets plus the RWA Breakdown sheet were genuinely not disclosed for both years. That holds for FY2019 only. A 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' document was located 2026-09-15 and FY2020 is now populated across the Pillar 3 sheets - see the source note on any Pillar 3 sheet for the document and the correction. The accounting-framework point itself is unaffected: FY2019 and FY2020 statutory accounts remain FRS 102, and that FY2020 Pillar 3 document says so itself ('Chetwood currently prepares its Financial Statements under FRS 102. Chetwood has developed an IFRS9 expected loss model that will be adopted in due course').
 - A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 PRESENTATION NOTE: Line items changed across the five years as the business grew (e.g. debt securities and derivative-related lines were introduced/split differently year to year, and FY2025 switched the starting line from 'Loss after tax' to '(Loss)/profit before tax'). Blank cells indicate that year's report did not disclose that specific split. Section totals (net cash from operating/investing/financing, cash and cash equivalents) are consistent and reconcile exactly across all 5 years.
 DATA QUALITY NOTE (added 2026-08-27, found during a project-wide sanity check): the AR24/AR25 source statements print BOTH a Group and a Company column side by side for each year; three line items were originally transcribed from the wrong column or with a digit error, causing FY2023/FY2024's operating and investing TOTALs to not reconcile to their own line items. Corrected against both AR24 (own-year figures) and AR25's FY2024 comparative column (cross-checked, both agree): 'Fair value adjustment on hedged items' FY2024 corrected from -11,182 to the Group figure -11,782 (a transcription slip); 'Interest received from investing activities' FY2024 corrected from 11,601 to the Group figure 17,601 (transcription slip); 'Loss on disposal of property, plant and equipment' FY2023 corrected from 4 to the Group figure 8 (was the Company figure); 'Impairment of investment in subsidiary/Yobota' FY2023 corrected from 6,753 to 0/nil (the Group figure is nil - 6,753 was the Company-only figure); 'Subscription of shares in subsidiary undertaking' FY2023 (-1,500) removed entirely - it is a Company-only line with no Group-basis equivalent, so it never belonged in this Group-basis statement. All four sections now reconcile exactly to the penny against the primary source.
@@ -9126,7 +9266,7 @@
 - Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
 - FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
 - FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
-- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table and no Pillar 3 disclosure at all (the FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course' - it wasn't yet). All 11 Pillar 3 metric sheets and the RWA Breakdown sheet are genuinely 'Not publicly disclosed' for FY2019 and FY2020 - a real self-skip, not a gap in transcription.
+- FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table. SUPERSEDED IN PART (2026-09-15): this note previously also claimed FY2019 and FY2020 had 'no Pillar 3 disclosure at all' and that all 11 Pillar 3 metric sheets plus the RWA Breakdown sheet were genuinely not disclosed for both years. That holds for FY2019 only. A 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' document was located 2026-09-15 and FY2020 is now populated across the Pillar 3 sheets - see the source note on any Pillar 3 sheet for the document and the correction. The accounting-framework point itself is unaffected: FY2019 and FY2020 statutory accounts remain FRS 102, and that FY2020 Pillar 3 document says so itself ('Chetwood currently prepares its Financial Statements under FRS 102. Chetwood has developed an IFRS9 expected loss model that will be adopted in due course').
 - A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
 PRESENTATION NOTE: these Note 36/37 tables report gross/net loans and advances measured at amortised cost only. The Balance Sheet's own 'Loans and advances to customers' line is larger in every year from FY2022 onward (e.g. FY2025: £2,691,247k on the Balance Sheet vs £2,665,626k gross / £2,655,384k net summed here) because some loans are measured at fair value through profit or loss and fall outside this amortised-cost IFRS 9 note - this gap is a genuine measurement-basis difference disclosed by the Bank, not a transcription error, and is not force-reconciled here. FY2021 is the exception: with no secured book yet and no FVTPL loans, the combined stage total ties to the Balance Sheet exactly (£156,249k both ways).
 FY2019/FY2020 NOTE: these two years' statutory accounts were prepared under UK GAAP FRS 102 (not IFRS), before Chetwood adopted IFRS 9 - there is no loan-staging (Stage 1/2/3) table in either year's accounts, only a single aggregate net loan balance and a simple impairment-allowance movement in the notes. The Stage/ECL breakdown rows above are genuinely 'Not publicly disclosed' for FY2019 and FY2020; only the single 'Net loans and advances to customers' total row is populated for those two years, tying exactly to the Balance Sheet.</t>
@@ -9170,7 +9310,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000, Group/consolidated basis (FY2021: standalone entity)</t>
+          <t>£'000, Group/consolidated basis (FY2020-FY2021: standalone entity)</t>
         </is>
       </c>
     </row>
@@ -9235,13 +9375,20 @@
       <c r="F4" s="6" t="n">
         <v>50637</v>
       </c>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="6" t="n">
+        <v>50697</v>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
+SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
+Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one.
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
     </row>
@@ -9251,10 +9398,14 @@
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -9369,33 +9520,73 @@
           <t>28%</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note. FY2021 is as stated in the source (rounded to the nearest whole percent; no decimal figure was disclosed that year).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 (CET1) capital ratio per Annual Report KPI table (whole %, alternative basis - see note)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
+SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
+Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. FY2021 is as stated in the source (rounded to the nearest whole percent; no decimal figure was disclosed that year).
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. The FY2020 document's Summary-analysis table prints a 'Tier 1 Ratio' of 30% and no separate CET1 ratio line; its own capital-resources table shows CET1 £50,697k going straight to Tier 2 with no Additional Tier 1 line, so Tier 1 = CET1 that year and 30% is the CET1 ratio as well - the same treatment already applied to every other year on this sheet.
+SECOND ROW (alternative basis, added 2026-09-15): the Annual Reports' KPI tables are the only source that states any FY2024 capital ratio, so their whole-percent Group CET1 ratio is carried on its own row - FY2024 21% (stated identically in the FY2024 report's own year column and the FY2025 report's FY2024 comparative column, two independent confirmations). It is NOT merged into the primary row because the two series do not agree: for FY2025 the KPI table says 16% where the Pillar 3 KM1 says 15.2%, a difference too large to be rounding, cause not explained in either document (FY2023 does reconcile: 27% vs 26.6%). Treat the FY2024 21% as indicative of level, not as a KM1-basis figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A6:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9495,13 +9686,20 @@
       <c r="F4" s="6" t="n">
         <v>50637</v>
       </c>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="6" t="n">
+        <v>50697</v>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived. FY2019 and FY2020 are also blank on every Pillar 3 sheet - Chetwood published no Pillar 3 disclosure at all for those two years (its FY2018/FY2019 statutory accounts say a Pillar 3 document 'will be published...in due course', but the earliest one actually published/archived is 'as at 31 March 2021'). See source note. Equal to CET1 capital in every year shown - Chetwood has no Additional Tier 1 (AT1) instruments.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
+SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
+Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. Equal to CET1 capital in every year shown - Chetwood has no Additional Tier 1 (AT1) instruments (in FY2020 confirmed by its capital-resources table running CET1 -&gt; Tier 2 -&gt; Total with no AT1 line).
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
     </row>
@@ -9511,10 +9709,14 @@
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2019/FY2020: No Pillar 3 disclosure was ever published for these years - as at 31 March 2021 is Chetwood's earliest published/archived Pillar 3 document. Left blank.</t>
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
     </row>

--- a/banks/CHETWOOD FINANCIALS.xlsx
+++ b/banks/CHETWOOD FINANCIALS.xlsx
@@ -3445,12 +3445,12 @@
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
 FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
@@ -3582,12 +3582,12 @@
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
 FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
@@ -3729,12 +3729,12 @@
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
 FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
@@ -3864,12 +3864,12 @@
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
 FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
@@ -4099,9 +4099,9 @@
         <is>
           <t>Sources - Chetwood's own Pillar 3 Disclosures, Section 6 'Overview of RWAs' (OV1 template from FY2022 onward; FY2021 uses an equivalent pre-KM1 category table).
 FY2025/FY2024: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 6.3, which unlike the standalone FY2024 KM1 gap noted on the other Pillar 3 sheets, discloses its OV1 table's FY2024 comparative RWEA column in full - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2023/FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 8.3 (OV1 table with FY2022 comparative) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 5.4 (pre-KM1 category table) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 (as at 31st March 2020), Section 1.2 ('Credit Risk Weighted Assets', p.3) and Section 8 (Operational risk, p.19) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf. This edition has no OV1 or category table at all; it states only Credit Risk RWAs of £119.4m (itself split in the narrative into £112.1m customer lending + £5.5m other assets + £1.8m lending to banks) and an operational-risk RWA requirement of £51.6m, which together make its printed £171.0m total exactly. Counterparty credit risk and securitisation are left blank rather than assumed nil - the document never mentions either, and Chetwood had no securitised exposures that early.
+FY2023/FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 8.3 (OV1 table with FY2022 comparative) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 5.4 (pre-KM1 category table) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 (as at 31st March 2020), Section 1.2 ('Credit Risk Weighted Assets', p.3) and Section 8 (Operational risk, p.19) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf. This edition has no OV1 or category table at all; it states only Credit Risk RWAs of £119.4m (itself split in the narrative into £112.1m customer lending + £5.5m other assets + £1.8m lending to banks) and an operational-risk RWA requirement of £51.6m, which together make its printed £171.0m total exactly. Counterparty credit risk and securitisation are left blank rather than assumed nil - the document never mentions either, and Chetwood had no securitised exposures that early.
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
 FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
 HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
@@ -4273,12 +4273,12 @@
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
 FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
@@ -4500,12 +4500,12 @@
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
 FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
@@ -4687,12 +4687,12 @@
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
 FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
@@ -4825,12 +4825,12 @@
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
 FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
@@ -5734,8 +5734,8 @@
         <is>
           <t>Sources - Chetwood Financial Limited's own Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, transcribed from each year's own Annual Report (not a later year's comparative column, except where noted). See entity note below re: FY2021 (standalone) and the FY2024 P&amp;L OCR-corruption note.
 FY2025/FY2024: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2025, p.44-47 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
-FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.24-27 (prior-year comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (As with the Cash Flow Statement, the FY2023 Annual Report's own PDF has a text-encoding fault; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
-FY2022/FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.22-25 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, Group and Company for FY2021) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
+FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.24-27 (prior-year comparative column) - http://web.archive.org/web/20240920030034id_/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (As with the Cash Flow Statement, the FY2023 Annual Report's own PDF has a text-encoding fault; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
+FY2022/FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.22-25 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, Group and Company for FY2021) - http://web.archive.org/web/20230131231341id_/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
 FY2020: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2020, p.19-21 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 FY2019: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2019, p.14-16 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
@@ -5749,8 +5749,8 @@
 DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
 INVESTMENT IN DEBT SECURITIES BREAKDOWN NOTE (added 2026-09-07): 'Investment in debt securities' is split into 'UK government treasury bills, measured at FVOCI' and 'Other debt securities (ABS loan notes / fixed rate bonds / covered bonds / senior loan notes), at amortised cost', sourced from each year's own Note 14/15/16 ('Investment in debt securities'), which reconciles exactly to the original total in every year it is disclosed:
 FY2025/FY2024: Annual Report 2025, p.71 (Note 14) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf. FY2025: FVOCI Treasury Bills £202,151k; amortised cost £1,119,515k (ABS £525,248k + Fixed rate bonds £384,031k + Covered bonds £39,059k + Senior loan notes £171,177k). FY2024: no Treasury Bills held (FVOCI leg £nil); amortised cost £537,291k (ABS £435,075k + Fixed rate bonds £102,216k).
-FY2023: Annual Report 2024, p.40 (Note 15, FY2023 comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. FVOCI Treasury Bills £4,825k; amortised cost £124,770k (ABS loan notes only).
-FY2022: Annual Report 2022, p.39 (Note 16) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf. The entire £4,883k balance is Treasury Bills measured at FVOCI ('all instruments are investments in UK sovereign treasury bills') - no amortised-cost leg that year.
+FY2023: Annual Report 2024, p.40 (Note 15, FY2023 comparative column) - http://web.archive.org/web/20240920030034id_/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. FVOCI Treasury Bills £4,825k; amortised cost £124,770k (ABS loan notes only).
+FY2022: Annual Report 2022, p.39 (Note 16) - http://web.archive.org/web/20230131231341id_/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf. The entire £4,883k balance is Treasury Bills measured at FVOCI ('all instruments are investments in UK sovereign treasury bills') - no amortised-cost leg that year.
 FY2020/FY2019: no note breaks down this line at all in either year's own Annual Report - the Statement of Financial Position shows 'Investment in debt securities' with no note-reference number next to it (unlike every other line, which cross-references a numbered note), confirmed by reading both years' full note set (pages 23-39 of the FY2020 AR, pages 18-32 of the FY2019 AR) - genuinely no further detail available for these two years.
 PRESENTATION NOTE: 'Cash and cash equivalents' (FY2023-25) and 'Loans and advances to banks' (FY2021-22) are the same balance-sheet line under two labels - shown on one row. 'Capital redemption reserve' (FY2023-25) and 'Capital contribution' (FY2022, first appearing that year as a debt waiver from the ultimate controlling party) are the same £6,247k reserve under two labels - shown on one row. P&amp;L structure changed across the five years as the business grew: FY2025 nets fee income/expense into a single 'Net fee and commission (expense)/income' line with no separate 'Other income' row; FY2022-23 include a 'Net gain arising from derecognition of financial assets at amortised cost' line with no FY2024-25 equivalent; only FY2024-25 disclose 'Deferred tax liabilities' or a 'Goodwill' balance sheet line, both absent 2021-23; only FY2025 discloses 'Debt securities in issue' as a live balance (£89k), though the line existed as a zero balance from FY2024. Blank cells indicate that year's report did not disclose that specific line.</t>
         </is>
@@ -6356,8 +6356,8 @@
         <is>
           <t>Sources - Chetwood Financial Limited's own Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, transcribed from each year's own Annual Report (not a later year's comparative column, except where noted). See entity note below re: FY2021 (standalone) and the FY2024 P&amp;L OCR-corruption note.
 FY2025/FY2024: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2025, p.44-47 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
-FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.24-27 (prior-year comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (As with the Cash Flow Statement, the FY2023 Annual Report's own PDF has a text-encoding fault; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
-FY2022/FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.22-25 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, Group and Company for FY2021) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
+FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.24-27 (prior-year comparative column) - http://web.archive.org/web/20240920030034id_/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (As with the Cash Flow Statement, the FY2023 Annual Report's own PDF has a text-encoding fault; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
+FY2022/FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.22-25 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, Group and Company for FY2021) - http://web.archive.org/web/20230131231341id_/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
 FY2020: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2020, p.19-21 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 FY2019: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2019, p.14-16 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
@@ -6371,8 +6371,8 @@
 DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
 INVESTMENT IN DEBT SECURITIES BREAKDOWN NOTE (added 2026-09-07): 'Investment in debt securities' is split into 'UK government treasury bills, measured at FVOCI' and 'Other debt securities (ABS loan notes / fixed rate bonds / covered bonds / senior loan notes), at amortised cost', sourced from each year's own Note 14/15/16 ('Investment in debt securities'), which reconciles exactly to the original total in every year it is disclosed:
 FY2025/FY2024: Annual Report 2025, p.71 (Note 14) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf. FY2025: FVOCI Treasury Bills £202,151k; amortised cost £1,119,515k (ABS £525,248k + Fixed rate bonds £384,031k + Covered bonds £39,059k + Senior loan notes £171,177k). FY2024: no Treasury Bills held (FVOCI leg £nil); amortised cost £537,291k (ABS £435,075k + Fixed rate bonds £102,216k).
-FY2023: Annual Report 2024, p.40 (Note 15, FY2023 comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. FVOCI Treasury Bills £4,825k; amortised cost £124,770k (ABS loan notes only).
-FY2022: Annual Report 2022, p.39 (Note 16) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf. The entire £4,883k balance is Treasury Bills measured at FVOCI ('all instruments are investments in UK sovereign treasury bills') - no amortised-cost leg that year.
+FY2023: Annual Report 2024, p.40 (Note 15, FY2023 comparative column) - http://web.archive.org/web/20240920030034id_/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. FVOCI Treasury Bills £4,825k; amortised cost £124,770k (ABS loan notes only).
+FY2022: Annual Report 2022, p.39 (Note 16) - http://web.archive.org/web/20230131231341id_/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf. The entire £4,883k balance is Treasury Bills measured at FVOCI ('all instruments are investments in UK sovereign treasury bills') - no amortised-cost leg that year.
 FY2020/FY2019: no note breaks down this line at all in either year's own Annual Report - the Statement of Financial Position shows 'Investment in debt securities' with no note-reference number next to it (unlike every other line, which cross-references a numbered note), confirmed by reading both years' full note set (pages 23-39 of the FY2020 AR, pages 18-32 of the FY2019 AR) - genuinely no further detail available for these two years.
 PRESENTATION NOTE: 'Cash and cash equivalents' (FY2023-25) and 'Loans and advances to banks' (FY2021-22) are the same balance-sheet line under two labels - shown on one row. 'Capital redemption reserve' (FY2023-25) and 'Capital contribution' (FY2022, first appearing that year as a debt waiver from the ultimate controlling party) are the same £6,247k reserve under two labels - shown on one row. P&amp;L structure changed across the five years as the business grew: FY2025 nets fee income/expense into a single 'Net fee and commission (expense)/income' line with no separate 'Other income' row; FY2022-23 include a 'Net gain arising from derecognition of financial assets at amortised cost' line with no FY2024-25 equivalent; only FY2024-25 disclose 'Deferred tax liabilities' or a 'Goodwill' balance sheet line, both absent 2021-23; only FY2025 discloses 'Debt securities in issue' as a live balance (£89k), though the line existed as a zero balance from FY2024. Blank cells indicate that year's report did not disclose that specific line.</t>
         </is>
@@ -7352,8 +7352,8 @@
         <is>
           <t>Sources - Chetwood Financial Limited's own Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, transcribed from each year's own Annual Report (not a later year's comparative column, except where noted). See entity note below re: FY2021 (standalone) and the FY2024 P&amp;L OCR-corruption note.
 FY2025/FY2024: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2025, p.44-47 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
-FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.24-27 (prior-year comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (As with the Cash Flow Statement, the FY2023 Annual Report's own PDF has a text-encoding fault; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
-FY2022/FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.22-25 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, Group and Company for FY2021) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
+FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.24-27 (prior-year comparative column) - http://web.archive.org/web/20240920030034id_/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (As with the Cash Flow Statement, the FY2023 Annual Report's own PDF has a text-encoding fault; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
+FY2022/FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.22-25 (Consolidated Statement of Financial Position / Statement of Total Comprehensive Income / Statement of Changes in Equity, Group and Company for FY2021) - http://web.archive.org/web/20230131231341id_/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
 FY2020: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2020, p.19-21 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 FY2019: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2019, p.14-16 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
@@ -7367,8 +7367,8 @@
 DATA QUALITY NOTE: the FY2024 Annual Report's own P&amp;L page (used for FY2023's comparative column) has the same text-encoding fault as its Cash Flow Statement page, corrupting individual digits in places (e.g. that page's own FY2024 'Impairment of loans and advances to customers' prints as -855, matching the clean FY2025 report's comparative figure exactly). The equity statement page in the same FY2024 report similarly corrupts one FY2024 'Total comprehensive income' cell (prints -8,605 instead of -8,685) - the FY2025 report's own FY2023-25 equity table and the P&amp;L's own OCI total agree exactly on -8,685, so -8,685 is used here.
 INVESTMENT IN DEBT SECURITIES BREAKDOWN NOTE (added 2026-09-07): 'Investment in debt securities' is split into 'UK government treasury bills, measured at FVOCI' and 'Other debt securities (ABS loan notes / fixed rate bonds / covered bonds / senior loan notes), at amortised cost', sourced from each year's own Note 14/15/16 ('Investment in debt securities'), which reconciles exactly to the original total in every year it is disclosed:
 FY2025/FY2024: Annual Report 2025, p.71 (Note 14) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf. FY2025: FVOCI Treasury Bills £202,151k; amortised cost £1,119,515k (ABS £525,248k + Fixed rate bonds £384,031k + Covered bonds £39,059k + Senior loan notes £171,177k). FY2024: no Treasury Bills held (FVOCI leg £nil); amortised cost £537,291k (ABS £435,075k + Fixed rate bonds £102,216k).
-FY2023: Annual Report 2024, p.40 (Note 15, FY2023 comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. FVOCI Treasury Bills £4,825k; amortised cost £124,770k (ABS loan notes only).
-FY2022: Annual Report 2022, p.39 (Note 16) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf. The entire £4,883k balance is Treasury Bills measured at FVOCI ('all instruments are investments in UK sovereign treasury bills') - no amortised-cost leg that year.
+FY2023: Annual Report 2024, p.40 (Note 15, FY2023 comparative column) - http://web.archive.org/web/20240920030034id_/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. FVOCI Treasury Bills £4,825k; amortised cost £124,770k (ABS loan notes only).
+FY2022: Annual Report 2022, p.39 (Note 16) - http://web.archive.org/web/20230131231341id_/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf. The entire £4,883k balance is Treasury Bills measured at FVOCI ('all instruments are investments in UK sovereign treasury bills') - no amortised-cost leg that year.
 FY2020/FY2019: no note breaks down this line at all in either year's own Annual Report - the Statement of Financial Position shows 'Investment in debt securities' with no note-reference number next to it (unlike every other line, which cross-references a numbered note), confirmed by reading both years' full note set (pages 23-39 of the FY2020 AR, pages 18-32 of the FY2019 AR) - genuinely no further detail available for these two years.
 PRESENTATION NOTE: 'Cash and cash equivalents' (FY2023-25) and 'Loans and advances to banks' (FY2021-22) are the same balance-sheet line under two labels - shown on one row. 'Capital redemption reserve' (FY2023-25) and 'Capital contribution' (FY2022, first appearing that year as a debt waiver from the ultimate controlling party) are the same £6,247k reserve under two labels - shown on one row. P&amp;L structure changed across the five years as the business grew: FY2025 nets fee income/expense into a single 'Net fee and commission (expense)/income' line with no separate 'Other income' row; FY2022-23 include a 'Net gain arising from derecognition of financial assets at amortised cost' line with no FY2024-25 equivalent; only FY2024-25 disclose 'Deferred tax liabilities' or a 'Goodwill' balance sheet line, both absent 2021-23; only FY2025 discloses 'Debt securities in issue' as a live balance (£89k), though the line existed as a zero balance from FY2024. Blank cells indicate that year's report did not disclose that specific line.</t>
         </is>
@@ -8754,10 +8754,10 @@
         <is>
           <t>Sources - all figures are Chetwood Financial Limited Group (consolidated) cash flow statement, £'000, unless noted. See entity note above re: FY2021 (standalone) and FY2024 (Pillar 3 gap).
 FY2025: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2025, p.48-49 (Consolidated and company statement of cashflows) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
-FY2024: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.29 (Consolidated and Company Statement of Cashflows) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf
-FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.29 (prior-year comparative column) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (The FY2023 Annual Report's own PDF has a text-encoding fault that corrupts extracted figures; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
-FY2022: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.26 (Consolidated and Company Statement of Cashflows) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
-FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2021, p.28 (Statement of Cashflows, standalone entity) - http://web.archive.org/web/20210830132929/https://chetwood.co/static/3d0ade6e892213e246ca03dc1d84b417/AnnualReport.pdf
+FY2024: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.29 (Consolidated and Company Statement of Cashflows) - http://web.archive.org/web/20240920030034id_/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf
+FY2023: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2024, p.29 (prior-year comparative column) - http://web.archive.org/web/20240920030034id_/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf. (The FY2023 Annual Report's own PDF has a text-encoding fault that corrupts extracted figures; the FY2024 report's clean comparative column was used instead - both present the same audited FY2023 statutory figures.)
+FY2022: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2022, p.26 (Consolidated and Company Statement of Cashflows) - http://web.archive.org/web/20230131231341id_/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
+FY2021: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2021, p.28 (Statement of Cashflows, standalone entity) - http://web.archive.org/web/20210830132929id_/https://chetwood.co/static/3d0ade6e892213e246ca03dc1d84b417/AnnualReport.pdf
 FY2020: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2020, p.22 (Statement of Cashflows, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 FY2019: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2019, p.17 (Statement of Cashflows, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
@@ -9256,8 +9256,8 @@
         <is>
           <t>Sources - Chetwood Financial Limited's own Credit Risk / Note 36 (37 in earlier years) disclosures, combining the separately-disclosed 'unsecured lending at amortised cost' and 'secured lending' IFRS 9 stage tables (secured mortgage lending only exists from FY2022, when CHL Mortgages for Intermediaries Limited was acquired - FY2021 is unsecured lending only, and ties exactly to that year's Balance Sheet loan figure).
 FY2025/FY2024: Annual Report 2025, p.96-100 (Note 36.2/36.3 Credit quality) - https://chetwoodbank.co.uk/documents/chetwood-bank-annual-report.pdf
-FY2023: Annual Report 2024, p.51-52 (Note 37, FY2023 comparative tables) - http://web.archive.org/web/20240920030034/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf
-FY2022/FY2021: Annual Report 2022, p.49-52 (Note 31.2 Credit quality) - http://web.archive.org/web/20230131231341/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
+FY2023: Annual Report 2024, p.51-52 (Note 37, FY2023 comparative tables) - http://web.archive.org/web/20240920030034id_/https://chetwood.co/static/97d26e488d5277699e5b9a9983db4d5b/AnnualReport.pdf
+FY2022/FY2021: Annual Report 2022, p.49-52 (Note 31.2 Credit quality) - http://web.archive.org/web/20230131231341id_/https://chetwood.co/static/7fbc3d1ed9c0913dca3435f640a5a570/AnnualReport.pdf
 FY2020: Annual Report and Financial Statements, year ended 31 March 2020, p.20/28 (Statement of Financial Position net loan balance; no IFRS 9 stage table - see FRS 102 note below) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2019: Annual Report and Financial Statements, year ended 31 March 2019, p.15 (Statement of Financial Position net loan balance; no IFRS 9 stage table - see FRS 102 note below) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
@@ -9399,12 +9399,12 @@
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
 FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
@@ -9573,12 +9573,12 @@
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
 FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>
@@ -9710,12 +9710,12 @@
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
 FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
 FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced an 8-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
 FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
         </is>
       </c>

--- a/banks/CHETWOOD FINANCIALS.xlsx
+++ b/banks/CHETWOOD FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3339,14 +3340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Tier 1 Ratio</t>
+          <t>Chetwood Financial Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -3395,34 +3396,24 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>187605</v>
       </c>
       <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>26.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>29.3%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
+      <c r="D4" s="6" t="n">
+        <v>91268</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>57554</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>50637</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>50697</v>
       </c>
       <c r="H4" s="6" t="n"/>
     </row>
@@ -3433,7 +3424,7 @@
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. Equal to CET1 capital in every year shown - Chetwood has no Additional Tier 1 (AT1) instruments (in FY2020 confirmed by its capital-resources table running CET1 -&gt; Tier 2 -&gt; Total with no AT1 line).
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
@@ -3486,14 +3477,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Total Capital</t>
+          <t>Chetwood Financial Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -3542,24 +3533,34 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>187605</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
       </c>
       <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n">
-        <v>91268</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>57554</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>50637</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>52835</v>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
       </c>
       <c r="H4" s="6" t="n"/>
     </row>
@@ -3570,7 +3571,7 @@
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. Equal to CET1/Tier 1 capital in FY2021-FY2025 - Chetwood had no Tier 2 capital in those years. FY2020 is the exception and the only year that differs: its capital-resources table discloses £2,138k of Tier 2 capital on top of CET1 £50,697k, giving Total regulatory capital £52,835k as printed.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one.
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
@@ -3623,14 +3624,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Total Capital Ratio</t>
+          <t>Chetwood Financial Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -3679,34 +3680,24 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>187605</v>
       </c>
       <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>26.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>29.3%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
+      <c r="D4" s="6" t="n">
+        <v>91268</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>57554</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>50637</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>52835</v>
       </c>
       <c r="H4" s="6" t="n"/>
     </row>
@@ -3717,8 +3708,8 @@
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one.
-FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's 31% is higher than that year's 30% Tier 1 ratio because of the £2,138k of Tier 2 capital described on the Total Capital sheet - both figures are printed in the document's own Summary-analysis table, neither is derived.</t>
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. Equal to CET1/Tier 1 capital in FY2021-FY2025 - Chetwood had no Tier 2 capital in those years. FY2020 is the exception and the only year that differs: its capital-resources table discloses £2,138k of Tier 2 capital on top of CET1 £50,697k, giving Total regulatory capital £52,835k as printed.
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
     </row>
@@ -3770,14 +3761,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Total RWAs</t>
+          <t>Chetwood Financial Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -3826,34 +3817,46 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1233321</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>824623</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>343668</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>196750</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>178987</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>171000</v>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
       </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's £171,000k is the document's own printed 'Risk Weighted Assets (£m) £171.0m' - disclosed to one decimal place of £m only, so the trailing three digits are the unit conversion, not spurious precision. It reconciles exactly to that document's own two components (Credit Risk RWAs £119.4m + operational-risk RWAs £51.6m = £171.0m), shown on the RWA Breakdown sheet.
-FY2024 is populated (unlike the other Pillar 3 sheets) because the FY2025 Pillar 3 document's own OV1 table (Section 6.3) discloses a full FY2024 comparative Total row (824,623) - the same figure the RWA Breakdown sheet's FY2024 column sums to. The KM1 template (Section 5) and LCR/NSFR/Overall Capital Requirement tables (Sections 5-6.6) that supply every other Pillar 3 metric on this workbook are all single-column ('as at 31 March 2025' only, no FY2024 comparative) - confirmed by reading the full FY2025 Pillar 3 document page by page, so CET1/Tier 1/Total Capital/all ratios/Leverage/LCR/NSFR/MREL genuinely remain blank for FY2024.</t>
+          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
+SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
+Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one.
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's 31% is higher than that year's 30% Tier 1 ratio because of the £2,138k of Tier 2 capital described on the Total Capital sheet - both figures are printed in the document's own Summary-analysis table, neither is derived.</t>
         </is>
       </c>
     </row>
@@ -3884,6 +3887,141 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024*</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1233321</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>824623</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>343668</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>196750</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>178987</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>171000</v>
+      </c>
+      <c r="H4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's £171,000k is the document's own printed 'Risk Weighted Assets (£m) £171.0m' - disclosed to one decimal place of £m only, so the trailing three digits are the unit conversion, not spurious precision. It reconciles exactly to that document's own two components (Credit Risk RWAs £119.4m + operational-risk RWAs £51.6m = £171.0m), shown on the RWA Breakdown sheet.
+FY2024 is populated (unlike the other Pillar 3 sheets) because the FY2025 Pillar 3 document's own OV1 table (Section 6.3) discloses a full FY2024 comparative Total row (824,623) - the same figure the RWA Breakdown sheet's FY2024 column sums to. The KM1 template (Section 5) and LCR/NSFR/Overall Capital Requirement tables (Sections 5-6.6) that supply every other Pillar 3 metric on this workbook are all single-column ('as at 31 March 2025' only, no FY2024 comparative) - confirmed by reading the full FY2025 Pillar 3 document page by page, so CET1/Tier 1/Total Capital/all ratios/Leverage/LCR/NSFR/MREL genuinely remain blank for FY2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources (see entity note on Cash Flow Statement sheet):
+FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
+FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
+FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A5:H5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4123,7 +4261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4292,7 +4430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4519,7 +4657,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4706,7 +4844,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9287,6 +9425,1024 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited — KM1 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Chetwood's own published UK key-metrics (KM1) template, reproduced in its row order with its own template row numbers, labels and printed precision. Amounts in £'000s, ratios as printed. Group/consolidated basis. Only the FY2022, FY2023 and FY2025 Pillar 3 editions carry a KM1 table, and each is single-column; FY2024 (no document), FY2021/FY2020 (editions pre-date the template) and FY2019 (no document) are intentionally blank. See source note below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024*</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (amounts, £'000s)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1    Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>187605</v>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n">
+        <v>91268</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>57554</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2    Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>187605</v>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n">
+        <v>91268</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>57554</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3    Total capital</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>187605</v>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n">
+        <v>91268</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>57554</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure amounts (£'000s)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4    Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1233321</v>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n">
+        <v>343668</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>196750</v>
+      </c>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Capital ratios (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>5    Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>6    Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7    Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements based on SREP (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>UK 7a    Additional CET1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.92%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>11.07%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>UK 7b    Additional AT1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>UK 7c    Additional T2 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>UK 7d    Total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>9.92%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>19.07%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>19.1%</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>8    Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>UK 8a    Conservation buffer due to macro-prudential or systemic risk identified at the level of a Member State (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>9    Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>UK 9a    Systemic risk buffer (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>10    Global Systemically Important Institution buffer (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>UK 10a    Other Systemically Important Institution buffer</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>11    Combined buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>UK 11a    Overall capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>14.42%</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>22.57%</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>12    CET1 available after meeting the total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>7.49%</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>20034</v>
+      </c>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio — as captioned in the FY2025 edition (excluding claims on central banks)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>13    Total exposure measure excluding claims on central banks</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>3615720</v>
+      </c>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>14    Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio — as captioned in the FY2022 and FY2023 editions (basis not stated)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>13    Leverage ratio total exposure measure</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n">
+        <v>1519817</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>394658</v>
+      </c>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>14    Leverage ratio</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>6.01%</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>14.58%</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements to address risks of excessive leverage (as a percentage of leverage ratio total exposure amount)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>UK 14a    Additional CET1 leverage ratio requirements (%)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>UK 14b    Additional AT1 leverage ratio requirements (%)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>UK 14c    Additional T2 leverage ratio requirements (%)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>UK 14d    Total SREP leverage ratio requirements (%)</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>UK 14e    Applicable leverage buffer</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>UK 14f    Overall leverage ratio requirements (%)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio (£'000s / %)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>15    Total high-quality liquid assets (HQLA) (Weighted value -average)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>897493</v>
+      </c>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n">
+        <v>302266</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>67841</v>
+      </c>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>UK 16a    Cash outflows - Total weighted value</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>489794</v>
+      </c>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n">
+        <v>52035</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>5627</v>
+      </c>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>UK 16b    Cash inflows - Total weighted value</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>28009</v>
+      </c>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n">
+        <v>15169</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>13656</v>
+      </c>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>16    Total net cash outflows (adjusted value)</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>461785</v>
+      </c>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n">
+        <v>36865</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>1407</v>
+      </c>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>17    Liquidity coverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>194%</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>1,015%</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>4,823%</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (£'000s / %)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>18    Total available stable funding</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>3677559</v>
+      </c>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n">
+        <v>1387511</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>380549</v>
+      </c>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>19    Total required stable funding</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>2536343</v>
+      </c>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n">
+        <v>572002</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>233566</v>
+      </c>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>20    NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>145%</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>243%</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>162.9%</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+    </row>
+    <row r="53" ht="460" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Chetwood's own UK KM1 key-metrics template, reproduced as printed. Each column is transcribed from the edition in which that year is the reporting year; every one of these editions is SINGLE-COLUMN (header block 'a  £'000s' over one year only), so no figure here is a later edition's comparative.
+FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 'Key Metrics', pp.9-10 of 15 - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31st March 2023, Section 6 'Key Metrics', p.17 (PDF p.18 of 34) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31st March 2022, 'Annex B: Key Metrics - KM1', pp.35-36 (PDF pp.36-37 of 41) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2024, FY2021, FY2020 and FY2019 are blank, for three different reasons, none of which is a failed search:
+• FY2024 - no Pillar 3 document 'as at 31 March 2024' exists (re-verified four ways 2026-09-15, see the FY2024 note on any metric sheet), and the FY2025 edition's KM1 has no comparative column to borrow from.
+• FY2021 and FY2020 - both editions pre-date the template. The FY2021 document was re-read in full for this sheet: 'key metric', 'KM1', 'combined buffer' and 'risk weighted exposure' appear nowhere in it, and its only capital table is a narrative 'Total CET1 Capital' build-up. The FY2020 edition is the same shape. The FY2020/FY2021 figures on the single-metric sheets come from those narrative tables and are deliberately NOT re-assembled into KM1 rows here.
+• FY2019 - Chetwood published no Pillar 3 disclosure at all that year.
+PRESENTATION NOTES:
+• ROW SET DRIFT: rows UK 8a, UK 9a, 10, UK 10a and UK 14a-UK 14f are printed by the FY2022 edition only; the FY2023 and FY2025 editions omit them from the table entirely. The union is shown, in the template's canonical order, so the sheet matches the table a reader of the FY2022 report would recognise.
+• DASH vs ZERO: the FY2022 edition uses both glyphs and means different things by them. It prints '-' at rows UK 7b, UK 7c and UK 14a-UK 14e (left BLANK here - the requirement does not apply) and '0%' at rows UK 8a, 9, UK 9a, 10, UK 10a, 11 and UK 14f (kept as a measured zero). The FY2023 and FY2025 editions print '-' at UK 7b/UK 7c only.
+• SOURCE DEFECT, row 11 (FY2022): the FY2022 edition prints Combined buffer requirement as '0%' even though row 8 immediately above prints a 2.50% capital conservation buffer, so the combined buffer cannot be nil. Reproduced as published and flagged here; the FY2023 (3.50%) and FY2025 (4.50%) editions are internally consistent.
+• SOURCE DEFECT, row 12 (FY2022): captioned 'CET1 available after meeting the total SREP own funds requirements (%)' but printed as 20,034 - a £'000 amount, not a percentage. Reproduced as printed.
+• LEVERAGE CAPTION CHANGE: the FY2022 and FY2023 editions caption rows 13/14 'Leverage ratio total exposure measure' / 'Leverage ratio' with no basis stated; the FY2025 edition captions the same rows 'Total exposure measure excluding claims on central banks' / 'Leverage ratio excluding claims on central banks (%)'. Shown as two separately-captioned blocks rather than merged. All three reporting dates fall after the 1 January 2022 UK change that excluded claims on central banks from the exposure measure, so the underlying basis is very likely unchanged and only the caption moved - but no Chetwood edition says so, and this sheet reproduces rather than infers. The Leverage Ratio metric sheet carries the same four figures as one series, with its own note.
+• PRECISION: the FY2022 edition prints ratios to one decimal place ('29.3%', '11.1%', '2.5%'); the FY2023 and FY2025 editions print two ('11.07%', '2.50%', '1.92%'), while still printing row 9 as '1%' in FY2023 and rows 17/20 as whole percents in FY2025. Each cell keeps the precision of its own edition.
+• Row 15 is a weighted 12-month average (the caption says so); rows 17 and 20 are as printed, including the FY2023 thousands separator in '1,015%'.
+LATEST-EDITION CHECK, 2026-09-16: chetwoodbank.co.uk publishes its documents at undated, overwritten URLs (/documents/chetwood-bank-pillar-three-disclosures.pdf and /documents/chetwood-bank-annual-report.pdf, both linked from /about-us). Both were downloaded fresh on that date: the Pillar 3 file is still the 'September 2025' edition with a single 2025 column, and the Annual Report file is still 'year ended 31 March 2025'. No FY2026 edition of either had been published. Checked, none newer.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A53:H53"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9418,7 +10574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9590,141 +10746,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Chetwood Financial Limited — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024*</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021†</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020†‡</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>187605</v>
-      </c>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n">
-        <v>91268</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>57554</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>50637</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>50697</v>
-      </c>
-      <c r="H4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
-FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
-SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
-Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. Equal to CET1 capital in every year shown - Chetwood has no Additional Tier 1 (AT1) instruments (in FY2020 confirmed by its capital-resources table running CET1 -&gt; Tier 2 -&gt; Total with no AT1 line).
-FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources (see entity note on Cash Flow Statement sheet):
-FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
-FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A5:H5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/banks/CHETWOOD FINANCIALS.xlsx
+++ b/banks/CHETWOOD FINANCIALS.xlsx
@@ -1742,6 +1742,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3324,7 +3325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3334,7 +3335,6 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3387,11 +3387,6 @@
           <t>FY2020†‡</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3402,7 +3397,11 @@
       <c r="B4" s="6" t="n">
         <v>187605</v>
       </c>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no Pillar 3 disclosure for this year</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="n">
         <v>91268</v>
       </c>
@@ -3415,7 +3414,6 @@
       <c r="G4" s="6" t="n">
         <v>50697</v>
       </c>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -3448,8 +3446,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3461,7 +3459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3471,7 +3469,6 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3524,11 +3521,6 @@
           <t>FY2020†‡</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3541,7 +3533,11 @@
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no Pillar 3 disclosure for this year</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>26.6%</t>
@@ -3562,7 +3558,6 @@
           <t>30%</t>
         </is>
       </c>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -3595,8 +3590,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3608,7 +3603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3618,7 +3613,6 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3671,11 +3665,6 @@
           <t>FY2020†‡</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3686,7 +3675,11 @@
       <c r="B4" s="6" t="n">
         <v>187605</v>
       </c>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no Pillar 3 disclosure for this year</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="n">
         <v>91268</v>
       </c>
@@ -3699,7 +3692,6 @@
       <c r="G4" s="6" t="n">
         <v>52835</v>
       </c>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -3732,8 +3724,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3745,7 +3737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3755,7 +3747,6 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3808,11 +3799,6 @@
           <t>FY2020†‡</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3825,7 +3811,11 @@
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no Pillar 3 disclosure for this year</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>26.6%</t>
@@ -3846,7 +3836,6 @@
           <t>31%</t>
         </is>
       </c>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -3879,8 +3868,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3892,7 +3881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3902,7 +3891,6 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3955,11 +3943,6 @@
           <t>FY2020†‡</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3985,7 +3968,6 @@
       <c r="G4" s="6" t="n">
         <v>171000</v>
       </c>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -4014,8 +3996,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4027,7 +4009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4037,7 +4019,6 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4090,16 +4071,11 @@
           <t>FY2020†‡ (£'000)</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡ (£'000)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>RWA by risk category</t>
+          <t>OV1 'Overview of RWAs' template — Chetwood's own Pillar 3 Disclosures, Section 6.3 (FY2025, with the FY2024 comparative column) and Section 8.3 (FY2023, with the FY2022 comparative column)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -4108,7 +4084,6 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4128,13 +4103,8 @@
       <c r="E5" s="6" t="n">
         <v>179962</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>126942</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>119400</v>
-      </c>
-      <c r="H5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4154,11 +4124,8 @@
       <c r="E6" s="6" t="n">
         <v>1937</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>450</v>
-      </c>
+      <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4178,7 +4145,6 @@
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4198,13 +4164,8 @@
       <c r="E8" s="6" t="n">
         <v>14852</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>51595</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>51600</v>
-      </c>
-      <c r="H8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -4224,16 +4185,142 @@
       <c r="E9" s="5" t="n">
         <v>196750</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Pre-KM1 equivalent category table — Pillar 3 Disclosure as at 31 March 2021 (FY2021). This edition predates Chetwood's use of the OV1 template and carries no securitisation line</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (excluding CCR)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n">
+        <v>126942</v>
+      </c>
+      <c r="G11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (CCR)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="G12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
+        <v>51595</v>
+      </c>
+      <c r="G13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n">
         <v>178987</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>No OV1 or category table published (FY2020) — figures taken from narrative sections of the Pillar 3 Disclosures of June 2020: Section 1.2 'Credit Risk Weighted Assets' (p.3) and Section 8 (operational risk, p.19), stated to 0.1 of £m only</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (excluding CCR)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n">
+        <v>119400</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n">
+        <v>51600</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n">
         <v>171000</v>
       </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="11" ht="220" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    </row>
+    <row r="20" ht="220" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Sources - Chetwood's own Pillar 3 Disclosures, Section 6 'Overview of RWAs' (OV1 template from FY2022 onward; FY2021 uses an equivalent pre-KM1 category table).
 FY2025/FY2024: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 6.3, which unlike the standalone FY2024 KM1 gap noted on the other Pillar 3 sheets, discloses its OV1 table's FY2024 comparative RWEA column in full - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
@@ -4255,7 +4342,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A20:G20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4267,7 +4354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4277,7 +4364,6 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4330,11 +4416,6 @@
           <t>FY2020†‡</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4356,7 +4437,6 @@
         <v>216375</v>
       </c>
       <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4369,7 +4449,11 @@
           <t>5.19%</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no Pillar 3 disclosure for this year</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>6.01%</t>
@@ -4390,7 +4474,6 @@
           <t>19%</t>
         </is>
       </c>
-      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -4423,8 +4506,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4436,7 +4519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4446,7 +4529,6 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4499,11 +4581,6 @@
           <t>FY2020†‡</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4523,7 +4600,6 @@
       </c>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4543,7 +4619,6 @@
       </c>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4563,7 +4638,6 @@
       </c>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4583,7 +4657,6 @@
       </c>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4596,7 +4669,11 @@
           <t>194%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no Pillar 3 disclosure for this year</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>1,015%</t>
@@ -4617,7 +4694,6 @@
           <t>68,110%</t>
         </is>
       </c>
-      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -4650,8 +4726,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4663,7 +4739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4673,7 +4749,6 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4726,11 +4801,6 @@
           <t>FY2020†‡</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4750,7 +4820,6 @@
       </c>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4770,7 +4839,6 @@
       </c>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4783,7 +4851,11 @@
           <t>145%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no Pillar 3 disclosure for this year</t>
+        </is>
+      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>243%</t>
@@ -4804,7 +4876,6 @@
           <t>193%</t>
         </is>
       </c>
-      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -4837,8 +4908,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4850,7 +4921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4859,8 +4930,6 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4904,16 +4973,6 @@
           <t>FY2021†</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020†‡</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4946,8 +5005,6 @@
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -4975,8 +5032,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9425,7 +9482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -9433,9 +9490,6 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9478,60 +9532,37 @@
           <t>FY2022</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021†</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020†‡</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Available own funds (amounts, £'000s)</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>[No UK KM1 published for this year - see note below]</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no Pillar 3 disclosure for this year</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>1    Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>187605</v>
-      </c>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (amounts, £'000s)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n">
-        <v>91268</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>57554</v>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2    Tier 1 capital</t>
+          <t>1    Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
@@ -9544,14 +9575,11 @@
       <c r="E6" s="6" t="n">
         <v>57554</v>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>3    Total capital</t>
+          <t>2    Tier 1 capital</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
@@ -9564,88 +9592,67 @@
       <c r="E7" s="6" t="n">
         <v>57554</v>
       </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>3    Total capital</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>187605</v>
+      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n">
+        <v>91268</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>57554</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Risk-weighted exposure amounts (£'000s)</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>4    Total risk-weighted exposure amount</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B10" s="6" t="n">
         <v>1233321</v>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n">
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n">
         <v>343668</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E10" s="6" t="n">
         <v>196750</v>
       </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Capital ratios (as a percentage of risk-weighted exposure amount)</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>5    Common Equity Tier 1 ratio (%)</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
+      <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>26.6%</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>29.3%</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>6    Tier 1 ratio (%)</t>
+          <t>5    Common Equity Tier 1 ratio (%)</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -9664,14 +9671,11 @@
           <t>29.3%</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>7    Total capital ratio (%)</t>
+          <t>6    Tier 1 ratio (%)</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -9690,210 +9694,209 @@
           <t>29.3%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>7    Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Additional own funds requirements based on SREP (as a percentage of risk-weighted exposure amount)</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>UK 7a    Additional CET1 SREP requirements (%)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>1.92%</t>
-        </is>
-      </c>
+      <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>11.07%</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>UK 7b    Additional AT1 SREP requirements (%)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
+          <t>UK 7a    Additional CET1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>1.92%</t>
+        </is>
+      </c>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>11.07%</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>UK 7c    Additional T2 SREP requirements (%)</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
+          <t>UK 7b    Additional AT1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>UK 7d    Total SREP own funds requirements (%)</t>
+          <t>UK 7c    Additional T2 SREP requirements (%)</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>9.92%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>UK 7d    Total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>9.92%</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
           <t>19.07%</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>19.1%</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Combined buffer requirement (as a percentage of risk-weighted exposure amount)</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>8    Capital conservation buffer (%)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
+      <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>UK 8a    Conservation buffer due to macro-prudential or systemic risk identified at the level of a Member State (%)</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
+          <t>8    Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
       <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+          <t>2.5%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>9    Institution specific countercyclical capital buffer (%)</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>2.00%</t>
-        </is>
-      </c>
+          <t>UK 8a    Conservation buffer due to macro-prudential or systemic risk identified at the level of a Member State (%)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
+      <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>UK 9a    Systemic risk buffer (%)</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
+          <t>9    Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
       <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>10    Global Systemically Important Institution buffer (%)</t>
+          <t>UK 9a    Systemic risk buffer (%)</t>
         </is>
       </c>
       <c r="B24" s="6" t="n"/>
@@ -9904,14 +9907,11 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>UK 10a    Other Systemically Important Institution buffer</t>
+          <t>10    Global Systemically Important Institution buffer (%)</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
@@ -9922,276 +9922,248 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>11    Combined buffer requirement (%)</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>4.50%</t>
-        </is>
-      </c>
+          <t>UK 10a    Other Systemically Important Institution buffer</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
       <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>3.50%</t>
-        </is>
-      </c>
+      <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>UK 11a    Overall capital requirements (%)</t>
+          <t>11    Combined buffer requirement (%)</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>14.42%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>22.57%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>21.6%</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>12    CET1 available after meeting the total SREP own funds requirements (%)</t>
+          <t>UK 11a    Overall capital requirements (%)</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>14.42%</t>
         </is>
       </c>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="6" t="inlineStr">
         <is>
+          <t>22.57%</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>12    CET1 available after meeting the total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
           <t>7.49%</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E29" s="6" t="n">
         <v>20034</v>
       </c>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Leverage ratio — as captioned in the FY2025 edition (excluding claims on central banks)</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>13    Total exposure measure excluding claims on central banks</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>3615720</v>
-      </c>
+      <c r="B30" s="6" t="n"/>
       <c r="C30" s="6" t="n"/>
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>14    Leverage ratio excluding claims on central banks (%)</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
+          <t>13    Total exposure measure excluding claims on central banks</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>3615720</v>
       </c>
       <c r="C31" s="6" t="n"/>
       <c r="D31" s="6" t="n"/>
       <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Leverage ratio — as captioned in the FY2022 and FY2023 editions (basis not stated)</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n"/>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>14    Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6" t="n"/>
       <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>13    Leverage ratio total exposure measure</t>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio — as captioned in the FY2022 and FY2023 editions (basis not stated)</t>
         </is>
       </c>
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n">
-        <v>1519817</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>394658</v>
-      </c>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>14    Leverage ratio</t>
+          <t>13    Leverage ratio total exposure measure</t>
         </is>
       </c>
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>6.01%</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>14.58%</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="6" t="n"/>
-      <c r="H34" s="6" t="n"/>
+      <c r="D34" s="6" t="n">
+        <v>1519817</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>394658</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Additional own funds requirements to address risks of excessive leverage (as a percentage of leverage ratio total exposure amount)</t>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>14    Leverage ratio</t>
         </is>
       </c>
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>6.01%</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>14.58%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>UK 14a    Additional CET1 leverage ratio requirements (%)</t>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements to address risks of excessive leverage (as a percentage of leverage ratio total exposure amount)</t>
         </is>
       </c>
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="6" t="n"/>
       <c r="D36" s="6" t="n"/>
       <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
-      <c r="G36" s="6" t="n"/>
-      <c r="H36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>UK 14b    Additional AT1 leverage ratio requirements (%)</t>
+          <t>UK 14a    Additional CET1 leverage ratio requirements (%)</t>
         </is>
       </c>
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>UK 14c    Additional T2 leverage ratio requirements (%)</t>
+          <t>UK 14b    Additional AT1 leverage ratio requirements (%)</t>
         </is>
       </c>
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="6" t="n"/>
       <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>UK 14d    Total SREP leverage ratio requirements (%)</t>
+          <t>UK 14c    Additional T2 leverage ratio requirements (%)</t>
         </is>
       </c>
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="6" t="n"/>
       <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n"/>
-      <c r="G39" s="6" t="n"/>
-      <c r="H39" s="6" t="n"/>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>UK 14e    Applicable leverage buffer</t>
+          <t>UK 14d    Total SREP leverage ratio requirements (%)</t>
         </is>
       </c>
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
-      <c r="G40" s="6" t="n"/>
-      <c r="H40" s="6" t="n"/>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>UK 14f    Overall leverage ratio requirements (%)</t>
+          <t>UK 14e    Applicable leverage buffer</t>
         </is>
       </c>
       <c r="B41" s="6" t="n"/>
@@ -10199,215 +10171,197 @@
       <c r="D41" s="6" t="n"/>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n"/>
-      <c r="G41" s="6" t="n"/>
-      <c r="H41" s="6" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Liquidity Coverage Ratio (£'000s / %)</t>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>UK 14f    Overall leverage ratio requirements (%)</t>
         </is>
       </c>
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="6" t="n"/>
       <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="n"/>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>15    Total high-quality liquid assets (HQLA) (Weighted value -average)</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n">
-        <v>897493</v>
-      </c>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio (£'000s / %)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
       <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n">
-        <v>302266</v>
-      </c>
-      <c r="E43" s="6" t="n">
-        <v>67841</v>
-      </c>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>UK 16a    Cash outflows - Total weighted value</t>
+          <t>15    Total high-quality liquid assets (HQLA) (Weighted value -average)</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>489794</v>
+        <v>897493</v>
       </c>
       <c r="C44" s="6" t="n"/>
       <c r="D44" s="6" t="n">
-        <v>52035</v>
+        <v>302266</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>5627</v>
-      </c>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="6" t="n"/>
+        <v>67841</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>UK 16b    Cash inflows - Total weighted value</t>
+          <t>UK 16a    Cash outflows - Total weighted value</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>28009</v>
+        <v>489794</v>
       </c>
       <c r="C45" s="6" t="n"/>
       <c r="D45" s="6" t="n">
-        <v>15169</v>
+        <v>52035</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>13656</v>
-      </c>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="6" t="n"/>
-      <c r="H45" s="6" t="n"/>
+        <v>5627</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>16    Total net cash outflows (adjusted value)</t>
+          <t>UK 16b    Cash inflows - Total weighted value</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>461785</v>
+        <v>28009</v>
       </c>
       <c r="C46" s="6" t="n"/>
       <c r="D46" s="6" t="n">
-        <v>36865</v>
+        <v>15169</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>1407</v>
-      </c>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
+        <v>13656</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
+          <t>16    Total net cash outflows (adjusted value)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>461785</v>
+      </c>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n">
+        <v>36865</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
           <t>17    Liquidity coverage ratio (%)</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>194%</t>
         </is>
       </c>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>1,015%</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>4,823%</t>
         </is>
       </c>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="6" t="n"/>
-      <c r="H47" s="6" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Net Stable Funding Ratio (£'000s / %)</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="6" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>18    Total available stable funding</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>3677559</v>
-      </c>
+      <c r="B49" s="6" t="n"/>
       <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n">
-        <v>1387511</v>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>380549</v>
-      </c>
-      <c r="F49" s="6" t="n"/>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>19    Total required stable funding</t>
+          <t>18    Total available stable funding</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>2536343</v>
+        <v>3677559</v>
       </c>
       <c r="C50" s="6" t="n"/>
       <c r="D50" s="6" t="n">
-        <v>572002</v>
+        <v>1387511</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>233566</v>
-      </c>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
+        <v>380549</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
+          <t>19    Total required stable funding</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>2536343</v>
+      </c>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n">
+        <v>572002</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>233566</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>20    NSFR ratio (%)</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>145%</t>
         </is>
       </c>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>243%</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>162.9%</t>
         </is>
       </c>
-      <c r="F51" s="6" t="n"/>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
-    </row>
-    <row r="53" ht="460" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
+    </row>
+    <row r="54" ht="460" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>Sources - Chetwood's own UK KM1 key-metrics template, reproduced as printed. Each column is transcribed from the edition in which that year is the reporting year; every one of these editions is SINGLE-COLUMN (header block 'a  £'000s' over one year only), so no figure here is a later edition's comparative.
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 'Key Metrics', pp.9-10 of 15 - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
@@ -10419,7 +10373,7 @@
 • FY2019 - Chetwood published no Pillar 3 disclosure at all that year.
 PRESENTATION NOTES:
 • ROW SET DRIFT: rows UK 8a, UK 9a, 10, UK 10a and UK 14a-UK 14f are printed by the FY2022 edition only; the FY2023 and FY2025 editions omit them from the table entirely. The union is shown, in the template's canonical order, so the sheet matches the table a reader of the FY2022 report would recognise.
-• DASH vs ZERO: the FY2022 edition uses both glyphs and means different things by them. It prints '-' at rows UK 7b, UK 7c and UK 14a-UK 14e (left BLANK here - the requirement does not apply) and '0%' at rows UK 8a, 9, UK 9a, 10, UK 10a, 11 and UK 14f (kept as a measured zero). The FY2023 and FY2025 editions print '-' at UK 7b/UK 7c only.
+• DASH vs ZERO, AND THIS SHEET NOW SHOWS THE DIFFERENCE. The FY2022 edition uses both glyphs in ONE table and means different things by them. It prints '-' at rows UK 7b, UK 7c and UK 14a-UK 14e - those cells carry a literal dash, because the requirement does not apply to Chetwood - and it prints '0%' at rows UK 8a, 9, UK 9a, 10, UK 10a, 11 and UK 14f, which are kept as the measured zeros the Bank published. The FY2023 and FY2025 editions print '-' at UK 7b/UK 7c only, and those carry dashes too; all three editions were re-read at source on 2026-09-18. Chetwood is the clearest demonstration in this corpus of why the two glyphs must not be flattened together: a single table, printed by a single bank on a single date, deliberately using a dash for 'does not apply' and a zero for 'measured at nil'. Anything that rendered both as the same thing would be discarding a distinction Chetwood took care to draw. Rows UK 14a-UK 14e are blank for FY2023 and FY2025 because those editions omit the block entirely - a third state again, and not the same as either.
 • SOURCE DEFECT, row 11 (FY2022): the FY2022 edition prints Combined buffer requirement as '0%' even though row 8 immediately above prints a 2.50% capital conservation buffer, so the combined buffer cannot be nil. Reproduced as published and flagged here; the FY2023 (3.50%) and FY2025 (4.50%) editions are internally consistent.
 • SOURCE DEFECT, row 12 (FY2022): captioned 'CET1 available after meeting the total SREP own funds requirements (%)' but printed as 20,034 - a £'000 amount, not a percentage. Reproduced as printed.
 • LEVERAGE CAPTION CHANGE: the FY2022 and FY2023 editions caption rows 13/14 'Leverage ratio total exposure measure' / 'Leverage ratio' with no basis stated; the FY2025 edition captions the same rows 'Total exposure measure excluding claims on central banks' / 'Leverage ratio excluding claims on central banks (%)'. Shown as two separately-captioned blocks rather than merged. All three reporting dates fall after the 1 January 2022 UK change that excluded claims on central banks from the exposure measure, so the underlying basis is very likely unchanged and only the caption moved - but no Chetwood edition says so, and this sheet reproduces rather than infers. The Leverage Ratio metric sheet carries the same four figures as one series, with its own note.
@@ -10431,7 +10385,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A54:E54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10443,7 +10397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -10453,7 +10407,6 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10506,11 +10459,6 @@
           <t>FY2020†‡</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -10521,7 +10469,11 @@
       <c r="B4" s="6" t="n">
         <v>187605</v>
       </c>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no Pillar 3 disclosure for this year</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="n">
         <v>91268</v>
       </c>
@@ -10534,7 +10486,6 @@
       <c r="G4" s="6" t="n">
         <v>50697</v>
       </c>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -10567,8 +10518,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10580,7 +10531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -10590,7 +10541,6 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10643,11 +10593,6 @@
           <t>FY2020†‡</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -10681,7 +10626,6 @@
           <t>30%</t>
         </is>
       </c>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -10707,7 +10651,6 @@
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -10741,8 +10684,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/CHETWOOD FINANCIALS.xlsx
+++ b/banks/CHETWOOD FINANCIALS.xlsx
@@ -1763,7 +1763,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -1932,6 +1932,9 @@
       <c r="BD6" t="n">
         <v>26.6</v>
       </c>
+      <c r="BE6" t="n">
+        <v>20.8</v>
+      </c>
       <c r="BF6" t="n">
         <v>15.2</v>
       </c>
@@ -2006,6 +2009,9 @@
       <c r="BD7" t="n">
         <v>26.6</v>
       </c>
+      <c r="BE7" t="n">
+        <v>20.8</v>
+      </c>
       <c r="BF7" t="n">
         <v>15.2</v>
       </c>
@@ -2080,6 +2086,9 @@
       <c r="BD8" t="n">
         <v>26.6</v>
       </c>
+      <c r="BE8" t="n">
+        <v>20.8</v>
+      </c>
       <c r="BF8" t="n">
         <v>15.2</v>
       </c>
@@ -2154,6 +2163,9 @@
       <c r="BD9" t="n">
         <v>6.01</v>
       </c>
+      <c r="BE9" t="n">
+        <v>7.19</v>
+      </c>
       <c r="BF9" t="n">
         <v>5.19</v>
       </c>
@@ -2176,6 +2188,9 @@
       <c r="BD10" t="n">
         <v>1015</v>
       </c>
+      <c r="BE10" t="n">
+        <v>184</v>
+      </c>
       <c r="BF10" t="n">
         <v>194</v>
       </c>
@@ -2203,6 +2218,9 @@
       <c r="BD11" t="n">
         <v>243</v>
       </c>
+      <c r="BE11" t="n">
+        <v>163</v>
+      </c>
       <c r="BF11" t="n">
         <v>145</v>
       </c>
@@ -2220,7 +2238,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -2275,7 +2293,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2466,7 +2484,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2521,7 +2539,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -2766,7 +2784,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2821,7 +2839,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -3066,7 +3084,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -3106,7 +3124,11 @@
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n"/>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
           <t>26.6%</t>
@@ -3140,7 +3162,11 @@
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n"/>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
           <t>26.6%</t>
@@ -3174,7 +3200,11 @@
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n"/>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
           <t>26.6%</t>
@@ -3208,7 +3238,11 @@
           <t>5.19%</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n"/>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>7.19%</t>
+        </is>
+      </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
           <t>6.01%</t>
@@ -3242,7 +3276,11 @@
           <t>194%</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n"/>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>184%</t>
+        </is>
+      </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
           <t>1,015%</t>
@@ -3276,7 +3314,11 @@
           <t>145%</t>
         </is>
       </c>
-      <c r="C38" s="6" t="n"/>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>163%</t>
+        </is>
+      </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
           <t>243%</t>
@@ -3302,11 +3344,11 @@
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Ratios are blank for FY2019 (Chetwood published no Pillar 3 disclosure that year); FY2020 was blank on the same basis until 2026-09-15, when its own 'as at 31 March 2020' Pillar 3 document was located - see any Pillar 3 sheet's source note for that correction. Note the ~£8.1m FY2020-closing/FY2021-opening equity gap explained on the Statement of Changes in Equity sheet (FRS 102-to-IFRS transition). FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Ratios are blank for FY2019 (Chetwood published no Pillar 3 disclosure that year); FY2020 was blank on the same basis until 2026-09-15, when its own 'as at 31 March 2020' Pillar 3 document was located - see any Pillar 3 sheet's source note for that correction. Note the ~£8.1m FY2020-closing/FY2021-opening equity gap explained on the Statement of Changes in Equity sheet (FRS 102-to-IFRS transition). FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one.</t>
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.)</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3406,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -3397,10 +3439,8 @@
       <c r="B4" s="6" t="n">
         <v>187605</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published - no Pillar 3 disclosure for this year</t>
-        </is>
+      <c r="C4" s="6" t="n">
+        <v>171791</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>91268</v>
@@ -3418,11 +3458,11 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+          <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. Equal to CET1 capital in every year shown - Chetwood has no Additional Tier 1 (AT1) instruments (in FY2020 confirmed by its capital-resources table running CET1 -&gt; Tier 2 -&gt; Total with no AT1 line).
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.) Equal to CET1 capital in every year shown - Chetwood has no Additional Tier 1 (AT1) instruments (in FY2020 confirmed by its capital-resources table running CET1 -&gt; Tier 2 -&gt; Total with no AT1 line).
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
@@ -3432,8 +3472,9 @@
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
 OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
@@ -3498,7 +3539,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -3535,7 +3576,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not published - no Pillar 3 disclosure for this year</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -3562,11 +3603,11 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+          <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.)
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
@@ -3576,8 +3617,9 @@
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
 OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
@@ -3642,7 +3684,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -3675,10 +3717,8 @@
       <c r="B4" s="6" t="n">
         <v>187605</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published - no Pillar 3 disclosure for this year</t>
-        </is>
+      <c r="C4" s="6" t="n">
+        <v>171791</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>91268</v>
@@ -3696,11 +3736,11 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+          <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. Equal to CET1/Tier 1 capital in FY2021-FY2025 - Chetwood had no Tier 2 capital in those years. FY2020 is the exception and the only year that differs: its capital-resources table discloses £2,138k of Tier 2 capital on top of CET1 £50,697k, giving Total regulatory capital £52,835k as printed.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.) Equal to CET1/Tier 1 capital in FY2021-FY2025 - Chetwood had no Tier 2 capital in those years. FY2020 is the exception and the only year that differs: its capital-resources table discloses £2,138k of Tier 2 capital on top of CET1 £50,697k, giving Total regulatory capital £52,835k as printed.
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
@@ -3710,8 +3750,9 @@
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
 OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
@@ -3776,7 +3817,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -3813,7 +3854,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not published - no Pillar 3 disclosure for this year</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -3840,11 +3881,11 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+          <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.)
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's 31% is higher than that year's 30% Tier 1 ratio because of the £2,138k of Tier 2 capital described on the Total Capital sheet - both figures are printed in the document's own Summary-analysis table, neither is derived.</t>
         </is>
       </c>
@@ -3854,8 +3895,9 @@
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
 OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
@@ -3920,7 +3962,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -3973,7 +4015,7 @@
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's £171,000k is the document's own printed 'Risk Weighted Assets (£m) £171.0m' - disclosed to one decimal place of £m only, so the trailing three digits are the unit conversion, not spurious precision. It reconciles exactly to that document's own two components (Credit Risk RWAs £119.4m + operational-risk RWAs £51.6m = £171.0m), shown on the RWA Breakdown sheet.
-FY2024 is populated (unlike the other Pillar 3 sheets) because the FY2025 Pillar 3 document's own OV1 table (Section 6.3) discloses a full FY2024 comparative Total row (824,623) - the same figure the RWA Breakdown sheet's FY2024 column sums to. The KM1 template (Section 5) and LCR/NSFR/Overall Capital Requirement tables (Sections 5-6.6) that supply every other Pillar 3 metric on this workbook are all single-column ('as at 31 March 2025' only, no FY2024 comparative) - confirmed by reading the full FY2025 Pillar 3 document page by page, so CET1/Tier 1/Total Capital/all ratios/Leverage/LCR/NSFR/MREL genuinely remain blank for FY2024.</t>
+FY2024's 824,623 is printed in the FY2024 edition's own KM1 row 4 (p.10) and OV1 total (p.12), and identically as the FY2025 edition's OV1 2024 comparative.</t>
         </is>
       </c>
     </row>
@@ -3982,8 +4024,9 @@
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
 OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
@@ -4048,7 +4091,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024* (£'000)</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -4075,7 +4118,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>OV1 'Overview of RWAs' template — Chetwood's own Pillar 3 Disclosures, Section 6.3 (FY2025, with the FY2024 comparative column) and Section 8.3 (FY2023, with the FY2022 comparative column)</t>
+          <t>OV1 'Overview of RWAs' template — Chetwood's own Pillar 3 Disclosures, Section 6.3 (FY2025; FY2024 from its own November 2024 edition, identical to the FY2025 comparative) and Section 8.3 (FY2023, with the FY2022 comparative column)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -4323,19 +4366,21 @@
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Sources - Chetwood's own Pillar 3 Disclosures, Section 6 'Overview of RWAs' (OV1 template from FY2022 onward; FY2021 uses an equivalent pre-KM1 category table).
-FY2025/FY2024: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 6.3, which unlike the standalone FY2024 KM1 gap noted on the other Pillar 3 sheets, discloses its OV1 table's FY2024 comparative RWEA column in full - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
+FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 6.3 OV1, p.11 - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 6.3 OV1, p.12, '2024' column - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf. Every FY2024 figure is identical to the FY2025 edition's 2024 comparative, from which this column was first filled.
 FY2023/FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 8.3 (OV1 table with FY2022 comparative) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 5.4 (pre-KM1 category table) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf
 FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 (as at 31st March 2020), Section 1.2 ('Credit Risk Weighted Assets', p.3) and Section 8 (Operational risk, p.19) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf. This edition has no OV1 or category table at all; it states only Credit Risk RWAs of £119.4m (itself split in the narrative into £112.1m customer lending + £5.5m other assets + £1.8m lending to banks) and an operational-risk RWA requirement of £51.6m, which together make its printed £171.0m total exactly. Counterparty credit risk and securitisation are left blank rather than assumed nil - the document never mentions either, and Chetwood had no securitised exposures that early.
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
-FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+FY2024 is consolidated. Its Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024) was long believed unpublished and was located on 2026-09-19 on the bank's CMS file host (cdn.sanity.io) - see the note on each Pillar 3 sheet.
 HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
 - Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
 - FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
 - FY2019 (year ended 31 Mar 2019): the PRA's restrictions on the banking licence were lifted 13 Dec 2018; this is the first year with real customer deposits (£26.1m) and a meaningful loan book (£46.3m) - i.e. the first genuine full year of Chetwood operating as an unrestricted retail bank. Treated as the floor.
 - FY2019 and FY2020 statutory accounts (like FY2018's) were prepared under UK GAAP FRS 102, NOT IFRS - Chetwood only adopted IFRS (and IFRS 9 stage-based credit-quality disclosure, and Pillar 3 reporting) from FY2021 onward, per its own accounting-policy notes ('in compliance with...FRS 102') each year 2018-2020. This is analogous to the ticket's flagged Basel II/CET1 terminology shift, but for the whole accounting framework: FY2019-FY2020 (marked ‡) have no IFRS 9 loan-stage table. SUPERSEDED IN PART (2026-09-15): this note previously also claimed FY2019 and FY2020 had 'no Pillar 3 disclosure at all' and that all 11 Pillar 3 metric sheets plus the RWA Breakdown sheet were genuinely not disclosed for both years. That holds for FY2019 only. A 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' document was located 2026-09-15 and FY2020 is now populated across the Pillar 3 sheets - see the source note on any Pillar 3 sheet for the document and the correction. The accounting-framework point itself is unaffected: FY2019 and FY2020 statutory accounts remain FRS 102, and that FY2020 Pillar 3 document says so itself ('Chetwood currently prepares its Financial Statements under FRS 102. Chetwood has developed an IFRS9 expected loss model that will be adopted in due course').
 - A further consequence of the FRS 102-to-IFRS transition: the FY2021 Annual Report's own FY2020 comparative equity balance (used as the prior-year opening figure in that report) does not exactly match FY2020's own originally-filed Statement of Changes in Equity (originally-filed closing Profit and Loss account -£36,357k, Total Equity £51,182k, vs the FY2021 AR's stated FY2020-closing comparative of -£44,513k / £43,067k, a ~£8.1m gap most likely reflecting transition adjustments on first-time IFRS application). The Statement of Changes in Equity sheet below uses Chetwood's own FY2019/FY2020 AS-FILED figures for the FY2019-FY2020 rows (matching those years' own Balance Sheet), and switches to the FY2021 AR's own stated FY2020-comparative opening balance only at the point the FY2021 movements begin - the ~£8.1m gap is disclosed here rather than silently bridged.
-FINDING: the other Pillar 3 sheets in this workbook leave FY2024 blank because no dedicated 'as at 31 March 2024' Pillar 3 document was ever published - true for the CET1/Tier 1/Total Capital/ratio figures. However the FY2025 Pillar 3 document's own OV1 table (used here) discloses a full FY2024 comparative RWEA-by-category column, so RWA Breakdown alone can be populated for FY2024 even though the other Pillar 3 sheets cannot.
+CORRECTION, 2026-09-19: this note previously said no 'as at 31 March 2024' Pillar 3 was ever published. It was: see the FY2024 line above.
 PRESENTATION NOTE: FY2021's pre-KM1 category table has no separate 'Securitisation' line (Chetwood had no securitised exposures that early) and combines credit valuation adjustment into Counterparty credit risk rather than breaking it out - both blank rather than assumed zero-and-separate.</t>
         </is>
       </c>
@@ -4393,7 +4438,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -4426,7 +4471,9 @@
       <c r="B4" s="6" t="n">
         <v>3615720</v>
       </c>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>2387717</v>
+      </c>
       <c r="D4" s="6" t="n">
         <v>1519817</v>
       </c>
@@ -4451,7 +4498,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Not published - no Pillar 3 disclosure for this year</t>
+          <t>7.19%</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4478,11 +4525,11 @@
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+          <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. Unlike Barclays/Monzo, Chetwood's disclosures do not distinguish an 'excluding/including claims on central banks' basis in any year - a single leverage ratio definition is used throughout (Tier 1 capital / total exposure measure). FY2021 used a pre-KM1 narrative table; FY2022 onward uses the formal KM1 rows 13-14.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.) Unlike Barclays/Monzo, Chetwood's disclosures do not distinguish an 'excluding/including claims on central banks' basis in any year - a single leverage ratio definition is used throughout (Tier 1 capital / total exposure measure). FY2021 used a pre-KM1 narrative table; FY2022 onward uses the formal KM1 rows 13-14.
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020 discloses only the headline ratio (19%, stated twice - in the Summary-analysis table and again in Section 3.6, 'At 31 March 2020, the leverage ratio stood at 19%'); no total exposure measure is given anywhere in that document, so that row stays blank for FY2020 rather than being back-solved from the ratio.</t>
         </is>
       </c>
@@ -4492,8 +4539,9 @@
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
 OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
@@ -4558,7 +4606,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -4591,7 +4639,9 @@
       <c r="B4" s="6" t="n">
         <v>897493</v>
       </c>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>665116</v>
+      </c>
       <c r="D4" s="6" t="n">
         <v>302266</v>
       </c>
@@ -4610,7 +4660,9 @@
       <c r="B5" s="6" t="n">
         <v>489794</v>
       </c>
-      <c r="C5" s="6" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>395674</v>
+      </c>
       <c r="D5" s="6" t="n">
         <v>52035</v>
       </c>
@@ -4629,7 +4681,9 @@
       <c r="B6" s="6" t="n">
         <v>28009</v>
       </c>
-      <c r="C6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>34098</v>
+      </c>
       <c r="D6" s="6" t="n">
         <v>15169</v>
       </c>
@@ -4648,7 +4702,9 @@
       <c r="B7" s="6" t="n">
         <v>461785</v>
       </c>
-      <c r="C7" s="6" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>361576</v>
+      </c>
       <c r="D7" s="6" t="n">
         <v>36865</v>
       </c>
@@ -4671,7 +4727,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Not published - no Pillar 3 disclosure for this year</t>
+          <t>184%</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -4698,11 +4754,11 @@
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+          <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. FY2020 and FY2021 disclosed only the headline ratio in narrative form (no HQLA/outflow £ breakdown was published those years - the formal KM1 liquidity rows were introduced from FY2022). Chetwood's LCR ratios are extremely high because, as a young/small deposit-taker at the time, its regulatory outflow assumptions were small relative to its liquid asset holdings - this is as disclosed by Chetwood, not a transcription error; the FY2020 document says so in terms ('Given the early stage of Chetwood's development and the limited value of outflows the calculation of the Liquidity Coverage Ratio (LCR) results in a very high value. Chetwood's LCR ratio as at 31st March 2020 was 68,110%').
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.) FY2020 and FY2021 disclosed only the headline ratio in narrative form (no HQLA/outflow £ breakdown was published those years - the formal KM1 liquidity rows were introduced from FY2022). Chetwood's LCR ratios are extremely high because, as a young/small deposit-taker at the time, its regulatory outflow assumptions were small relative to its liquid asset holdings - this is as disclosed by Chetwood, not a transcription error; the FY2020 document says so in terms ('Given the early stage of Chetwood's development and the limited value of outflows the calculation of the Liquidity Coverage Ratio (LCR) results in a very high value. Chetwood's LCR ratio as at 31st March 2020 was 68,110%').
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
@@ -4712,8 +4768,9 @@
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
 OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
@@ -4778,7 +4835,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -4811,7 +4868,9 @@
       <c r="B4" s="6" t="n">
         <v>3677559</v>
       </c>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>2862609</v>
+      </c>
       <c r="D4" s="6" t="n">
         <v>1387511</v>
       </c>
@@ -4830,7 +4889,9 @@
       <c r="B5" s="6" t="n">
         <v>2536343</v>
       </c>
-      <c r="C5" s="6" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>1760110</v>
+      </c>
       <c r="D5" s="6" t="n">
         <v>572002</v>
       </c>
@@ -4853,7 +4914,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Not published - no Pillar 3 disclosure for this year</t>
+          <t>163%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -4880,11 +4941,11 @@
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+          <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. FY2021's NSFR figure (146.5%) is quoted exactly as printed in the FY2021 Pillar 3 report, which oddly labels it 'as at the 31 March 2020' in a document otherwise dated 'as at 31 March 2021' - this looks like a typo in Chetwood's own document, but it is reproduced verbatim rather than silently corrected; no £ breakdown was published for FY2020 or FY2021 (the formal KM1 NSFR rows were introduced from FY2022).
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.) FY2021's NSFR figure (146.5%) is quoted exactly as printed in the FY2021 Pillar 3 report, which oddly labels it 'as at the 31 March 2020' in a document otherwise dated 'as at 31 March 2021' - this looks like a typo in Chetwood's own document, but it is reproduced verbatim rather than silently corrected; no £ breakdown was published for FY2020 or FY2021 (the formal KM1 NSFR rows were introduced from FY2022).
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's own 193% comes from that year's own document ('The Company's Net Stable Funding Ratio (NSFR) as at the 31 March 2020 was 193%') and is a genuinely different figure from the 146.5% the FY2021 report mislabels as 'at the 31 March 2020' - further evidence that the FY2021 label is the typo, and that 146.5% belongs to FY2021 as carried here.</t>
         </is>
       </c>
@@ -4894,8 +4955,9 @@
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
 OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
@@ -4955,7 +5017,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -4982,27 +5044,27 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not published – Chetwood Pillar 3 FY2025 (SNCI reduced format) and Annual Report 2025 (text search, 2026-09-19) give no MREL figure or statement.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not published – Chetwood Pillar 3 FY2024 (Nov 2024, SNCI reduced format, contents p.2) and Annual Report 2024 (text search, 2026-09-19) give no MREL figure or statement.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – Chetwood Pillar 3 FY2023: 'has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its minimum capital requirement'.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – Chetwood Pillar 3 FY2022: 'has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its minimum capital requirement'.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – Chetwood Pillar 3 FY2021: 'has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its minimum capital requirement'.</t>
         </is>
       </c>
     </row>
@@ -5018,8 +5080,9 @@
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
 OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
@@ -5085,7 +5148,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024* (£'000)</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -5934,7 +5997,7 @@
 FY2020: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2020, p.19-21 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 FY2019: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2019, p.14-16 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
-FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+FY2024 is consolidated. Its Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024) was long believed unpublished and was located on 2026-09-19 on the bank's CMS file host (cdn.sanity.io) - see the note on each Pillar 3 sheet.
 HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
 - Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
 - FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
@@ -6005,7 +6068,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024* (£'000)</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -6556,7 +6619,7 @@
 FY2020: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2020, p.19-21 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 FY2019: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2019, p.14-16 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
-FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+FY2024 is consolidated. Its Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024) was long believed unpublished and was located on 2026-09-19 on the bank's CMS file host (cdn.sanity.io) - see the note on each Pillar 3 sheet.
 HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
 - Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
 - FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
@@ -7552,7 +7615,7 @@
 FY2020: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2020, p.19-21 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 FY2019: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2019, p.14-16 (Statement of Total Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
-FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+FY2024 is consolidated. Its Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024) was long believed unpublished and was located on 2026-09-19 on the bank's CMS file host (cdn.sanity.io) - see the note on each Pillar 3 sheet.
 HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
 - Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
 - FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
@@ -7623,7 +7686,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024* (£'000)</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -8956,7 +9019,7 @@
 FY2020: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2020, p.22 (Statement of Cashflows, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 FY2019: Chetwood Financial Limited Annual Report and Financial Statements, year ended 31 March 2019, p.17 (Statement of Cashflows, standalone entity, FRS 102 basis) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House filing history, company no. 09964966)
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
-FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+FY2024 is consolidated. Its Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024) was long believed unpublished and was located on 2026-09-19 on the bank's CMS file host (cdn.sanity.io) - see the note on each Pillar 3 sheet.
 HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
 - Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
 - FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
@@ -9023,7 +9086,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024* (£'000)</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -9456,7 +9519,7 @@
 FY2020: Annual Report and Financial Statements, year ended 31 March 2020, p.20/28 (Statement of Financial Position net loan balance; no IFRS 9 stage table - see FRS 102 note below) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI3NDIxOTQ2OWFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2019: Annual Report and Financial Statements, year ended 31 March 2019, p.15 (Statement of Financial Position net loan balance; no IFRS 9 stage table - see FRS 102 note below) - https://find-and-update.company-information.service.gov.uk/company/09964966/filing-history/MzI0MTExMzg0OGFkaXF6a2N4/document?format=pdf&amp;download=0
 ENTITY NOTE: Chetwood Financial Limited (trading as Chetwood Bank) is the entity on the PRA register - no holding-company substitution was needed here (unlike Monzo). All years are Chetwood Financial Limited, consolidated/Group basis, EXCEPT FY2021-FY2019 (marked †), which are Chetwood's own standalone entity accounts - the Group didn't exist yet (Chetwood acquired Yobota Limited on 1 March 2022, and CHL Mortgages for Intermediaries Limited later still), so there is no consolidated cash flow statement before FY2022. Companies House confirms FY2019-FY2021 accounts were filed as 'Full accounts' (solo), while FY2022-FY2025 were filed as 'Group of companies' accounts' (consolidated). Per user direction, FY2019-FY2021 are included on a standalone basis and clearly flagged, rather than omitted.
-FY2024 (marked *) is consolidated, but no Pillar 3 disclosure for 'as at 31 March 2024' was ever published or archived - see the note on each Pillar 3 sheet.
+FY2024 is consolidated. Its Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024) was long believed unpublished and was located on 2026-09-19 on the bank's CMS file host (cdn.sanity.io) - see the note on each Pillar 3 sheet.
 HISTORICAL-DEPTH FLOOR NOTE (added 2026-09-06, HD-023): the workbook's true floor is FY2019, not FY2016 as originally listed on that ticket, and not FY2021 as a since-corrected version of the same ticket guessed. Verified against Chetwood's own Companies House filing history (company no. 09964966, incorporated 22 Jan 2016) and its own statutory accounts, not a domain/snapshot scan:
 - Period to 31 Dec 2016: dormant shell only ('Total exemption full accounts', total assets £954k, no lending or deposits) - pre-banking, excluded.
 - FY2018 (15-month period, 1 Jan 2017 - 31 Mar 2018): the Company was granted a banking licence WITH RESTRICTIONS only on 22 Dec 2017; consumer lending commenced Feb 2018 (2 months of the 15-month period); there were zero customer deposits all period (total assets £7.1m, no deposit-taking yet) - this is a pre-launch/development-stage period, not a genuine operating bank year, so excluded as a self-skipped year despite audited accounts existing for it.
@@ -9482,7 +9545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -9502,7 +9565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Chetwood's own published UK key-metrics (KM1) template, reproduced in its row order with its own template row numbers, labels and printed precision. Amounts in £'000s, ratios as printed. Group/consolidated basis. Only the FY2022, FY2023 and FY2025 Pillar 3 editions carry a KM1 table, and each is single-column; FY2024 (no document), FY2021/FY2020 (editions pre-date the template) and FY2019 (no document) are intentionally blank. See source note below.</t>
+          <t>Chetwood's own published UK key-metrics (KM1) template, reproduced in its row order with its own template row numbers, labels and printed precision. Amounts in £'000s, ratios as printed. Group/consolidated basis. Only the FY2022-FY2025 Pillar 3 editions carry a KM1 table, and each is single-column (FY2024's is headed '2023' in error - see note); FY2021/FY2020 (editions pre-date the template) and FY2019 (no document) are intentionally blank. See source note below.</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9582,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -9534,41 +9597,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>[No UK KM1 published for this year - see note below]</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (amounts, £'000s)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published - no Pillar 3 disclosure for this year</t>
-        </is>
-      </c>
+      <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Available own funds (amounts, £'000s)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1    Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>187605</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>171791</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>91268</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>57554</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1    Common Equity Tier 1 (CET1) capital</t>
+          <t>2    Tier 1 capital</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
         <v>187605</v>
       </c>
-      <c r="C6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>171791</v>
+      </c>
       <c r="D6" s="6" t="n">
         <v>91268</v>
       </c>
@@ -9579,13 +9648,15 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2    Tier 1 capital</t>
+          <t>3    Total capital</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
         <v>187605</v>
       </c>
-      <c r="C7" s="6" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>171791</v>
+      </c>
       <c r="D7" s="6" t="n">
         <v>91268</v>
       </c>
@@ -9594,65 +9665,77 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>3    Total capital</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>187605</v>
-      </c>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure amounts (£'000s)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n">
-        <v>91268</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>57554</v>
-      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Risk-weighted exposure amounts (£'000s)</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4    Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1233321</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>824623</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>343668</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>196750</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>4    Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>1233321</v>
-      </c>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Capital ratios (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n">
-        <v>343668</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>196750</v>
-      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Capital ratios (as a percentage of risk-weighted exposure amount)</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>5    Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>5    Common Equity Tier 1 ratio (%)</t>
+          <t>6    Tier 1 ratio (%)</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -9660,7 +9743,11 @@
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
           <t>26.6%</t>
@@ -9675,7 +9762,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>6    Tier 1 ratio (%)</t>
+          <t>7    Total capital ratio (%)</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -9683,7 +9770,11 @@
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
           <t>26.6%</t>
@@ -9696,66 +9787,74 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>7    Total capital ratio (%)</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements based on SREP (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>26.6%</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>29.3%</t>
-        </is>
-      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Additional own funds requirements based on SREP (as a percentage of risk-weighted exposure amount)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>UK 7a    Additional CET1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.92%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>5.35%</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>11.07%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>UK 7a    Additional CET1 SREP requirements (%)</t>
+          <t>UK 7b    Additional AT1 SREP requirements (%)</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>1.92%</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>11.07%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>UK 7b    Additional AT1 SREP requirements (%)</t>
+          <t>UK 7c    Additional T2 SREP requirements (%)</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -9763,7 +9862,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>-</t>
@@ -9778,92 +9881,104 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>UK 7c    Additional T2 SREP requirements (%)</t>
+          <t>UK 7d    Total SREP own funds requirements (%)</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n"/>
+          <t>9.92%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>13.35%</t>
+        </is>
+      </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19.07%</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>UK 7d    Total SREP own funds requirements (%)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>9.92%</t>
-        </is>
-      </c>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>19.07%</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>19.1%</t>
-        </is>
-      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Combined buffer requirement (as a percentage of risk-weighted exposure amount)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>8    Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>8    Capital conservation buffer (%)</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
+          <t>UK 8a    Conservation buffer due to macro-prudential or systemic risk identified at the level of a Member State (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
+      <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>UK 8a    Conservation buffer due to macro-prudential or systemic risk identified at the level of a Member State (%)</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
+          <t>9    Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
           <t>0%</t>
@@ -9873,20 +9988,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>9    Institution specific countercyclical capital buffer (%)</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>2.00%</t>
-        </is>
-      </c>
+          <t>UK 9a    Systemic risk buffer (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
+      <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
           <t>0%</t>
@@ -9896,7 +10003,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>UK 9a    Systemic risk buffer (%)</t>
+          <t>10    Global Systemically Important Institution buffer (%)</t>
         </is>
       </c>
       <c r="B24" s="6" t="n"/>
@@ -9911,7 +10018,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>10    Global Systemically Important Institution buffer (%)</t>
+          <t>UK 10a    Other Systemically Important Institution buffer</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
@@ -9926,12 +10033,24 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>UK 10a    Other Systemically Important Institution buffer</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
+          <t>11    Combined buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
           <t>0%</t>
@@ -9941,169 +10060,175 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>11    Combined buffer requirement (%)</t>
+          <t>UK 11a    Overall capital requirements (%)</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>4.50%</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n"/>
+          <t>14.42%</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>17.85%</t>
+        </is>
+      </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>22.57%</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21.6%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>UK 11a    Overall capital requirements (%)</t>
+          <t>12    CET1 available after meeting the total SREP own funds requirements (%)</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>14.42%</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n"/>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>7.48%</t>
+        </is>
+      </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>22.57%</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>21.6%</t>
-        </is>
+          <t>7.49%</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>20034</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>12    CET1 available after meeting the total SREP own funds requirements (%)</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>5.29%</t>
-        </is>
-      </c>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio — as captioned in the FY2024 and FY2025 editions (excluding claims on central banks)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
       <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>7.49%</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>20034</v>
-      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Leverage ratio — as captioned in the FY2025 edition (excluding claims on central banks)</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>13    Total exposure measure excluding claims on central banks</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>3615720</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>2387717</v>
+      </c>
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>13    Total exposure measure excluding claims on central banks</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>3615720</v>
-      </c>
-      <c r="C31" s="6" t="n"/>
+          <t>14    Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>7.19%</t>
+        </is>
+      </c>
       <c r="D31" s="6" t="n"/>
       <c r="E31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>14    Leverage ratio excluding claims on central banks (%)</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio — as captioned in the FY2022 and FY2023 editions (basis not stated)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6" t="n"/>
       <c r="E32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Leverage ratio — as captioned in the FY2022 and FY2023 editions (basis not stated)</t>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>13    Leverage ratio total exposure measure</t>
         </is>
       </c>
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
+      <c r="D33" s="6" t="n">
+        <v>1519817</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>394658</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>13    Leverage ratio total exposure measure</t>
+          <t>14    Leverage ratio</t>
         </is>
       </c>
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n">
-        <v>1519817</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>394658</v>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>6.01%</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>14.58%</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>14    Leverage ratio</t>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements to address risks of excessive leverage (as a percentage of leverage ratio total exposure amount)</t>
         </is>
       </c>
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>6.01%</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>14.58%</t>
-        </is>
-      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Additional own funds requirements to address risks of excessive leverage (as a percentage of leverage ratio total exposure amount)</t>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>UK 14a    Additional CET1 leverage ratio requirements (%)</t>
         </is>
       </c>
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="6" t="n"/>
       <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>UK 14a    Additional CET1 leverage ratio requirements (%)</t>
+          <t>UK 14b    Additional AT1 leverage ratio requirements (%)</t>
         </is>
       </c>
       <c r="B37" s="6" t="n"/>
@@ -10118,7 +10243,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>UK 14b    Additional AT1 leverage ratio requirements (%)</t>
+          <t>UK 14c    Additional T2 leverage ratio requirements (%)</t>
         </is>
       </c>
       <c r="B38" s="6" t="n"/>
@@ -10133,7 +10258,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>UK 14c    Additional T2 leverage ratio requirements (%)</t>
+          <t>UK 14d    Total SREP leverage ratio requirements (%)</t>
         </is>
       </c>
       <c r="B39" s="6" t="n"/>
@@ -10148,7 +10273,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>UK 14d    Total SREP leverage ratio requirements (%)</t>
+          <t>UK 14e    Applicable leverage buffer</t>
         </is>
       </c>
       <c r="B40" s="6" t="n"/>
@@ -10163,7 +10288,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>UK 14e    Applicable leverage buffer</t>
+          <t>UK 14f    Overall leverage ratio requirements (%)</t>
         </is>
       </c>
       <c r="B41" s="6" t="n"/>
@@ -10171,221 +10296,228 @@
       <c r="D41" s="6" t="n"/>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>UK 14f    Overall leverage ratio requirements (%)</t>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio (£'000s / %)</t>
         </is>
       </c>
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="6" t="n"/>
       <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="E42" s="6" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Liquidity Coverage Ratio (£'000s / %)</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>15    Total high-quality liquid assets (HQLA) (Weighted value -average)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>897493</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>665116</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>302266</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>67841</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>15    Total high-quality liquid assets (HQLA) (Weighted value -average)</t>
+          <t>UK 16a    Cash outflows - Total weighted value</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>897493</v>
-      </c>
-      <c r="C44" s="6" t="n"/>
+        <v>489794</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>395674</v>
+      </c>
       <c r="D44" s="6" t="n">
-        <v>302266</v>
+        <v>52035</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>67841</v>
+        <v>5627</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>UK 16a    Cash outflows - Total weighted value</t>
+          <t>UK 16b    Cash inflows - Total weighted value</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>489794</v>
-      </c>
-      <c r="C45" s="6" t="n"/>
+        <v>28009</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>34098</v>
+      </c>
       <c r="D45" s="6" t="n">
-        <v>52035</v>
+        <v>15169</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>5627</v>
+        <v>13656</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>UK 16b    Cash inflows - Total weighted value</t>
+          <t>16    Total net cash outflows (adjusted value)</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>28009</v>
-      </c>
-      <c r="C46" s="6" t="n"/>
+        <v>461785</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>361576</v>
+      </c>
       <c r="D46" s="6" t="n">
-        <v>15169</v>
+        <v>36865</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>13656</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>16    Total net cash outflows (adjusted value)</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>461785</v>
-      </c>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n">
-        <v>36865</v>
-      </c>
-      <c r="E47" s="6" t="n">
-        <v>1407</v>
+          <t>17    Liquidity coverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>194%</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>184%</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>1,015%</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>4,823%</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>17    Liquidity coverage ratio (%)</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>194%</t>
-        </is>
-      </c>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (£'000s / %)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n"/>
       <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>1,015%</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>4,823%</t>
-        </is>
-      </c>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Net Stable Funding Ratio (£'000s / %)</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>18    Total available stable funding</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>3677559</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>2862609</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>1387511</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>380549</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>18    Total available stable funding</t>
+          <t>19    Total required stable funding</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>3677559</v>
-      </c>
-      <c r="C50" s="6" t="n"/>
+        <v>2536343</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>1760110</v>
+      </c>
       <c r="D50" s="6" t="n">
-        <v>1387511</v>
+        <v>572002</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>380549</v>
+        <v>233566</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>19    Total required stable funding</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="n">
-        <v>2536343</v>
-      </c>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n">
-        <v>572002</v>
-      </c>
-      <c r="E51" s="6" t="n">
-        <v>233566</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
           <t>20    NSFR ratio (%)</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>145%</t>
         </is>
       </c>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>163%</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>243%</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>162.9%</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="460" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
+    <row r="53" ht="460" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>Sources - Chetwood's own UK KM1 key-metrics template, reproduced as printed. Each column is transcribed from the edition in which that year is the reporting year; every one of these editions is SINGLE-COLUMN (header block 'a  £'000s' over one year only), so no figure here is a later edition's comparative.
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 'Key Metrics', pp.9-10 of 15 - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31st March 2023, Section 6 'Key Metrics', p.17 (PDF p.18 of 34) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31st March 2022, 'Annex B: Key Metrics - KM1', pp.35-36 (PDF pp.36-37 of 41) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2024, FY2021, FY2020 and FY2019 are blank, for three different reasons, none of which is a failed search:
-• FY2024 - no Pillar 3 document 'as at 31 March 2024' exists (re-verified four ways 2026-09-15, see the FY2024 note on any metric sheet), and the FY2025 edition's KM1 has no comparative column to borrow from.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 'Key Metrics', pp.10-11 of 15 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf. SOURCE DEFECT: its single KM1 column is headed '2023', but the document is 'as at 31 March 2024' (p.3) and its row 4 (824,623) equals the OV1 '2024' column on p.12; reproduced under FY2024 with the heading recorded here. It prints UK 7b/UK 7c as an en dash '–'. CORRECTION: from 2026-09-18 to 2026-09-19 this column carried a statement that no Pillar 3 was published for FY2024; that was false - the edition was on the bank's CMS file host (cdn.sanity.io), which no earlier search had looked at.
+FY2021, FY2020 and FY2019 are blank, for two different reasons, none of which is a failed search:
 • FY2021 and FY2020 - both editions pre-date the template. The FY2021 document was re-read in full for this sheet: 'key metric', 'KM1', 'combined buffer' and 'risk weighted exposure' appear nowhere in it, and its only capital table is a narrative 'Total CET1 Capital' build-up. The FY2020 edition is the same shape. The FY2020/FY2021 figures on the single-metric sheets come from those narrative tables and are deliberately NOT re-assembled into KM1 rows here.
 • FY2019 - Chetwood published no Pillar 3 disclosure at all that year.
 PRESENTATION NOTES:
-• ROW SET DRIFT: rows UK 8a, UK 9a, 10, UK 10a and UK 14a-UK 14f are printed by the FY2022 edition only; the FY2023 and FY2025 editions omit them from the table entirely. The union is shown, in the template's canonical order, so the sheet matches the table a reader of the FY2022 report would recognise.
-• DASH vs ZERO, AND THIS SHEET NOW SHOWS THE DIFFERENCE. The FY2022 edition uses both glyphs in ONE table and means different things by them. It prints '-' at rows UK 7b, UK 7c and UK 14a-UK 14e - those cells carry a literal dash, because the requirement does not apply to Chetwood - and it prints '0%' at rows UK 8a, 9, UK 9a, 10, UK 10a, 11 and UK 14f, which are kept as the measured zeros the Bank published. The FY2023 and FY2025 editions print '-' at UK 7b/UK 7c only, and those carry dashes too; all three editions were re-read at source on 2026-09-18. Chetwood is the clearest demonstration in this corpus of why the two glyphs must not be flattened together: a single table, printed by a single bank on a single date, deliberately using a dash for 'does not apply' and a zero for 'measured at nil'. Anything that rendered both as the same thing would be discarding a distinction Chetwood took care to draw. Rows UK 14a-UK 14e are blank for FY2023 and FY2025 because those editions omit the block entirely - a third state again, and not the same as either.
+• ROW SET DRIFT: rows UK 8a, UK 9a, 10, UK 10a and UK 14a-UK 14f are printed by the FY2022 edition only; the FY2023, FY2024 and FY2025 editions omit them from the table entirely. The union is shown, in the template's canonical order, so the sheet matches the table a reader of the FY2022 report would recognise.
+• DASH vs ZERO, AND THIS SHEET NOW SHOWS THE DIFFERENCE. The FY2022 edition uses both glyphs in ONE table and means different things by them. It prints '-' at rows UK 7b, UK 7c and UK 14a-UK 14e - those cells carry a literal dash, because the requirement does not apply to Chetwood - and it prints '0%' at rows UK 8a, 9, UK 9a, 10, UK 10a, 11 and UK 14f, which are kept as the measured zeros the Bank published. The FY2023, FY2024 and FY2025 editions print a dash at UK 7b/UK 7c only, and those carry dashes too; all three editions were re-read at source on 2026-09-18. Chetwood is the clearest demonstration in this corpus of why the two glyphs must not be flattened together: a single table, printed by a single bank on a single date, deliberately using a dash for 'does not apply' and a zero for 'measured at nil'. Anything that rendered both as the same thing would be discarding a distinction Chetwood took care to draw. Rows UK 14a-UK 14e are blank for FY2023 and FY2025 because those editions omit the block entirely - a third state again, and not the same as either.
 • SOURCE DEFECT, row 11 (FY2022): the FY2022 edition prints Combined buffer requirement as '0%' even though row 8 immediately above prints a 2.50% capital conservation buffer, so the combined buffer cannot be nil. Reproduced as published and flagged here; the FY2023 (3.50%) and FY2025 (4.50%) editions are internally consistent.
 • SOURCE DEFECT, row 12 (FY2022): captioned 'CET1 available after meeting the total SREP own funds requirements (%)' but printed as 20,034 - a £'000 amount, not a percentage. Reproduced as printed.
-• LEVERAGE CAPTION CHANGE: the FY2022 and FY2023 editions caption rows 13/14 'Leverage ratio total exposure measure' / 'Leverage ratio' with no basis stated; the FY2025 edition captions the same rows 'Total exposure measure excluding claims on central banks' / 'Leverage ratio excluding claims on central banks (%)'. Shown as two separately-captioned blocks rather than merged. All three reporting dates fall after the 1 January 2022 UK change that excluded claims on central banks from the exposure measure, so the underlying basis is very likely unchanged and only the caption moved - but no Chetwood edition says so, and this sheet reproduces rather than infers. The Leverage Ratio metric sheet carries the same four figures as one series, with its own note.
+• LEVERAGE CAPTION CHANGE: the FY2022 and FY2023 editions caption rows 13/14 'Leverage ratio total exposure measure' / 'Leverage ratio' with no basis stated; the FY2024 and FY2025 editions caption the same rows 'Total exposure measure excluding claims on central banks' / 'Leverage ratio excluding claims on central banks (%)'. Shown as two separately-captioned blocks rather than merged. All three reporting dates fall after the 1 January 2022 UK change that excluded claims on central banks from the exposure measure, so the underlying basis is very likely unchanged and only the caption moved - but no Chetwood edition says so, and this sheet reproduces rather than infers. The Leverage Ratio metric sheet carries the same four figures as one series, with its own note.
 • PRECISION: the FY2022 edition prints ratios to one decimal place ('29.3%', '11.1%', '2.5%'); the FY2023 and FY2025 editions print two ('11.07%', '2.50%', '1.92%'), while still printing row 9 as '1%' in FY2023 and rows 17/20 as whole percents in FY2025. Each cell keeps the precision of its own edition.
 • Row 15 is a weighted 12-month average (the caption says so); rows 17 and 20 are as printed, including the FY2023 thousands separator in '1,015%'.
-LATEST-EDITION CHECK, 2026-09-16: chetwoodbank.co.uk publishes its documents at undated, overwritten URLs (/documents/chetwood-bank-pillar-three-disclosures.pdf and /documents/chetwood-bank-annual-report.pdf, both linked from /about-us). Both were downloaded fresh on that date: the Pillar 3 file is still the 'September 2025' edition with a single 2025 column, and the Annual Report file is still 'year ended 31 March 2025'. No FY2026 edition of either had been published. Checked, none newer.</t>
+LATEST-EDITION CHECK, 2026-09-16: chetwoodbank.co.uk publishes its documents at undated, overwritten URLs (/documents/chetwood-bank-pillar-three-disclosures.pdf and /documents/chetwood-bank-annual-report.pdf, both linked from /about-us). Both were downloaded fresh on that date: the Pillar 3 file is still the 'September 2025' edition with a single 2025 column, and the Annual Report file is still 'year ended 31 March 2025'. No FY2026 edition of either had been published. Checked, none newer.
+FY2026 CHECK, 2026-09-19 (year ended 31 March 2026): no FY2026 edition of either document is out, so no FY2026 column is added. Routes: (1) both undated live URLs re-downloaded - the Annual Report is still 'Year ended 31 March 2025' (PDF created 29 Oct 2025, modified 17 Nov 2025) and the Pillar 3 still 'as at 31 March 2025' (PDF created 7 Nov 2025); (2) Companies House filing history for 09964966, unfiltered, page 1: the newest accounts filing is AA 'Group of companies' accounts made up to 31 March 2025' (20 Dec 2025), and the company page gives next accounts made up to 31 March 2026 due by 31 December 2026; (3) Wayback CDX of chetwoodbank.co.uk holds no /documents/ capture, and archived homepages link only the FY2023-FY2025 cdn.sanity.io files. Prior pattern: the FY2025 Annual Report was filed 20 Dec 2025 and its Pillar 3 published Sept-Nov 2025; the FY2024 accounts were filed 4 Oct 2024 and its Pillar 3 is dated Nov 2024.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A53:E53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10436,7 +10568,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -10469,10 +10601,8 @@
       <c r="B4" s="6" t="n">
         <v>187605</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published - no Pillar 3 disclosure for this year</t>
-        </is>
+      <c r="C4" s="6" t="n">
+        <v>171791</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>91268</v>
@@ -10490,11 +10620,11 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+          <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.)
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
@@ -10504,8 +10634,9 @@
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
 OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
@@ -10570,7 +10701,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024*</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -10605,7 +10736,11 @@
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>26.6%</t>
@@ -10655,13 +10790,13 @@
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2024 is blank - no Pillar 3 disclosure 'as at 31 March 2024' was published/archived, re-verified 2026-09-15 four ways (see source note). Critically, the FY2025 Pillar 3 document's KM1 template has a SINGLE '2025' column with no prior-year comparative, so it cannot fill FY2024 the way a comparative column normally would; the one exception is its OV1 table, which does carry a full FY2024 comparative and so populates the Total RWAs and RWA Breakdown sheets. Both Annual Reports were also read in full: the FY2024 and FY2025 reports disclose a Group CET1 capital RATIO (rounded to a whole percent) in their KPI tables - shown as a separate, clearly-labelled row on the CET1 Ratio sheet - and a 'Total regulatory capital' capital-management note, but that note's figure is NOT CET1 (it differs from the Pillar 3 CET1 by -£2.3m in FY2023 and +£5.7m in FY2025, an undisclosed set of prudential deductions/filters), and neither report states RWAs, Tier 1/Total capital, leverage, LCR or NSFR at all. Those cells therefore stay blank.
+          <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. The FY2024 absence therefore remains what it was: an unexplained non-publication for the year ended 31 March 2024, with no waiver, exemption or replacement disclosure located - NOT a structural exemption. Do not upgrade it to one. FY2021 is as stated in the source (rounded to the nearest whole percent; no decimal figure was disclosed that year).
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.) FY2021 is as stated in the source (rounded to the nearest whole percent; no decimal figure was disclosed that year).
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. The FY2020 document's Summary-analysis table prints a 'Tier 1 Ratio' of 30% and no separate CET1 ratio line; its own capital-resources table shows CET1 £50,697k going straight to Tier 2 with no Additional Tier 1 line, so Tier 1 = CET1 that year and 30% is the CET1 ratio as well - the same treatment already applied to every other year on this sheet.
-SECOND ROW (alternative basis, added 2026-09-15): the Annual Reports' KPI tables are the only source that states any FY2024 capital ratio, so their whole-percent Group CET1 ratio is carried on its own row - FY2024 21% (stated identically in the FY2024 report's own year column and the FY2025 report's FY2024 comparative column, two independent confirmations). It is NOT merged into the primary row because the two series do not agree: for FY2025 the KPI table says 16% where the Pillar 3 KM1 says 15.2%, a difference too large to be rounding, cause not explained in either document (FY2023 does reconcile: 27% vs 26.6%). Treat the FY2024 21% as indicative of level, not as a KM1-basis figure.</t>
+SECOND ROW (alternative basis, added 2026-09-15): the Annual Reports' KPI tables were then thought the only source of any FY2024 capital ratio (the FY2024 Pillar 3, found 2026-09-19, prints 20.8%), and their whole-percent Group CET1 ratio is carried on its own row - FY2024 21% (stated identically in the FY2024 report's own year column and the FY2025 report's FY2024 comparative column, two independent confirmations). It is NOT merged into the primary row because the two series do not agree: for FY2025 the KPI table says 16% where the Pillar 3 KM1 says 15.2%, a difference too large to be rounding, cause not explained in either document (FY2023 does reconcile: 27% vs 26.6%). Treat the FY2024 21% as indicative of level, not as a KM1-basis figure.</t>
         </is>
       </c>
     </row>
@@ -10670,8 +10805,9 @@
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2024: No Pillar 3 disclosure 'as at 31 March 2024' was found - not published on Chetwood's live site (which hosts only the current edition at a non-dated URL) and no snapshot was captured by the Internet Archive Wayback Machine between the FY2023 edition (published Jan 2024) and the FY2025 edition (published Sept 2025). Left blank.
-FY2024 RE-VERIFIED 2026-09-15 (interior-gap sweep). The FY2024 Pillar 3 document remains genuinely unobtainable, checked four ways: (1) the FY2025 Pillar 3 document's own KM1 template has a SINGLE '2025' column with no prior-year comparative at all, so it cannot supply FY2024; (2) the live site hosts only https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf - chetwoodbank.co.uk/documents/ is not browsable and six plausible dated URL variants (…-2024.pdf, …-pillar-3-…, …-march-2024.pdf etc.) all return the site's HTML 404 page; (3) a Wayback CDX scan of BOTH domains found only the four chetwood.co/static/… Pillar 3 snapshots already cited here (plus one Sept-2020 snapshot, see the FY2019/FY2020 line below) and NO archived chetwoodbank.co.uk/documents/ URL of any kind; (4) the FY2024 and FY2025 Annual Reports were read in full for regulatory-capital content - see the CET1 Ratio sheet for the one FY2024 figure they do yield, and the FY2024 gap note on each sheet for what they do not.
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
 OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
 FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
 FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf

--- a/banks/CHETWOOD FINANCIALS.xlsx
+++ b/banks/CHETWOOD FINANCIALS.xlsx
@@ -1022,12 +1022,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AZ$5:$BF$5</f>
+              <f>'Overview'!$AZ$5:$BE$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AZ$6:$BF$6</f>
+              <f>'Overview'!$AZ$6:$BE$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1055,12 +1055,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AZ$5:$BF$5</f>
+              <f>'Overview'!$AZ$5:$BE$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AZ$7:$BF$7</f>
+              <f>'Overview'!$AZ$7:$BE$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1088,12 +1088,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AZ$5:$BF$5</f>
+              <f>'Overview'!$AZ$5:$BE$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AZ$8:$BF$8</f>
+              <f>'Overview'!$AZ$8:$BE$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1121,12 +1121,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AZ$5:$BF$5</f>
+              <f>'Overview'!$AZ$5:$BE$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AZ$9:$BF$9</f>
+              <f>'Overview'!$AZ$9:$BE$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1154,12 +1154,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AZ$5:$BF$5</f>
+              <f>'Overview'!$AZ$5:$BE$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AZ$10:$BF$10</f>
+              <f>'Overview'!$AZ$10:$BE$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1187,12 +1187,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AZ$5:$BF$5</f>
+              <f>'Overview'!$AZ$5:$BE$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AZ$11:$BF$11</f>
+              <f>'Overview'!$AZ$11:$BE$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1667,7 +1667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF40"/>
+  <dimension ref="A1:BE40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1725,7 +1725,6 @@
     <col hidden="1" width="13" customWidth="1" min="55" max="55"/>
     <col hidden="1" width="13" customWidth="1" min="56" max="56"/>
     <col hidden="1" width="13" customWidth="1" min="57" max="57"/>
-    <col hidden="1" width="13" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1828,35 +1827,30 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>FY2019†‡</t>
+          <t>FY2020†‡</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>FY2020†‡</t>
+          <t>FY2021†</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>FY2021†</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1920,22 +1914,22 @@
           <t>CET1 Ratio</t>
         </is>
       </c>
+      <c r="AZ6" t="n">
+        <v>30</v>
+      </c>
       <c r="BA6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB6" t="n">
-        <v>28</v>
+        <v>29.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>29.3</v>
+        <v>26.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>26.6</v>
+        <v>20.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="BF6" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -1997,22 +1991,22 @@
           <t>Tier 1 Ratio</t>
         </is>
       </c>
+      <c r="AZ7" t="n">
+        <v>30</v>
+      </c>
       <c r="BA7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB7" t="n">
-        <v>28</v>
+        <v>29.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>29.3</v>
+        <v>26.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>26.6</v>
+        <v>20.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="BF7" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -2074,22 +2068,22 @@
           <t>Total Capital Ratio</t>
         </is>
       </c>
+      <c r="AZ8" t="n">
+        <v>31</v>
+      </c>
       <c r="BA8" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>28</v>
+        <v>29.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>29.3</v>
+        <v>26.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>26.6</v>
+        <v>20.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="BF8" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -2151,22 +2145,22 @@
           <t>Leverage Ratio</t>
         </is>
       </c>
+      <c r="AZ9" t="n">
+        <v>19</v>
+      </c>
       <c r="BA9" t="n">
-        <v>19</v>
+        <v>23.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>23.4</v>
+        <v>14.58</v>
       </c>
       <c r="BC9" t="n">
-        <v>14.58</v>
+        <v>6.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.01</v>
+        <v>7.19</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="BF9" t="n">
         <v>5.19</v>
       </c>
     </row>
@@ -2176,22 +2170,22 @@
           <t>LCR</t>
         </is>
       </c>
+      <c r="AZ10" t="n">
+        <v>68110</v>
+      </c>
       <c r="BA10" t="n">
-        <v>68110</v>
+        <v>51086</v>
       </c>
       <c r="BB10" t="n">
-        <v>51086</v>
+        <v>4823</v>
       </c>
       <c r="BC10" t="n">
-        <v>4823</v>
+        <v>1015</v>
       </c>
       <c r="BD10" t="n">
-        <v>1015</v>
+        <v>184</v>
       </c>
       <c r="BE10" t="n">
-        <v>184</v>
-      </c>
-      <c r="BF10" t="n">
         <v>194</v>
       </c>
     </row>
@@ -2206,22 +2200,22 @@
           <t>NSFR</t>
         </is>
       </c>
+      <c r="AZ11" t="n">
+        <v>193</v>
+      </c>
       <c r="BA11" t="n">
-        <v>193</v>
+        <v>146.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>146.5</v>
+        <v>162.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>162.9</v>
+        <v>243</v>
       </c>
       <c r="BD11" t="n">
-        <v>243</v>
+        <v>163</v>
       </c>
       <c r="BE11" t="n">
-        <v>163</v>
-      </c>
-      <c r="BF11" t="n">
         <v>145</v>
       </c>
     </row>
@@ -3107,11 +3101,6 @@
           <t>FY2020†‡</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>FY2019†‡</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3149,7 +3138,6 @@
           <t>30%</t>
         </is>
       </c>
-      <c r="H33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -3187,7 +3175,6 @@
           <t>30%</t>
         </is>
       </c>
-      <c r="H34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -3225,7 +3212,6 @@
           <t>31%</t>
         </is>
       </c>
-      <c r="H35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -3263,7 +3249,6 @@
           <t>19%</t>
         </is>
       </c>
-      <c r="H36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -3301,7 +3286,6 @@
           <t>68,110%</t>
         </is>
       </c>
-      <c r="H37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -3339,7 +3323,6 @@
           <t>193%</t>
         </is>
       </c>
-      <c r="H38" s="6" t="n"/>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
@@ -4465,7 +4448,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Leverage ratio total exposure measure</t>
+          <t>Total exposure measure</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">

--- a/banks/CHETWOOD FINANCIALS.xlsx
+++ b/banks/CHETWOOD FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3350,7 +3351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3365,14 +3366,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Tier 1 Capital</t>
+          <t>Chetwood Financial Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -3416,42 +3417,80 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>187605</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>171791</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>91268</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>57554</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>50637</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>50697</v>
-      </c>
-    </row>
-    <row r="5" ht="325" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 (CET1) capital ratio per Annual Report KPI table (whole %, alternative basis - see note)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="390" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.) Equal to CET1 capital in every year shown - Chetwood has no Additional Tier 1 (AT1) instruments (in FY2020 confirmed by its capital-resources table running CET1 -&gt; Tier 2 -&gt; Total with no AT1 line).
-FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="377" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.) FY2021 is as stated in the source (rounded to the nearest whole percent; no decimal figure was disclosed that year).
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. The FY2020 document's Summary-analysis table prints a 'Tier 1 Ratio' of 30% and no separate CET1 ratio line; its own capital-resources table shows CET1 £50,697k going straight to Tier 2 with no Additional Tier 1 line, so Tier 1 = CET1 that year and 30% is the CET1 ratio as well - the same treatment already applied to every other year on this sheet.
+SECOND ROW (alternative basis, added 2026-09-15): the Annual Reports' KPI tables were then thought the only source of any FY2024 capital ratio (the FY2024 Pillar 3, found 2026-09-19, prints 20.8%), and their whole-percent Group CET1 ratio is carried on its own row - FY2024 21% (stated identically in the FY2024 report's own year column and the FY2025 report's FY2024 comparative column, two independent confirmations). It is NOT merged into the primary row because the two series do not agree: for FY2025 the KPI table says 16% where the Pillar 3 KM1 says 15.2%, a difference too large to be rounding, cause not explained in either document (FY2023 does reconcile: 27% vs 26.6%). Treat the FY2024 21% as indicative of level, not as a KM1-basis figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="377" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources (see entity note on Cash Flow Statement sheet):
 FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
@@ -3464,8 +3503,8 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="195" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="10" ht="195" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>(continued)
 FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
@@ -3477,9 +3516,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3506,14 +3545,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Tier 1 Ratio</t>
+          <t>Chetwood Financial Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -3557,48 +3596,36 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.8%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>26.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>29.3%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="312" customHeight="1">
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>187605</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>171791</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>91268</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>57554</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>50637</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>50697</v>
+      </c>
+    </row>
+    <row r="5" ht="325" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.)
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.) Equal to CET1 capital in every year shown - Chetwood has no Additional Tier 1 (AT1) instruments (in FY2020 confirmed by its capital-resources table running CET1 -&gt; Tier 2 -&gt; Total with no AT1 line).
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
@@ -3659,14 +3686,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Total Capital</t>
+          <t>Chetwood Financial Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -3710,36 +3737,48 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>187605</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>171791</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>91268</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>57554</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>50637</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>52835</v>
-      </c>
-    </row>
-    <row r="5" ht="325" customHeight="1">
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="312" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.) Equal to CET1/Tier 1 capital in FY2021-FY2025 - Chetwood had no Tier 2 capital in those years. FY2020 is the exception and the only year that differs: its capital-resources table discloses £2,138k of Tier 2 capital on top of CET1 £50,697k, giving Total regulatory capital £52,835k as printed.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.)
 FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
@@ -3800,14 +3839,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Total Capital Ratio</t>
+          <t>Chetwood Financial Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -3851,38 +3890,26 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.8%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>26.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>29.3%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>187605</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>171791</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>91268</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>57554</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>50637</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>52835</v>
       </c>
     </row>
     <row r="5" ht="325" customHeight="1">
@@ -3892,8 +3919,8 @@
 FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
 SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
 Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.)
-FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's 31% is higher than that year's 30% Tier 1 ratio because of the £2,138k of Tier 2 capital described on the Total Capital sheet - both figures are printed in the document's own Summary-analysis table, neither is derived.</t>
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.) Equal to CET1/Tier 1 capital in FY2021-FY2025 - Chetwood had no Tier 2 capital in those years. FY2020 is the exception and the only year that differs: its capital-resources table discloses £2,138k of Tier 2 capital on top of CET1 £50,697k, giving Total regulatory capital £52,835k as printed.
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only.</t>
         </is>
       </c>
     </row>
@@ -3953,14 +3980,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chetwood Financial Limited — Total RWAs</t>
+          <t>Chetwood Financial Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -4004,33 +4031,49 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1233321</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>824623</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>343668</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>196750</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>178987</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>171000</v>
-      </c>
-    </row>
-    <row r="5" ht="78" customHeight="1">
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="325" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's £171,000k is the document's own printed 'Risk Weighted Assets (£m) £171.0m' - disclosed to one decimal place of £m only, so the trailing three digits are the unit conversion, not spurious precision. It reconciles exactly to that document's own two components (Credit Risk RWAs £119.4m + operational-risk RWAs £51.6m = £171.0m), shown on the RWA Breakdown sheet.
-FY2024's 824,623 is printed in the FY2024 edition's own KM1 row 4 (p.10) and OV1 total (p.12), and identically as the FY2025 edition's OV1 2024 comparative.</t>
+          <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
+FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
+SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
+Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
+What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.)
+FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's 31% is higher than that year's 30% Tier 1 ratio because of the £2,138k of Tier 2 capital described on the Total Capital sheet - both figures are printed in the document's own Summary-analysis table, neither is derived.</t>
         </is>
       </c>
     </row>
@@ -4070,6 +4113,143 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1233321</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>824623</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>343668</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>196750</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>178987</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>171000</v>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. FY2020's £171,000k is the document's own printed 'Risk Weighted Assets (£m) £171.0m' - disclosed to one decimal place of £m only, so the trailing three digits are the unit conversion, not spurious precision. It reconciles exactly to that document's own two components (Credit Risk RWAs £119.4m + operational-risk RWAs £51.6m = £171.0m), shown on the RWA Breakdown sheet.
+FY2024's 824,623 is printed in the FY2024 edition's own KM1 row 4 (p.10) and OV1 total (p.12), and identically as the FY2025 edition's OV1 2024 comparative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="377" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources (see entity note on Cash Flow Statement sheet):
+FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="195" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4424,7 +4604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4600,7 +4780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4837,7 +5017,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5027,139 +5207,6 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A9:G9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Chetwood Financial Limited — MREL Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021†</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>MREL ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – Chetwood Pillar 3 FY2025 (SNCI reduced format) and Annual Report 2025 (text search, 2026-09-19) give no MREL figure or statement.</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – Chetwood Pillar 3 FY2024 (Nov 2024, SNCI reduced format, contents p.2) and Annual Report 2024 (text search, 2026-09-19) give no MREL figure or statement.</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – Chetwood Pillar 3 FY2023: 'has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its minimum capital requirement'.</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – Chetwood Pillar 3 FY2022: 'has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its minimum capital requirement'.</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – Chetwood Pillar 3 FY2021: 'has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its minimum capital requirement'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="78" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Chetwood is classified as a 'small and non-complex institution' (SNCI) and is not subject to any MREL requirement above its minimum capital requirement - stated explicitly in the FY2021, FY2022 and FY2023 Pillar 3 reports ('...has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its [minimum capital requirement]'). The FY2025 report uses a shorter reduced-disclosure format that omits this narrative section, but there is no indication Chetwood's MREL/SNCI status has changed. FY2019/FY2020 are left blank rather than 'Not applicable'. For FY2019 no Pillar 3 disclosure was published at all. For FY2020 one was (located 2026-09-15 - see the source note), but it was read in full and the word MREL does not appear anywhere in it, so Chetwood's SNCI/MREL status as at 31 March 2020 was still never publicly stated - blank remains correct for that year, now on evidence rather than on the absence of a document.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="377" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources (see entity note on Cash Flow Statement sheet):
-FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
-FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
-FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="234" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
-FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6088,6 +6135,139 @@
   <mergeCells count="2">
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="A39:H39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – Chetwood Pillar 3 FY2025 (SNCI reduced format) and Annual Report 2025 (text search, 2026-09-19) give no MREL figure or statement.</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – Chetwood Pillar 3 FY2024 (Nov 2024, SNCI reduced format, contents p.2) and Annual Report 2024 (text search, 2026-09-19) give no MREL figure or statement.</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – Chetwood Pillar 3 FY2023: 'has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its minimum capital requirement'.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – Chetwood Pillar 3 FY2022: 'has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its minimum capital requirement'.</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – Chetwood Pillar 3 FY2021: 'has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its minimum capital requirement'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Chetwood is classified as a 'small and non-complex institution' (SNCI) and is not subject to any MREL requirement above its minimum capital requirement - stated explicitly in the FY2021, FY2022 and FY2023 Pillar 3 reports ('...has no minimum requirements for Own funds and Eligible Liabilities (MREL) above its [minimum capital requirement]'). The FY2025 report uses a shorter reduced-disclosure format that omits this narrative section, but there is no indication Chetwood's MREL/SNCI status has changed. FY2019/FY2020 are left blank rather than 'Not applicable'. For FY2019 no Pillar 3 disclosure was published at all. For FY2020 one was (located 2026-09-15 - see the source note), but it was read in full and the word MREL does not appear anywhere in it, so Chetwood's SNCI/MREL status as at 31 March 2020 was still never publicly stated - blank remains correct for that year, now on evidence rather than on the absence of a document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="377" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources (see entity note on Cash Flow Statement sheet):
+FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
+FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
+FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
+FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
+OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
+FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="234" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf
+FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
+FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
+CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
+FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9648,6 +9828,309 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="51" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021†</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020†‡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019†‡</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>-2.55%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>-6.67%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>-73.38%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>-50.94%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>-41.78%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>-36.39%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>-2.40%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>-5.12%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>-62.87%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>-45.09%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>-41.92%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>-35.78%</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>-23.31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>-0.39%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>-6.14%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>-9.65%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>-8.83%</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>-10.65%</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>-3.89%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>-7.44%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-9.84%</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>-6.88%</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>-14.83%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Chetwood Financial Limited's own published return</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="143" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: COMPUTED, NOT PUBLISHED. Chetwood Financial Limited publishes no ROE, RoTE or ROA in its 2025 Annual Report. The full 118-page born-digital report was searched for return-on-equity/assets/tangible variants with no genuine match. The Strategic Report instead reports a £4.7m loss after tax (2024: £8.9m loss), funding and balance-sheet growth, and its path toward profitability. Every percentage above is therefore this project's own arithmetic on the figures printed on this workbook's statement sheets, and is labelled as such. That the bank publishes none is a POSITIVE FINDING, recorded in research/profitability/published_returns.jsonl, and not a failed search: for this bank the computed figure is the only figure there is.
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return. The two diverge most in FY2023, where return on equity is -73.38% on an average basis and -62.87% on a year-end basis.
+FY2019 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2019 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2019 because it needs only the closing balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “loss after tax and loss for the year” and the Balance Sheet rows “total equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from Chetwood Financial Limited's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The finding that Chetwood Financial Limited publishes no return of its own is recorded in research/profitability/published_returns.jsonl under ‘CHETWOOD’, verified against the bank's own annual report rendered at 300 dpi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A11:H11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10634,7 +11117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10773,183 +11256,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Chetwood Financial Limited — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>% of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021†</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020†‡</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.8%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>26.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>29.3%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital ratio per Annual Report KPI table (whole %, alternative basis - see note)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="390" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2024 comes from Chetwood's own FY2024 Pillar 3 ('Pillar 3 Disclosures November 2024', as at 31 March 2024), located 2026-09-19 on the bank's CMS file host after earlier passes had recorded it as never published (see source note). Its KM1 is single-column and headed '2023' although the document is as at 31 March 2024 - a source labelling defect; row 4 (824,623) equals the same document's OV1 '2024' total, which fixes the date. The Annual Reports' whole-percent KPI CET1 ratio remains a separate row on the CET1 Ratio sheet.
-FY2019 is likewise blank - Chetwood published no Pillar 3 disclosure for that year. FY2020 WAS previously blank on this basis and is now populated: see the source note's 2026-09-15 correction.
-SDDT RULED OUT, 2026-09-15 (cross-bank SDDT pass) - recorded as a negative result so this line of enquiry is not reopened. Many small UK deposit-takers' FY2024/FY2025 Pillar 3 gaps turn out to be the Small Domestic Deposit Taker (SDDT) exemption, which removes the Pillar 3 disclosure obligation outright. That is NOT the explanation here. Chetwood Financial Limited does not appear at all in the SDDT rows of the PRA's own firm-level register - the Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv). FRN 740551 'Chetwood Financial Limited' holds four modifications in that register (two Capital Requirements Regulation entries from 2017/2018, a Capital Buffers Part 5.1-5.3/5.5 direction from 10/09/2021, and an Individual Consolidation permission from 19/08/2024) and NONE is a modification by consent under Rule 3.1 of the 'SDDT Regime - General Application' Part - the instrument by which a firm becomes an SDDT, and which ten other banks checked in this same pass do hold.
-Corroborated by Chetwood's own documents. The FY2024 and FY2025 Annual Reports and the FY2025 Pillar 3 disclosure were downloaded and text-extracted in full (all three have readable text layers - 523k, 457k and 60k characters respectively, so these are true negatives, not scanned-PDF false negatives) and searched for 'SDDT', 'Small Domestic Deposit Taker', 'modification by consent', 'Simplified Retail Deposit Ratio', 'SRDR', 'Strong and Simple', 'Interim Capital Regime' and 'Basel 3.1'. Zero hits in any of the three - Chetwood does not mention the SDDT regime anywhere.
-What the FY2025 Pillar 3 document DOES state is a different proportionality regime, and it is the evidenced reason that document is short and single-column: section 2.3 'Basis of Preparation', p.3 - 'Chetwood meets the definition of a "small and non-complex institution" and is therefore subject to proportional disclosure requirements in accordance with Article 433b of the Disclosure (CRR) Part of the PRA Rulebook.' Article 433b is the reduced annual-disclosure article; unlike the SDDT modification it does not remove the obligation to publish, which is consistent with Chetwood still publishing a Pillar 3 document. (Written when FY2024 was believed absent; the FY2024 edition has since been found, 2026-09-19, and the SDDT finding above stands: no exemption applies.) FY2021 is as stated in the source (rounded to the nearest whole percent; no decimal figure was disclosed that year).
-FY2020 added 2026-09-15 from Chetwood's own 'Pillar 3 Disclosures June 2020 (as at 31st March 2020)' - a document earlier sessions concluded did not exist (see the source note's correction). That edition pre-dates the KM1 template, so it reports a narrative Summary-analysis table plus a capital-resources build-up rather than KM1 rows, and it states its ratios and RWA to whole percents / one decimal place of £m only. The FY2020 document's Summary-analysis table prints a 'Tier 1 Ratio' of 30% and no separate CET1 ratio line; its own capital-resources table shows CET1 £50,697k going straight to Tier 2 with no Additional Tier 1 line, so Tier 1 = CET1 that year and 30% is the CET1 ratio as well - the same treatment already applied to every other year on this sheet.
-SECOND ROW (alternative basis, added 2026-09-15): the Annual Reports' KPI tables were then thought the only source of any FY2024 capital ratio (the FY2024 Pillar 3, found 2026-09-19, prints 20.8%), and their whole-percent Group CET1 ratio is carried on its own row - FY2024 21% (stated identically in the FY2024 report's own year column and the FY2025 report's FY2024 comparative column, two independent confirmations). It is NOT merged into the primary row because the two series do not agree: for FY2025 the KPI table says 16% where the Pillar 3 KM1 says 15.2%, a difference too large to be rounding, cause not explained in either document (FY2023 does reconcile: 27% vs 26.6%). Treat the FY2024 21% as indicative of level, not as a KM1-basis figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="377" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Sources (see entity note on Cash Flow Statement sheet):
-FY2025: Chetwood Bank Pillar 3 Disclosures, September 2025 (as at 31 March 2025), Section 5 (Key Metrics - KM1) - https://chetwoodbank.co.uk/documents/chetwood-bank-pillar-three-disclosures.pdf
-FY2025 EDITION CHECK, 2026-09-19. 'September 2025' is the cover date printed on the live file, not a separate edition. The live undated URL (P3_25_URL) was re-downloaded on 2026-09-19 (HTTP 200, application/pdf, %PDF-1.7, 368,755 bytes, 15 pp., cover 'Pillar 3 Disclosures September 2025', 'as at 31 March 2025'; PDF CreationDate 7 Nov 2025 15:27:41 GMT, ModDate 15:27:42 GMT; MD5 b0be18a50b91c88280a99aced75e2265). The copies other sessions saved earlier in 2026 are byte-identical to it, and this workbook's FY2025 figures were first transcribed in 2026, so they come from this 7 Nov 2025 file. Every FY2025 figure the workbook carries was compared with it on 2026-09-19 and ALL MATCH: KM1 (Section 5, printed pp.9-10) rows 1-3 187,605; 4 1,233,321; 5-7 15.2%; UK 7a 1.92%; UK 7b/7c '-'; UK 7d 9.92%; 8 2.50%; 9 2.00%; 11 4.50%; UK 11a 14.42%; 12 5.29%; 13 3,615,720; 14 5.19%; 15 897,493; UK 16a 489,794; UK 16b 28,009; 16 461,785; 17 194%; 18 3,677,559; 19 2,536,343; 20 145%; and OV1 (Section 6.3, printed p.11) 2025 column credit risk 1,017,779, CCR 23,777, securitisation 102,610, operational risk 89,154, total 1,233,321, plus its 2024 comparative 703,828 / 13,638 / 62,980 / 44,177 / 824,623, which also equals the FY2024 edition's own figures. No other FY2025 copy was found, so no second edition could be compared: Wayback CDX holds no capture of any chetwoodbank.co.uk/documents/ URL (prefix query); the nine cdn.sanity.io PDFs linked from archived homepages of Nov 2024-Jun 2025 are the FY2023/FY2024 Pillar 3, AR2024, complaints, governance, gender-pay, tax and supplier documents, none the FY2025 Pillar 3; CDX of cdn.sanity.io/files/cdijb9eo/ holds 7 files, none of them it; homepages from 7 Aug 2025 onward link only the undated /documents/ path; archive.ph has no copy (404); a web search returned none. The homepage of 7 Aug 2025 already links the /documents/ Pillar 3 path, so an earlier file may have been served there before 7 Nov 2025. It was never captured, so whether it differs is unreached, not established.
-FY2024: Chetwood Bank Pillar 3 Disclosures, November 2024 (as at 31 March 2024), Section 5 (Key Metrics - KM1) pp.10-11 of 15 and Section 6.3 (OV1) p.12 - https://cdn.sanity.io/files/cdijb9eo/production/c43453174d3cd53859ae5bf91d91ff6a901b314b.pdf
-FY2024 CORRECTION, 2026-09-19. Until 2026-09-19 this workbook said that no FY2024 Pillar 3 was ever published, after a search of chetwood.co and chetwoodbank.co.uk (live site, dated URL variants, Wayback CDX of both domains) and of both Annual Reports. That was a claim about our search, not about the bank: the edition exists and was on the CMS file host cdn.sanity.io all along, linked from the bank's own homepage (Wayback 20250430162819). Its KM1 column is headed '2023' although the document states on p.3 that it is 'as at 31 March 2024' and its KM1 row 4 (824,623) equals the OV1 table's '2024' column on p.12 (and the FY2025 edition's 2024 comparative), so the '2023' heading is a source labelling defect, reproduced in this note rather than corrected in the data.
-OUT-OF-SCOPE LEAD (not acted on here): that CDX scan also turned up an un-cited Pillar 3 snapshot at http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf, captured Sept 2020 - i.e. predating the 'as at 31 March 2021' edition this workbook currently treats as Chetwood's earliest. It was not opened or transcribed in this pass (the FY2019/FY2020 columns are an exterior, not interior, gap and were out of scope), but it should be checked before the FY2019/FY2020 'no Pillar 3 was ever published' claim below is relied on.
-FY2023: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2023, Section 6 (Key Metrics - KM1) and Section 7.1 (Capital Resources) - http://web.archive.org/web/20240315022245id_/https://chetwood.co/static/330c40d433df90b83d3b3e5c673e21cc/Pillar3Disclosures.pdf
-FY2022: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2022, Annex B (Key Metrics - KM1) - http://web.archive.org/web/20230131235943id_/https://chetwood.co/static/815e2dd174c4655ddf55a93ca1029ce3/Pillar3Disclosures.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="195" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
-FY2021: Chetwood Financial Ltd Pillar 3 Disclosure, as at 31 March 2021, Section 1.2 (Summary Analysis) and Section 4 (Capital Resources) - http://web.archive.org/web/20211128171331id_/https://chetwood.co/static/221a3946677e4d8c49c5525d22f9b534/Pillar3Disclosures.pdf (pre-dates the formal KM1 template; Chetwood adopted the CRR KM1 annex from the FY2022 report onward)
-FY2020: Chetwood Financial Ltd Pillar 3 Disclosures, June 2020 ('as at 31st March 2020'), Section 1.2 (Summary analysis, p.3), Section 3.3 (Capital Resources, p.15), Section 3.6 (The leverage ratio, p.16) and Section 5.2 (Liquidity ratios, p.18) - http://web.archive.org/web/20200929085826id_/https://chetwood.co/static/ea27728be3ae831ddb0ef7888e332546/Pillar3Disclosures.pdf
-CORRECTION (2026-09-15): earlier versions of this workbook stated that 'no Pillar 3 disclosure was ever published' for FY2019/FY2020 and that the 'as at 31 March 2021' edition was Chetwood's earliest. That was wrong for FY2020. A Wayback CDX scan of the whole chetwood.co domain surfaced a 23-page 'Pillar 3 Disclosures June 2020' PDF at an un-cited static path (captured 29 Sept 2020, real text layer, 767KB - not a soft 404), carrying a full FY2020 capital/leverage/liquidity set. Every FY2020 Pillar 3 figure in this workbook comes from that document. It pre-dates the formal KM1 template (like the FY2021 edition), so its figures are narrative/summary-table style rather than KM1 rows; the capital-resources table's build-up (share capital 84,688 + share premium 2,851 + retained earnings (36,357) - intangibles (485) = CET1 50,697) ties exactly to the FY2020 Balance Sheet sheet's own as-filed FRS 102 figures, an independent confirmation that the document is Chetwood's own and is for the right year.
-FY2019: still genuinely blank. The FY2020 document is a single-column 'as at 31 March 2020' disclosure with no FY2019 comparative anywhere in it, and no earlier Pillar 3 snapshot exists in the Wayback CDX index for either chetwood.co or chetwoodbank.co.uk (Chetwood's own FY2018/FY2019 strategic reports say a Pillar 3 document 'will be published...in due course').</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A10:G10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>